--- a/theme/calcmycard/assets/downloads/credit-card-interest-calculator-template.xlsx
+++ b/theme/calcmycard/assets/downloads/credit-card-interest-calculator-template.xlsx
@@ -149,7 +149,7 @@
         </is>
       </c>
       <c r="B9" s="8">
-        <f>IF(B12&lt;&gt;"","Never",COUNTIF(B14:B613,"&gt;0"))</f>
+        <f>IF(B6+B7&lt;=ROUND(B4*B5/12,2),"Never",IF(F613&gt;0.005,"Over 600",COUNTIF(B14:B613,"&gt;0.005")))</f>
         <v>58</v>
       </c>
     </row>
@@ -160,7 +160,7 @@
         </is>
       </c>
       <c r="B10" s="2">
-        <f>SUM(C14:C613)</f>
+        <f>IF(B6+B7&lt;=ROUND(B4*B5/12,2),"n/a",SUM(C14:C613))</f>
         <v>3622.26</v>
       </c>
     </row>
@@ -171,7 +171,7 @@
         </is>
       </c>
       <c r="B11" s="2">
-        <f>SUM(D14:D613)</f>
+        <f>IF(B6+B7&lt;=ROUND(B4*B5/12,2),"n/a",SUM(D14:D613))</f>
         <v>8622.26</v>
       </c>
     </row>
@@ -182,7 +182,7 @@
         </is>
       </c>
       <c r="B12" s="0" t="str">
-        <f>IF(B6+B7&lt;=ROUND(B4*B5/12,2),"Payment does not cover the monthly interest, so this balance never gets paid off.","")</f>
+        <f>IF(B6+B7&lt;=ROUND(B4*B5/12,2),"Payment does not cover the monthly interest, so this balance never gets paid off.",IF(F613&gt;0.005,"This payment takes more than 50 years (600 months), so the balance is not paid off within this table.",""))</f>
         <v/>
       </c>
     </row>
@@ -227,11 +227,11 @@
         <v>5000</v>
       </c>
       <c r="C14" s="2">
-        <f>IF(B14&gt;0,ROUND(B14*$B$5/12,2),0)</f>
+        <f>IF(B14&gt;0.005,ROUND(B14*$B$5/12,2),0)</f>
         <v>104.13</v>
       </c>
       <c r="D14" s="2">
-        <f>IF(B14&gt;0,MIN($B$6+$B$7,B14+C14),0)</f>
+        <f>IF(B14&gt;0.005,MIN($B$6+$B$7,B14+C14),0)</f>
         <v>150.0</v>
       </c>
       <c r="E14" s="2">
@@ -252,11 +252,11 @@
         <v>4954.13</v>
       </c>
       <c r="C15" s="2">
-        <f>IF(B15&gt;0,ROUND(B15*$B$5/12,2),0)</f>
+        <f>IF(B15&gt;0.005,ROUND(B15*$B$5/12,2),0)</f>
         <v>103.17</v>
       </c>
       <c r="D15" s="2">
-        <f>IF(B15&gt;0,MIN($B$6+$B$7,B15+C15),0)</f>
+        <f>IF(B15&gt;0.005,MIN($B$6+$B$7,B15+C15),0)</f>
         <v>150.0</v>
       </c>
       <c r="E15" s="2">
@@ -277,11 +277,11 @@
         <v>4907.3</v>
       </c>
       <c r="C16" s="2">
-        <f>IF(B16&gt;0,ROUND(B16*$B$5/12,2),0)</f>
+        <f>IF(B16&gt;0.005,ROUND(B16*$B$5/12,2),0)</f>
         <v>102.19</v>
       </c>
       <c r="D16" s="2">
-        <f>IF(B16&gt;0,MIN($B$6+$B$7,B16+C16),0)</f>
+        <f>IF(B16&gt;0.005,MIN($B$6+$B$7,B16+C16),0)</f>
         <v>150.0</v>
       </c>
       <c r="E16" s="2">
@@ -302,11 +302,11 @@
         <v>4859.49</v>
       </c>
       <c r="C17" s="2">
-        <f>IF(B17&gt;0,ROUND(B17*$B$5/12,2),0)</f>
+        <f>IF(B17&gt;0.005,ROUND(B17*$B$5/12,2),0)</f>
         <v>101.2</v>
       </c>
       <c r="D17" s="2">
-        <f>IF(B17&gt;0,MIN($B$6+$B$7,B17+C17),0)</f>
+        <f>IF(B17&gt;0.005,MIN($B$6+$B$7,B17+C17),0)</f>
         <v>150.0</v>
       </c>
       <c r="E17" s="2">
@@ -327,11 +327,11 @@
         <v>4810.69</v>
       </c>
       <c r="C18" s="2">
-        <f>IF(B18&gt;0,ROUND(B18*$B$5/12,2),0)</f>
+        <f>IF(B18&gt;0.005,ROUND(B18*$B$5/12,2),0)</f>
         <v>100.18</v>
       </c>
       <c r="D18" s="2">
-        <f>IF(B18&gt;0,MIN($B$6+$B$7,B18+C18),0)</f>
+        <f>IF(B18&gt;0.005,MIN($B$6+$B$7,B18+C18),0)</f>
         <v>150.0</v>
       </c>
       <c r="E18" s="2">
@@ -352,11 +352,11 @@
         <v>4760.87</v>
       </c>
       <c r="C19" s="2">
-        <f>IF(B19&gt;0,ROUND(B19*$B$5/12,2),0)</f>
+        <f>IF(B19&gt;0.005,ROUND(B19*$B$5/12,2),0)</f>
         <v>99.15</v>
       </c>
       <c r="D19" s="2">
-        <f>IF(B19&gt;0,MIN($B$6+$B$7,B19+C19),0)</f>
+        <f>IF(B19&gt;0.005,MIN($B$6+$B$7,B19+C19),0)</f>
         <v>150.0</v>
       </c>
       <c r="E19" s="2">
@@ -377,11 +377,11 @@
         <v>4710.02</v>
       </c>
       <c r="C20" s="2">
-        <f>IF(B20&gt;0,ROUND(B20*$B$5/12,2),0)</f>
+        <f>IF(B20&gt;0.005,ROUND(B20*$B$5/12,2),0)</f>
         <v>98.09</v>
       </c>
       <c r="D20" s="2">
-        <f>IF(B20&gt;0,MIN($B$6+$B$7,B20+C20),0)</f>
+        <f>IF(B20&gt;0.005,MIN($B$6+$B$7,B20+C20),0)</f>
         <v>150.0</v>
       </c>
       <c r="E20" s="2">
@@ -402,11 +402,11 @@
         <v>4658.11</v>
       </c>
       <c r="C21" s="2">
-        <f>IF(B21&gt;0,ROUND(B21*$B$5/12,2),0)</f>
+        <f>IF(B21&gt;0.005,ROUND(B21*$B$5/12,2),0)</f>
         <v>97.01</v>
       </c>
       <c r="D21" s="2">
-        <f>IF(B21&gt;0,MIN($B$6+$B$7,B21+C21),0)</f>
+        <f>IF(B21&gt;0.005,MIN($B$6+$B$7,B21+C21),0)</f>
         <v>150.0</v>
       </c>
       <c r="E21" s="2">
@@ -427,11 +427,11 @@
         <v>4605.12</v>
       </c>
       <c r="C22" s="2">
-        <f>IF(B22&gt;0,ROUND(B22*$B$5/12,2),0)</f>
+        <f>IF(B22&gt;0.005,ROUND(B22*$B$5/12,2),0)</f>
         <v>95.9</v>
       </c>
       <c r="D22" s="2">
-        <f>IF(B22&gt;0,MIN($B$6+$B$7,B22+C22),0)</f>
+        <f>IF(B22&gt;0.005,MIN($B$6+$B$7,B22+C22),0)</f>
         <v>150.0</v>
       </c>
       <c r="E22" s="2">
@@ -452,11 +452,11 @@
         <v>4551.02</v>
       </c>
       <c r="C23" s="2">
-        <f>IF(B23&gt;0,ROUND(B23*$B$5/12,2),0)</f>
+        <f>IF(B23&gt;0.005,ROUND(B23*$B$5/12,2),0)</f>
         <v>94.77</v>
       </c>
       <c r="D23" s="2">
-        <f>IF(B23&gt;0,MIN($B$6+$B$7,B23+C23),0)</f>
+        <f>IF(B23&gt;0.005,MIN($B$6+$B$7,B23+C23),0)</f>
         <v>150.0</v>
       </c>
       <c r="E23" s="2">
@@ -477,11 +477,11 @@
         <v>4495.79</v>
       </c>
       <c r="C24" s="2">
-        <f>IF(B24&gt;0,ROUND(B24*$B$5/12,2),0)</f>
+        <f>IF(B24&gt;0.005,ROUND(B24*$B$5/12,2),0)</f>
         <v>93.62</v>
       </c>
       <c r="D24" s="2">
-        <f>IF(B24&gt;0,MIN($B$6+$B$7,B24+C24),0)</f>
+        <f>IF(B24&gt;0.005,MIN($B$6+$B$7,B24+C24),0)</f>
         <v>150.0</v>
       </c>
       <c r="E24" s="2">
@@ -502,11 +502,11 @@
         <v>4439.41</v>
       </c>
       <c r="C25" s="2">
-        <f>IF(B25&gt;0,ROUND(B25*$B$5/12,2),0)</f>
+        <f>IF(B25&gt;0.005,ROUND(B25*$B$5/12,2),0)</f>
         <v>92.45</v>
       </c>
       <c r="D25" s="2">
-        <f>IF(B25&gt;0,MIN($B$6+$B$7,B25+C25),0)</f>
+        <f>IF(B25&gt;0.005,MIN($B$6+$B$7,B25+C25),0)</f>
         <v>150.0</v>
       </c>
       <c r="E25" s="2">
@@ -527,11 +527,11 @@
         <v>4381.86</v>
       </c>
       <c r="C26" s="2">
-        <f>IF(B26&gt;0,ROUND(B26*$B$5/12,2),0)</f>
+        <f>IF(B26&gt;0.005,ROUND(B26*$B$5/12,2),0)</f>
         <v>91.25</v>
       </c>
       <c r="D26" s="2">
-        <f>IF(B26&gt;0,MIN($B$6+$B$7,B26+C26),0)</f>
+        <f>IF(B26&gt;0.005,MIN($B$6+$B$7,B26+C26),0)</f>
         <v>150.0</v>
       </c>
       <c r="E26" s="2">
@@ -552,11 +552,11 @@
         <v>4323.11</v>
       </c>
       <c r="C27" s="2">
-        <f>IF(B27&gt;0,ROUND(B27*$B$5/12,2),0)</f>
+        <f>IF(B27&gt;0.005,ROUND(B27*$B$5/12,2),0)</f>
         <v>90.03</v>
       </c>
       <c r="D27" s="2">
-        <f>IF(B27&gt;0,MIN($B$6+$B$7,B27+C27),0)</f>
+        <f>IF(B27&gt;0.005,MIN($B$6+$B$7,B27+C27),0)</f>
         <v>150.0</v>
       </c>
       <c r="E27" s="2">
@@ -577,11 +577,11 @@
         <v>4263.14</v>
       </c>
       <c r="C28" s="2">
-        <f>IF(B28&gt;0,ROUND(B28*$B$5/12,2),0)</f>
+        <f>IF(B28&gt;0.005,ROUND(B28*$B$5/12,2),0)</f>
         <v>88.78</v>
       </c>
       <c r="D28" s="2">
-        <f>IF(B28&gt;0,MIN($B$6+$B$7,B28+C28),0)</f>
+        <f>IF(B28&gt;0.005,MIN($B$6+$B$7,B28+C28),0)</f>
         <v>150.0</v>
       </c>
       <c r="E28" s="2">
@@ -602,11 +602,11 @@
         <v>4201.92</v>
       </c>
       <c r="C29" s="2">
-        <f>IF(B29&gt;0,ROUND(B29*$B$5/12,2),0)</f>
+        <f>IF(B29&gt;0.005,ROUND(B29*$B$5/12,2),0)</f>
         <v>87.5</v>
       </c>
       <c r="D29" s="2">
-        <f>IF(B29&gt;0,MIN($B$6+$B$7,B29+C29),0)</f>
+        <f>IF(B29&gt;0.005,MIN($B$6+$B$7,B29+C29),0)</f>
         <v>150.0</v>
       </c>
       <c r="E29" s="2">
@@ -627,11 +627,11 @@
         <v>4139.42</v>
       </c>
       <c r="C30" s="2">
-        <f>IF(B30&gt;0,ROUND(B30*$B$5/12,2),0)</f>
+        <f>IF(B30&gt;0.005,ROUND(B30*$B$5/12,2),0)</f>
         <v>86.2</v>
       </c>
       <c r="D30" s="2">
-        <f>IF(B30&gt;0,MIN($B$6+$B$7,B30+C30),0)</f>
+        <f>IF(B30&gt;0.005,MIN($B$6+$B$7,B30+C30),0)</f>
         <v>150.0</v>
       </c>
       <c r="E30" s="2">
@@ -652,11 +652,11 @@
         <v>4075.62</v>
       </c>
       <c r="C31" s="2">
-        <f>IF(B31&gt;0,ROUND(B31*$B$5/12,2),0)</f>
+        <f>IF(B31&gt;0.005,ROUND(B31*$B$5/12,2),0)</f>
         <v>84.87</v>
       </c>
       <c r="D31" s="2">
-        <f>IF(B31&gt;0,MIN($B$6+$B$7,B31+C31),0)</f>
+        <f>IF(B31&gt;0.005,MIN($B$6+$B$7,B31+C31),0)</f>
         <v>150.0</v>
       </c>
       <c r="E31" s="2">
@@ -677,11 +677,11 @@
         <v>4010.49</v>
       </c>
       <c r="C32" s="2">
-        <f>IF(B32&gt;0,ROUND(B32*$B$5/12,2),0)</f>
+        <f>IF(B32&gt;0.005,ROUND(B32*$B$5/12,2),0)</f>
         <v>83.52</v>
       </c>
       <c r="D32" s="2">
-        <f>IF(B32&gt;0,MIN($B$6+$B$7,B32+C32),0)</f>
+        <f>IF(B32&gt;0.005,MIN($B$6+$B$7,B32+C32),0)</f>
         <v>150.0</v>
       </c>
       <c r="E32" s="2">
@@ -702,11 +702,11 @@
         <v>3944.01</v>
       </c>
       <c r="C33" s="2">
-        <f>IF(B33&gt;0,ROUND(B33*$B$5/12,2),0)</f>
+        <f>IF(B33&gt;0.005,ROUND(B33*$B$5/12,2),0)</f>
         <v>82.13</v>
       </c>
       <c r="D33" s="2">
-        <f>IF(B33&gt;0,MIN($B$6+$B$7,B33+C33),0)</f>
+        <f>IF(B33&gt;0.005,MIN($B$6+$B$7,B33+C33),0)</f>
         <v>150.0</v>
       </c>
       <c r="E33" s="2">
@@ -727,11 +727,11 @@
         <v>3876.14</v>
       </c>
       <c r="C34" s="2">
-        <f>IF(B34&gt;0,ROUND(B34*$B$5/12,2),0)</f>
+        <f>IF(B34&gt;0.005,ROUND(B34*$B$5/12,2),0)</f>
         <v>80.72</v>
       </c>
       <c r="D34" s="2">
-        <f>IF(B34&gt;0,MIN($B$6+$B$7,B34+C34),0)</f>
+        <f>IF(B34&gt;0.005,MIN($B$6+$B$7,B34+C34),0)</f>
         <v>150.0</v>
       </c>
       <c r="E34" s="2">
@@ -752,11 +752,11 @@
         <v>3806.86</v>
       </c>
       <c r="C35" s="2">
-        <f>IF(B35&gt;0,ROUND(B35*$B$5/12,2),0)</f>
+        <f>IF(B35&gt;0.005,ROUND(B35*$B$5/12,2),0)</f>
         <v>79.28</v>
       </c>
       <c r="D35" s="2">
-        <f>IF(B35&gt;0,MIN($B$6+$B$7,B35+C35),0)</f>
+        <f>IF(B35&gt;0.005,MIN($B$6+$B$7,B35+C35),0)</f>
         <v>150.0</v>
       </c>
       <c r="E35" s="2">
@@ -777,11 +777,11 @@
         <v>3736.14</v>
       </c>
       <c r="C36" s="2">
-        <f>IF(B36&gt;0,ROUND(B36*$B$5/12,2),0)</f>
+        <f>IF(B36&gt;0.005,ROUND(B36*$B$5/12,2),0)</f>
         <v>77.81</v>
       </c>
       <c r="D36" s="2">
-        <f>IF(B36&gt;0,MIN($B$6+$B$7,B36+C36),0)</f>
+        <f>IF(B36&gt;0.005,MIN($B$6+$B$7,B36+C36),0)</f>
         <v>150.0</v>
       </c>
       <c r="E36" s="2">
@@ -802,11 +802,11 @@
         <v>3663.95</v>
       </c>
       <c r="C37" s="2">
-        <f>IF(B37&gt;0,ROUND(B37*$B$5/12,2),0)</f>
+        <f>IF(B37&gt;0.005,ROUND(B37*$B$5/12,2),0)</f>
         <v>76.3</v>
       </c>
       <c r="D37" s="2">
-        <f>IF(B37&gt;0,MIN($B$6+$B$7,B37+C37),0)</f>
+        <f>IF(B37&gt;0.005,MIN($B$6+$B$7,B37+C37),0)</f>
         <v>150.0</v>
       </c>
       <c r="E37" s="2">
@@ -827,11 +827,11 @@
         <v>3590.25</v>
       </c>
       <c r="C38" s="2">
-        <f>IF(B38&gt;0,ROUND(B38*$B$5/12,2),0)</f>
+        <f>IF(B38&gt;0.005,ROUND(B38*$B$5/12,2),0)</f>
         <v>74.77</v>
       </c>
       <c r="D38" s="2">
-        <f>IF(B38&gt;0,MIN($B$6+$B$7,B38+C38),0)</f>
+        <f>IF(B38&gt;0.005,MIN($B$6+$B$7,B38+C38),0)</f>
         <v>150.0</v>
       </c>
       <c r="E38" s="2">
@@ -852,11 +852,11 @@
         <v>3515.02</v>
       </c>
       <c r="C39" s="2">
-        <f>IF(B39&gt;0,ROUND(B39*$B$5/12,2),0)</f>
+        <f>IF(B39&gt;0.005,ROUND(B39*$B$5/12,2),0)</f>
         <v>73.2</v>
       </c>
       <c r="D39" s="2">
-        <f>IF(B39&gt;0,MIN($B$6+$B$7,B39+C39),0)</f>
+        <f>IF(B39&gt;0.005,MIN($B$6+$B$7,B39+C39),0)</f>
         <v>150.0</v>
       </c>
       <c r="E39" s="2">
@@ -877,11 +877,11 @@
         <v>3438.22</v>
       </c>
       <c r="C40" s="2">
-        <f>IF(B40&gt;0,ROUND(B40*$B$5/12,2),0)</f>
+        <f>IF(B40&gt;0.005,ROUND(B40*$B$5/12,2),0)</f>
         <v>71.6</v>
       </c>
       <c r="D40" s="2">
-        <f>IF(B40&gt;0,MIN($B$6+$B$7,B40+C40),0)</f>
+        <f>IF(B40&gt;0.005,MIN($B$6+$B$7,B40+C40),0)</f>
         <v>150.0</v>
       </c>
       <c r="E40" s="2">
@@ -902,11 +902,11 @@
         <v>3359.82</v>
       </c>
       <c r="C41" s="2">
-        <f>IF(B41&gt;0,ROUND(B41*$B$5/12,2),0)</f>
+        <f>IF(B41&gt;0.005,ROUND(B41*$B$5/12,2),0)</f>
         <v>69.97</v>
       </c>
       <c r="D41" s="2">
-        <f>IF(B41&gt;0,MIN($B$6+$B$7,B41+C41),0)</f>
+        <f>IF(B41&gt;0.005,MIN($B$6+$B$7,B41+C41),0)</f>
         <v>150.0</v>
       </c>
       <c r="E41" s="2">
@@ -927,11 +927,11 @@
         <v>3279.79</v>
       </c>
       <c r="C42" s="2">
-        <f>IF(B42&gt;0,ROUND(B42*$B$5/12,2),0)</f>
+        <f>IF(B42&gt;0.005,ROUND(B42*$B$5/12,2),0)</f>
         <v>68.3</v>
       </c>
       <c r="D42" s="2">
-        <f>IF(B42&gt;0,MIN($B$6+$B$7,B42+C42),0)</f>
+        <f>IF(B42&gt;0.005,MIN($B$6+$B$7,B42+C42),0)</f>
         <v>150.0</v>
       </c>
       <c r="E42" s="2">
@@ -952,11 +952,11 @@
         <v>3198.09</v>
       </c>
       <c r="C43" s="2">
-        <f>IF(B43&gt;0,ROUND(B43*$B$5/12,2),0)</f>
+        <f>IF(B43&gt;0.005,ROUND(B43*$B$5/12,2),0)</f>
         <v>66.6</v>
       </c>
       <c r="D43" s="2">
-        <f>IF(B43&gt;0,MIN($B$6+$B$7,B43+C43),0)</f>
+        <f>IF(B43&gt;0.005,MIN($B$6+$B$7,B43+C43),0)</f>
         <v>150.0</v>
       </c>
       <c r="E43" s="2">
@@ -977,11 +977,11 @@
         <v>3114.69</v>
       </c>
       <c r="C44" s="2">
-        <f>IF(B44&gt;0,ROUND(B44*$B$5/12,2),0)</f>
+        <f>IF(B44&gt;0.005,ROUND(B44*$B$5/12,2),0)</f>
         <v>64.86</v>
       </c>
       <c r="D44" s="2">
-        <f>IF(B44&gt;0,MIN($B$6+$B$7,B44+C44),0)</f>
+        <f>IF(B44&gt;0.005,MIN($B$6+$B$7,B44+C44),0)</f>
         <v>150.0</v>
       </c>
       <c r="E44" s="2">
@@ -1002,11 +1002,11 @@
         <v>3029.55</v>
       </c>
       <c r="C45" s="2">
-        <f>IF(B45&gt;0,ROUND(B45*$B$5/12,2),0)</f>
+        <f>IF(B45&gt;0.005,ROUND(B45*$B$5/12,2),0)</f>
         <v>63.09</v>
       </c>
       <c r="D45" s="2">
-        <f>IF(B45&gt;0,MIN($B$6+$B$7,B45+C45),0)</f>
+        <f>IF(B45&gt;0.005,MIN($B$6+$B$7,B45+C45),0)</f>
         <v>150.0</v>
       </c>
       <c r="E45" s="2">
@@ -1027,11 +1027,11 @@
         <v>2942.64</v>
       </c>
       <c r="C46" s="2">
-        <f>IF(B46&gt;0,ROUND(B46*$B$5/12,2),0)</f>
+        <f>IF(B46&gt;0.005,ROUND(B46*$B$5/12,2),0)</f>
         <v>61.28</v>
       </c>
       <c r="D46" s="2">
-        <f>IF(B46&gt;0,MIN($B$6+$B$7,B46+C46),0)</f>
+        <f>IF(B46&gt;0.005,MIN($B$6+$B$7,B46+C46),0)</f>
         <v>150.0</v>
       </c>
       <c r="E46" s="2">
@@ -1052,11 +1052,11 @@
         <v>2853.92</v>
       </c>
       <c r="C47" s="2">
-        <f>IF(B47&gt;0,ROUND(B47*$B$5/12,2),0)</f>
+        <f>IF(B47&gt;0.005,ROUND(B47*$B$5/12,2),0)</f>
         <v>59.43</v>
       </c>
       <c r="D47" s="2">
-        <f>IF(B47&gt;0,MIN($B$6+$B$7,B47+C47),0)</f>
+        <f>IF(B47&gt;0.005,MIN($B$6+$B$7,B47+C47),0)</f>
         <v>150.0</v>
       </c>
       <c r="E47" s="2">
@@ -1077,11 +1077,11 @@
         <v>2763.35</v>
       </c>
       <c r="C48" s="2">
-        <f>IF(B48&gt;0,ROUND(B48*$B$5/12,2),0)</f>
+        <f>IF(B48&gt;0.005,ROUND(B48*$B$5/12,2),0)</f>
         <v>57.55</v>
       </c>
       <c r="D48" s="2">
-        <f>IF(B48&gt;0,MIN($B$6+$B$7,B48+C48),0)</f>
+        <f>IF(B48&gt;0.005,MIN($B$6+$B$7,B48+C48),0)</f>
         <v>150.0</v>
       </c>
       <c r="E48" s="2">
@@ -1102,11 +1102,11 @@
         <v>2670.9</v>
       </c>
       <c r="C49" s="2">
-        <f>IF(B49&gt;0,ROUND(B49*$B$5/12,2),0)</f>
+        <f>IF(B49&gt;0.005,ROUND(B49*$B$5/12,2),0)</f>
         <v>55.62</v>
       </c>
       <c r="D49" s="2">
-        <f>IF(B49&gt;0,MIN($B$6+$B$7,B49+C49),0)</f>
+        <f>IF(B49&gt;0.005,MIN($B$6+$B$7,B49+C49),0)</f>
         <v>150.0</v>
       </c>
       <c r="E49" s="2">
@@ -1127,11 +1127,11 @@
         <v>2576.52</v>
       </c>
       <c r="C50" s="2">
-        <f>IF(B50&gt;0,ROUND(B50*$B$5/12,2),0)</f>
+        <f>IF(B50&gt;0.005,ROUND(B50*$B$5/12,2),0)</f>
         <v>53.66</v>
       </c>
       <c r="D50" s="2">
-        <f>IF(B50&gt;0,MIN($B$6+$B$7,B50+C50),0)</f>
+        <f>IF(B50&gt;0.005,MIN($B$6+$B$7,B50+C50),0)</f>
         <v>150.0</v>
       </c>
       <c r="E50" s="2">
@@ -1152,11 +1152,11 @@
         <v>2480.18</v>
       </c>
       <c r="C51" s="2">
-        <f>IF(B51&gt;0,ROUND(B51*$B$5/12,2),0)</f>
+        <f>IF(B51&gt;0.005,ROUND(B51*$B$5/12,2),0)</f>
         <v>51.65</v>
       </c>
       <c r="D51" s="2">
-        <f>IF(B51&gt;0,MIN($B$6+$B$7,B51+C51),0)</f>
+        <f>IF(B51&gt;0.005,MIN($B$6+$B$7,B51+C51),0)</f>
         <v>150.0</v>
       </c>
       <c r="E51" s="2">
@@ -1177,11 +1177,11 @@
         <v>2381.83</v>
       </c>
       <c r="C52" s="2">
-        <f>IF(B52&gt;0,ROUND(B52*$B$5/12,2),0)</f>
+        <f>IF(B52&gt;0.005,ROUND(B52*$B$5/12,2),0)</f>
         <v>49.6</v>
       </c>
       <c r="D52" s="2">
-        <f>IF(B52&gt;0,MIN($B$6+$B$7,B52+C52),0)</f>
+        <f>IF(B52&gt;0.005,MIN($B$6+$B$7,B52+C52),0)</f>
         <v>150.0</v>
       </c>
       <c r="E52" s="2">
@@ -1202,11 +1202,11 @@
         <v>2281.43</v>
       </c>
       <c r="C53" s="2">
-        <f>IF(B53&gt;0,ROUND(B53*$B$5/12,2),0)</f>
+        <f>IF(B53&gt;0.005,ROUND(B53*$B$5/12,2),0)</f>
         <v>47.51</v>
       </c>
       <c r="D53" s="2">
-        <f>IF(B53&gt;0,MIN($B$6+$B$7,B53+C53),0)</f>
+        <f>IF(B53&gt;0.005,MIN($B$6+$B$7,B53+C53),0)</f>
         <v>150.0</v>
       </c>
       <c r="E53" s="2">
@@ -1227,11 +1227,11 @@
         <v>2178.94</v>
       </c>
       <c r="C54" s="2">
-        <f>IF(B54&gt;0,ROUND(B54*$B$5/12,2),0)</f>
+        <f>IF(B54&gt;0.005,ROUND(B54*$B$5/12,2),0)</f>
         <v>45.38</v>
       </c>
       <c r="D54" s="2">
-        <f>IF(B54&gt;0,MIN($B$6+$B$7,B54+C54),0)</f>
+        <f>IF(B54&gt;0.005,MIN($B$6+$B$7,B54+C54),0)</f>
         <v>150.0</v>
       </c>
       <c r="E54" s="2">
@@ -1252,11 +1252,11 @@
         <v>2074.32</v>
       </c>
       <c r="C55" s="2">
-        <f>IF(B55&gt;0,ROUND(B55*$B$5/12,2),0)</f>
+        <f>IF(B55&gt;0.005,ROUND(B55*$B$5/12,2),0)</f>
         <v>43.2</v>
       </c>
       <c r="D55" s="2">
-        <f>IF(B55&gt;0,MIN($B$6+$B$7,B55+C55),0)</f>
+        <f>IF(B55&gt;0.005,MIN($B$6+$B$7,B55+C55),0)</f>
         <v>150.0</v>
       </c>
       <c r="E55" s="2">
@@ -1277,11 +1277,11 @@
         <v>1967.52</v>
       </c>
       <c r="C56" s="2">
-        <f>IF(B56&gt;0,ROUND(B56*$B$5/12,2),0)</f>
+        <f>IF(B56&gt;0.005,ROUND(B56*$B$5/12,2),0)</f>
         <v>40.97</v>
       </c>
       <c r="D56" s="2">
-        <f>IF(B56&gt;0,MIN($B$6+$B$7,B56+C56),0)</f>
+        <f>IF(B56&gt;0.005,MIN($B$6+$B$7,B56+C56),0)</f>
         <v>150.0</v>
       </c>
       <c r="E56" s="2">
@@ -1302,11 +1302,11 @@
         <v>1858.49</v>
       </c>
       <c r="C57" s="2">
-        <f>IF(B57&gt;0,ROUND(B57*$B$5/12,2),0)</f>
+        <f>IF(B57&gt;0.005,ROUND(B57*$B$5/12,2),0)</f>
         <v>38.7</v>
       </c>
       <c r="D57" s="2">
-        <f>IF(B57&gt;0,MIN($B$6+$B$7,B57+C57),0)</f>
+        <f>IF(B57&gt;0.005,MIN($B$6+$B$7,B57+C57),0)</f>
         <v>150.0</v>
       </c>
       <c r="E57" s="2">
@@ -1327,11 +1327,11 @@
         <v>1747.19</v>
       </c>
       <c r="C58" s="2">
-        <f>IF(B58&gt;0,ROUND(B58*$B$5/12,2),0)</f>
+        <f>IF(B58&gt;0.005,ROUND(B58*$B$5/12,2),0)</f>
         <v>36.39</v>
       </c>
       <c r="D58" s="2">
-        <f>IF(B58&gt;0,MIN($B$6+$B$7,B58+C58),0)</f>
+        <f>IF(B58&gt;0.005,MIN($B$6+$B$7,B58+C58),0)</f>
         <v>150.0</v>
       </c>
       <c r="E58" s="2">
@@ -1352,11 +1352,11 @@
         <v>1633.58</v>
       </c>
       <c r="C59" s="2">
-        <f>IF(B59&gt;0,ROUND(B59*$B$5/12,2),0)</f>
+        <f>IF(B59&gt;0.005,ROUND(B59*$B$5/12,2),0)</f>
         <v>34.02</v>
       </c>
       <c r="D59" s="2">
-        <f>IF(B59&gt;0,MIN($B$6+$B$7,B59+C59),0)</f>
+        <f>IF(B59&gt;0.005,MIN($B$6+$B$7,B59+C59),0)</f>
         <v>150.0</v>
       </c>
       <c r="E59" s="2">
@@ -1377,11 +1377,11 @@
         <v>1517.6</v>
       </c>
       <c r="C60" s="2">
-        <f>IF(B60&gt;0,ROUND(B60*$B$5/12,2),0)</f>
+        <f>IF(B60&gt;0.005,ROUND(B60*$B$5/12,2),0)</f>
         <v>31.6</v>
       </c>
       <c r="D60" s="2">
-        <f>IF(B60&gt;0,MIN($B$6+$B$7,B60+C60),0)</f>
+        <f>IF(B60&gt;0.005,MIN($B$6+$B$7,B60+C60),0)</f>
         <v>150.0</v>
       </c>
       <c r="E60" s="2">
@@ -1402,11 +1402,11 @@
         <v>1399.2</v>
       </c>
       <c r="C61" s="2">
-        <f>IF(B61&gt;0,ROUND(B61*$B$5/12,2),0)</f>
+        <f>IF(B61&gt;0.005,ROUND(B61*$B$5/12,2),0)</f>
         <v>29.14</v>
       </c>
       <c r="D61" s="2">
-        <f>IF(B61&gt;0,MIN($B$6+$B$7,B61+C61),0)</f>
+        <f>IF(B61&gt;0.005,MIN($B$6+$B$7,B61+C61),0)</f>
         <v>150.0</v>
       </c>
       <c r="E61" s="2">
@@ -1427,11 +1427,11 @@
         <v>1278.34</v>
       </c>
       <c r="C62" s="2">
-        <f>IF(B62&gt;0,ROUND(B62*$B$5/12,2),0)</f>
+        <f>IF(B62&gt;0.005,ROUND(B62*$B$5/12,2),0)</f>
         <v>26.62</v>
       </c>
       <c r="D62" s="2">
-        <f>IF(B62&gt;0,MIN($B$6+$B$7,B62+C62),0)</f>
+        <f>IF(B62&gt;0.005,MIN($B$6+$B$7,B62+C62),0)</f>
         <v>150.0</v>
       </c>
       <c r="E62" s="2">
@@ -1452,11 +1452,11 @@
         <v>1154.96</v>
       </c>
       <c r="C63" s="2">
-        <f>IF(B63&gt;0,ROUND(B63*$B$5/12,2),0)</f>
+        <f>IF(B63&gt;0.005,ROUND(B63*$B$5/12,2),0)</f>
         <v>24.05</v>
       </c>
       <c r="D63" s="2">
-        <f>IF(B63&gt;0,MIN($B$6+$B$7,B63+C63),0)</f>
+        <f>IF(B63&gt;0.005,MIN($B$6+$B$7,B63+C63),0)</f>
         <v>150.0</v>
       </c>
       <c r="E63" s="2">
@@ -1477,11 +1477,11 @@
         <v>1029.01</v>
       </c>
       <c r="C64" s="2">
-        <f>IF(B64&gt;0,ROUND(B64*$B$5/12,2),0)</f>
+        <f>IF(B64&gt;0.005,ROUND(B64*$B$5/12,2),0)</f>
         <v>21.43</v>
       </c>
       <c r="D64" s="2">
-        <f>IF(B64&gt;0,MIN($B$6+$B$7,B64+C64),0)</f>
+        <f>IF(B64&gt;0.005,MIN($B$6+$B$7,B64+C64),0)</f>
         <v>150.0</v>
       </c>
       <c r="E64" s="2">
@@ -1502,11 +1502,11 @@
         <v>900.44</v>
       </c>
       <c r="C65" s="2">
-        <f>IF(B65&gt;0,ROUND(B65*$B$5/12,2),0)</f>
+        <f>IF(B65&gt;0.005,ROUND(B65*$B$5/12,2),0)</f>
         <v>18.75</v>
       </c>
       <c r="D65" s="2">
-        <f>IF(B65&gt;0,MIN($B$6+$B$7,B65+C65),0)</f>
+        <f>IF(B65&gt;0.005,MIN($B$6+$B$7,B65+C65),0)</f>
         <v>150.0</v>
       </c>
       <c r="E65" s="2">
@@ -1527,11 +1527,11 @@
         <v>769.19</v>
       </c>
       <c r="C66" s="2">
-        <f>IF(B66&gt;0,ROUND(B66*$B$5/12,2),0)</f>
+        <f>IF(B66&gt;0.005,ROUND(B66*$B$5/12,2),0)</f>
         <v>16.02</v>
       </c>
       <c r="D66" s="2">
-        <f>IF(B66&gt;0,MIN($B$6+$B$7,B66+C66),0)</f>
+        <f>IF(B66&gt;0.005,MIN($B$6+$B$7,B66+C66),0)</f>
         <v>150.0</v>
       </c>
       <c r="E66" s="2">
@@ -1552,11 +1552,11 @@
         <v>635.21</v>
       </c>
       <c r="C67" s="2">
-        <f>IF(B67&gt;0,ROUND(B67*$B$5/12,2),0)</f>
+        <f>IF(B67&gt;0.005,ROUND(B67*$B$5/12,2),0)</f>
         <v>13.23</v>
       </c>
       <c r="D67" s="2">
-        <f>IF(B67&gt;0,MIN($B$6+$B$7,B67+C67),0)</f>
+        <f>IF(B67&gt;0.005,MIN($B$6+$B$7,B67+C67),0)</f>
         <v>150.0</v>
       </c>
       <c r="E67" s="2">
@@ -1577,11 +1577,11 @@
         <v>498.44</v>
       </c>
       <c r="C68" s="2">
-        <f>IF(B68&gt;0,ROUND(B68*$B$5/12,2),0)</f>
+        <f>IF(B68&gt;0.005,ROUND(B68*$B$5/12,2),0)</f>
         <v>10.38</v>
       </c>
       <c r="D68" s="2">
-        <f>IF(B68&gt;0,MIN($B$6+$B$7,B68+C68),0)</f>
+        <f>IF(B68&gt;0.005,MIN($B$6+$B$7,B68+C68),0)</f>
         <v>150.0</v>
       </c>
       <c r="E68" s="2">
@@ -1602,11 +1602,11 @@
         <v>358.82</v>
       </c>
       <c r="C69" s="2">
-        <f>IF(B69&gt;0,ROUND(B69*$B$5/12,2),0)</f>
+        <f>IF(B69&gt;0.005,ROUND(B69*$B$5/12,2),0)</f>
         <v>7.47</v>
       </c>
       <c r="D69" s="2">
-        <f>IF(B69&gt;0,MIN($B$6+$B$7,B69+C69),0)</f>
+        <f>IF(B69&gt;0.005,MIN($B$6+$B$7,B69+C69),0)</f>
         <v>150.0</v>
       </c>
       <c r="E69" s="2">
@@ -1627,11 +1627,11 @@
         <v>216.29</v>
       </c>
       <c r="C70" s="2">
-        <f>IF(B70&gt;0,ROUND(B70*$B$5/12,2),0)</f>
+        <f>IF(B70&gt;0.005,ROUND(B70*$B$5/12,2),0)</f>
         <v>4.5</v>
       </c>
       <c r="D70" s="2">
-        <f>IF(B70&gt;0,MIN($B$6+$B$7,B70+C70),0)</f>
+        <f>IF(B70&gt;0.005,MIN($B$6+$B$7,B70+C70),0)</f>
         <v>150.0</v>
       </c>
       <c r="E70" s="2">
@@ -1652,11 +1652,11 @@
         <v>70.79</v>
       </c>
       <c r="C71" s="2">
-        <f>IF(B71&gt;0,ROUND(B71*$B$5/12,2),0)</f>
+        <f>IF(B71&gt;0.005,ROUND(B71*$B$5/12,2),0)</f>
         <v>1.47</v>
       </c>
       <c r="D71" s="2">
-        <f>IF(B71&gt;0,MIN($B$6+$B$7,B71+C71),0)</f>
+        <f>IF(B71&gt;0.005,MIN($B$6+$B$7,B71+C71),0)</f>
         <v>72.26</v>
       </c>
       <c r="E71" s="2">
@@ -1677,11 +1677,11 @@
         <v>0.0</v>
       </c>
       <c r="C72" s="2">
-        <f>IF(B72&gt;0,ROUND(B72*$B$5/12,2),0)</f>
+        <f>IF(B72&gt;0.005,ROUND(B72*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D72" s="2">
-        <f>IF(B72&gt;0,MIN($B$6+$B$7,B72+C72),0)</f>
+        <f>IF(B72&gt;0.005,MIN($B$6+$B$7,B72+C72),0)</f>
         <v>0</v>
       </c>
       <c r="E72" s="2">
@@ -1702,11 +1702,11 @@
         <v>0.0</v>
       </c>
       <c r="C73" s="2">
-        <f>IF(B73&gt;0,ROUND(B73*$B$5/12,2),0)</f>
+        <f>IF(B73&gt;0.005,ROUND(B73*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D73" s="2">
-        <f>IF(B73&gt;0,MIN($B$6+$B$7,B73+C73),0)</f>
+        <f>IF(B73&gt;0.005,MIN($B$6+$B$7,B73+C73),0)</f>
         <v>0</v>
       </c>
       <c r="E73" s="2">
@@ -1727,11 +1727,11 @@
         <v>0.0</v>
       </c>
       <c r="C74" s="2">
-        <f>IF(B74&gt;0,ROUND(B74*$B$5/12,2),0)</f>
+        <f>IF(B74&gt;0.005,ROUND(B74*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D74" s="2">
-        <f>IF(B74&gt;0,MIN($B$6+$B$7,B74+C74),0)</f>
+        <f>IF(B74&gt;0.005,MIN($B$6+$B$7,B74+C74),0)</f>
         <v>0</v>
       </c>
       <c r="E74" s="2">
@@ -1752,11 +1752,11 @@
         <v>0.0</v>
       </c>
       <c r="C75" s="2">
-        <f>IF(B75&gt;0,ROUND(B75*$B$5/12,2),0)</f>
+        <f>IF(B75&gt;0.005,ROUND(B75*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D75" s="2">
-        <f>IF(B75&gt;0,MIN($B$6+$B$7,B75+C75),0)</f>
+        <f>IF(B75&gt;0.005,MIN($B$6+$B$7,B75+C75),0)</f>
         <v>0</v>
       </c>
       <c r="E75" s="2">
@@ -1777,11 +1777,11 @@
         <v>0.0</v>
       </c>
       <c r="C76" s="2">
-        <f>IF(B76&gt;0,ROUND(B76*$B$5/12,2),0)</f>
+        <f>IF(B76&gt;0.005,ROUND(B76*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D76" s="2">
-        <f>IF(B76&gt;0,MIN($B$6+$B$7,B76+C76),0)</f>
+        <f>IF(B76&gt;0.005,MIN($B$6+$B$7,B76+C76),0)</f>
         <v>0</v>
       </c>
       <c r="E76" s="2">
@@ -1802,11 +1802,11 @@
         <v>0.0</v>
       </c>
       <c r="C77" s="2">
-        <f>IF(B77&gt;0,ROUND(B77*$B$5/12,2),0)</f>
+        <f>IF(B77&gt;0.005,ROUND(B77*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D77" s="2">
-        <f>IF(B77&gt;0,MIN($B$6+$B$7,B77+C77),0)</f>
+        <f>IF(B77&gt;0.005,MIN($B$6+$B$7,B77+C77),0)</f>
         <v>0</v>
       </c>
       <c r="E77" s="2">
@@ -1827,11 +1827,11 @@
         <v>0.0</v>
       </c>
       <c r="C78" s="2">
-        <f>IF(B78&gt;0,ROUND(B78*$B$5/12,2),0)</f>
+        <f>IF(B78&gt;0.005,ROUND(B78*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D78" s="2">
-        <f>IF(B78&gt;0,MIN($B$6+$B$7,B78+C78),0)</f>
+        <f>IF(B78&gt;0.005,MIN($B$6+$B$7,B78+C78),0)</f>
         <v>0</v>
       </c>
       <c r="E78" s="2">
@@ -1852,11 +1852,11 @@
         <v>0.0</v>
       </c>
       <c r="C79" s="2">
-        <f>IF(B79&gt;0,ROUND(B79*$B$5/12,2),0)</f>
+        <f>IF(B79&gt;0.005,ROUND(B79*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D79" s="2">
-        <f>IF(B79&gt;0,MIN($B$6+$B$7,B79+C79),0)</f>
+        <f>IF(B79&gt;0.005,MIN($B$6+$B$7,B79+C79),0)</f>
         <v>0</v>
       </c>
       <c r="E79" s="2">
@@ -1877,11 +1877,11 @@
         <v>0.0</v>
       </c>
       <c r="C80" s="2">
-        <f>IF(B80&gt;0,ROUND(B80*$B$5/12,2),0)</f>
+        <f>IF(B80&gt;0.005,ROUND(B80*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D80" s="2">
-        <f>IF(B80&gt;0,MIN($B$6+$B$7,B80+C80),0)</f>
+        <f>IF(B80&gt;0.005,MIN($B$6+$B$7,B80+C80),0)</f>
         <v>0</v>
       </c>
       <c r="E80" s="2">
@@ -1902,11 +1902,11 @@
         <v>0.0</v>
       </c>
       <c r="C81" s="2">
-        <f>IF(B81&gt;0,ROUND(B81*$B$5/12,2),0)</f>
+        <f>IF(B81&gt;0.005,ROUND(B81*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D81" s="2">
-        <f>IF(B81&gt;0,MIN($B$6+$B$7,B81+C81),0)</f>
+        <f>IF(B81&gt;0.005,MIN($B$6+$B$7,B81+C81),0)</f>
         <v>0</v>
       </c>
       <c r="E81" s="2">
@@ -1927,11 +1927,11 @@
         <v>0.0</v>
       </c>
       <c r="C82" s="2">
-        <f>IF(B82&gt;0,ROUND(B82*$B$5/12,2),0)</f>
+        <f>IF(B82&gt;0.005,ROUND(B82*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D82" s="2">
-        <f>IF(B82&gt;0,MIN($B$6+$B$7,B82+C82),0)</f>
+        <f>IF(B82&gt;0.005,MIN($B$6+$B$7,B82+C82),0)</f>
         <v>0</v>
       </c>
       <c r="E82" s="2">
@@ -1952,11 +1952,11 @@
         <v>0.0</v>
       </c>
       <c r="C83" s="2">
-        <f>IF(B83&gt;0,ROUND(B83*$B$5/12,2),0)</f>
+        <f>IF(B83&gt;0.005,ROUND(B83*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D83" s="2">
-        <f>IF(B83&gt;0,MIN($B$6+$B$7,B83+C83),0)</f>
+        <f>IF(B83&gt;0.005,MIN($B$6+$B$7,B83+C83),0)</f>
         <v>0</v>
       </c>
       <c r="E83" s="2">
@@ -1977,11 +1977,11 @@
         <v>0.0</v>
       </c>
       <c r="C84" s="2">
-        <f>IF(B84&gt;0,ROUND(B84*$B$5/12,2),0)</f>
+        <f>IF(B84&gt;0.005,ROUND(B84*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D84" s="2">
-        <f>IF(B84&gt;0,MIN($B$6+$B$7,B84+C84),0)</f>
+        <f>IF(B84&gt;0.005,MIN($B$6+$B$7,B84+C84),0)</f>
         <v>0</v>
       </c>
       <c r="E84" s="2">
@@ -2002,11 +2002,11 @@
         <v>0.0</v>
       </c>
       <c r="C85" s="2">
-        <f>IF(B85&gt;0,ROUND(B85*$B$5/12,2),0)</f>
+        <f>IF(B85&gt;0.005,ROUND(B85*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D85" s="2">
-        <f>IF(B85&gt;0,MIN($B$6+$B$7,B85+C85),0)</f>
+        <f>IF(B85&gt;0.005,MIN($B$6+$B$7,B85+C85),0)</f>
         <v>0</v>
       </c>
       <c r="E85" s="2">
@@ -2027,11 +2027,11 @@
         <v>0.0</v>
       </c>
       <c r="C86" s="2">
-        <f>IF(B86&gt;0,ROUND(B86*$B$5/12,2),0)</f>
+        <f>IF(B86&gt;0.005,ROUND(B86*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D86" s="2">
-        <f>IF(B86&gt;0,MIN($B$6+$B$7,B86+C86),0)</f>
+        <f>IF(B86&gt;0.005,MIN($B$6+$B$7,B86+C86),0)</f>
         <v>0</v>
       </c>
       <c r="E86" s="2">
@@ -2052,11 +2052,11 @@
         <v>0.0</v>
       </c>
       <c r="C87" s="2">
-        <f>IF(B87&gt;0,ROUND(B87*$B$5/12,2),0)</f>
+        <f>IF(B87&gt;0.005,ROUND(B87*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D87" s="2">
-        <f>IF(B87&gt;0,MIN($B$6+$B$7,B87+C87),0)</f>
+        <f>IF(B87&gt;0.005,MIN($B$6+$B$7,B87+C87),0)</f>
         <v>0</v>
       </c>
       <c r="E87" s="2">
@@ -2077,11 +2077,11 @@
         <v>0.0</v>
       </c>
       <c r="C88" s="2">
-        <f>IF(B88&gt;0,ROUND(B88*$B$5/12,2),0)</f>
+        <f>IF(B88&gt;0.005,ROUND(B88*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D88" s="2">
-        <f>IF(B88&gt;0,MIN($B$6+$B$7,B88+C88),0)</f>
+        <f>IF(B88&gt;0.005,MIN($B$6+$B$7,B88+C88),0)</f>
         <v>0</v>
       </c>
       <c r="E88" s="2">
@@ -2102,11 +2102,11 @@
         <v>0.0</v>
       </c>
       <c r="C89" s="2">
-        <f>IF(B89&gt;0,ROUND(B89*$B$5/12,2),0)</f>
+        <f>IF(B89&gt;0.005,ROUND(B89*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D89" s="2">
-        <f>IF(B89&gt;0,MIN($B$6+$B$7,B89+C89),0)</f>
+        <f>IF(B89&gt;0.005,MIN($B$6+$B$7,B89+C89),0)</f>
         <v>0</v>
       </c>
       <c r="E89" s="2">
@@ -2127,11 +2127,11 @@
         <v>0.0</v>
       </c>
       <c r="C90" s="2">
-        <f>IF(B90&gt;0,ROUND(B90*$B$5/12,2),0)</f>
+        <f>IF(B90&gt;0.005,ROUND(B90*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D90" s="2">
-        <f>IF(B90&gt;0,MIN($B$6+$B$7,B90+C90),0)</f>
+        <f>IF(B90&gt;0.005,MIN($B$6+$B$7,B90+C90),0)</f>
         <v>0</v>
       </c>
       <c r="E90" s="2">
@@ -2152,11 +2152,11 @@
         <v>0.0</v>
       </c>
       <c r="C91" s="2">
-        <f>IF(B91&gt;0,ROUND(B91*$B$5/12,2),0)</f>
+        <f>IF(B91&gt;0.005,ROUND(B91*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D91" s="2">
-        <f>IF(B91&gt;0,MIN($B$6+$B$7,B91+C91),0)</f>
+        <f>IF(B91&gt;0.005,MIN($B$6+$B$7,B91+C91),0)</f>
         <v>0</v>
       </c>
       <c r="E91" s="2">
@@ -2177,11 +2177,11 @@
         <v>0.0</v>
       </c>
       <c r="C92" s="2">
-        <f>IF(B92&gt;0,ROUND(B92*$B$5/12,2),0)</f>
+        <f>IF(B92&gt;0.005,ROUND(B92*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D92" s="2">
-        <f>IF(B92&gt;0,MIN($B$6+$B$7,B92+C92),0)</f>
+        <f>IF(B92&gt;0.005,MIN($B$6+$B$7,B92+C92),0)</f>
         <v>0</v>
       </c>
       <c r="E92" s="2">
@@ -2202,11 +2202,11 @@
         <v>0.0</v>
       </c>
       <c r="C93" s="2">
-        <f>IF(B93&gt;0,ROUND(B93*$B$5/12,2),0)</f>
+        <f>IF(B93&gt;0.005,ROUND(B93*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D93" s="2">
-        <f>IF(B93&gt;0,MIN($B$6+$B$7,B93+C93),0)</f>
+        <f>IF(B93&gt;0.005,MIN($B$6+$B$7,B93+C93),0)</f>
         <v>0</v>
       </c>
       <c r="E93" s="2">
@@ -2227,11 +2227,11 @@
         <v>0.0</v>
       </c>
       <c r="C94" s="2">
-        <f>IF(B94&gt;0,ROUND(B94*$B$5/12,2),0)</f>
+        <f>IF(B94&gt;0.005,ROUND(B94*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D94" s="2">
-        <f>IF(B94&gt;0,MIN($B$6+$B$7,B94+C94),0)</f>
+        <f>IF(B94&gt;0.005,MIN($B$6+$B$7,B94+C94),0)</f>
         <v>0</v>
       </c>
       <c r="E94" s="2">
@@ -2252,11 +2252,11 @@
         <v>0.0</v>
       </c>
       <c r="C95" s="2">
-        <f>IF(B95&gt;0,ROUND(B95*$B$5/12,2),0)</f>
+        <f>IF(B95&gt;0.005,ROUND(B95*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D95" s="2">
-        <f>IF(B95&gt;0,MIN($B$6+$B$7,B95+C95),0)</f>
+        <f>IF(B95&gt;0.005,MIN($B$6+$B$7,B95+C95),0)</f>
         <v>0</v>
       </c>
       <c r="E95" s="2">
@@ -2277,11 +2277,11 @@
         <v>0.0</v>
       </c>
       <c r="C96" s="2">
-        <f>IF(B96&gt;0,ROUND(B96*$B$5/12,2),0)</f>
+        <f>IF(B96&gt;0.005,ROUND(B96*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D96" s="2">
-        <f>IF(B96&gt;0,MIN($B$6+$B$7,B96+C96),0)</f>
+        <f>IF(B96&gt;0.005,MIN($B$6+$B$7,B96+C96),0)</f>
         <v>0</v>
       </c>
       <c r="E96" s="2">
@@ -2302,11 +2302,11 @@
         <v>0.0</v>
       </c>
       <c r="C97" s="2">
-        <f>IF(B97&gt;0,ROUND(B97*$B$5/12,2),0)</f>
+        <f>IF(B97&gt;0.005,ROUND(B97*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D97" s="2">
-        <f>IF(B97&gt;0,MIN($B$6+$B$7,B97+C97),0)</f>
+        <f>IF(B97&gt;0.005,MIN($B$6+$B$7,B97+C97),0)</f>
         <v>0</v>
       </c>
       <c r="E97" s="2">
@@ -2327,11 +2327,11 @@
         <v>0.0</v>
       </c>
       <c r="C98" s="2">
-        <f>IF(B98&gt;0,ROUND(B98*$B$5/12,2),0)</f>
+        <f>IF(B98&gt;0.005,ROUND(B98*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D98" s="2">
-        <f>IF(B98&gt;0,MIN($B$6+$B$7,B98+C98),0)</f>
+        <f>IF(B98&gt;0.005,MIN($B$6+$B$7,B98+C98),0)</f>
         <v>0</v>
       </c>
       <c r="E98" s="2">
@@ -2352,11 +2352,11 @@
         <v>0.0</v>
       </c>
       <c r="C99" s="2">
-        <f>IF(B99&gt;0,ROUND(B99*$B$5/12,2),0)</f>
+        <f>IF(B99&gt;0.005,ROUND(B99*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D99" s="2">
-        <f>IF(B99&gt;0,MIN($B$6+$B$7,B99+C99),0)</f>
+        <f>IF(B99&gt;0.005,MIN($B$6+$B$7,B99+C99),0)</f>
         <v>0</v>
       </c>
       <c r="E99" s="2">
@@ -2377,11 +2377,11 @@
         <v>0.0</v>
       </c>
       <c r="C100" s="2">
-        <f>IF(B100&gt;0,ROUND(B100*$B$5/12,2),0)</f>
+        <f>IF(B100&gt;0.005,ROUND(B100*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D100" s="2">
-        <f>IF(B100&gt;0,MIN($B$6+$B$7,B100+C100),0)</f>
+        <f>IF(B100&gt;0.005,MIN($B$6+$B$7,B100+C100),0)</f>
         <v>0</v>
       </c>
       <c r="E100" s="2">
@@ -2402,11 +2402,11 @@
         <v>0.0</v>
       </c>
       <c r="C101" s="2">
-        <f>IF(B101&gt;0,ROUND(B101*$B$5/12,2),0)</f>
+        <f>IF(B101&gt;0.005,ROUND(B101*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D101" s="2">
-        <f>IF(B101&gt;0,MIN($B$6+$B$7,B101+C101),0)</f>
+        <f>IF(B101&gt;0.005,MIN($B$6+$B$7,B101+C101),0)</f>
         <v>0</v>
       </c>
       <c r="E101" s="2">
@@ -2427,11 +2427,11 @@
         <v>0.0</v>
       </c>
       <c r="C102" s="2">
-        <f>IF(B102&gt;0,ROUND(B102*$B$5/12,2),0)</f>
+        <f>IF(B102&gt;0.005,ROUND(B102*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D102" s="2">
-        <f>IF(B102&gt;0,MIN($B$6+$B$7,B102+C102),0)</f>
+        <f>IF(B102&gt;0.005,MIN($B$6+$B$7,B102+C102),0)</f>
         <v>0</v>
       </c>
       <c r="E102" s="2">
@@ -2452,11 +2452,11 @@
         <v>0.0</v>
       </c>
       <c r="C103" s="2">
-        <f>IF(B103&gt;0,ROUND(B103*$B$5/12,2),0)</f>
+        <f>IF(B103&gt;0.005,ROUND(B103*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D103" s="2">
-        <f>IF(B103&gt;0,MIN($B$6+$B$7,B103+C103),0)</f>
+        <f>IF(B103&gt;0.005,MIN($B$6+$B$7,B103+C103),0)</f>
         <v>0</v>
       </c>
       <c r="E103" s="2">
@@ -2477,11 +2477,11 @@
         <v>0.0</v>
       </c>
       <c r="C104" s="2">
-        <f>IF(B104&gt;0,ROUND(B104*$B$5/12,2),0)</f>
+        <f>IF(B104&gt;0.005,ROUND(B104*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D104" s="2">
-        <f>IF(B104&gt;0,MIN($B$6+$B$7,B104+C104),0)</f>
+        <f>IF(B104&gt;0.005,MIN($B$6+$B$7,B104+C104),0)</f>
         <v>0</v>
       </c>
       <c r="E104" s="2">
@@ -2502,11 +2502,11 @@
         <v>0.0</v>
       </c>
       <c r="C105" s="2">
-        <f>IF(B105&gt;0,ROUND(B105*$B$5/12,2),0)</f>
+        <f>IF(B105&gt;0.005,ROUND(B105*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D105" s="2">
-        <f>IF(B105&gt;0,MIN($B$6+$B$7,B105+C105),0)</f>
+        <f>IF(B105&gt;0.005,MIN($B$6+$B$7,B105+C105),0)</f>
         <v>0</v>
       </c>
       <c r="E105" s="2">
@@ -2527,11 +2527,11 @@
         <v>0.0</v>
       </c>
       <c r="C106" s="2">
-        <f>IF(B106&gt;0,ROUND(B106*$B$5/12,2),0)</f>
+        <f>IF(B106&gt;0.005,ROUND(B106*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D106" s="2">
-        <f>IF(B106&gt;0,MIN($B$6+$B$7,B106+C106),0)</f>
+        <f>IF(B106&gt;0.005,MIN($B$6+$B$7,B106+C106),0)</f>
         <v>0</v>
       </c>
       <c r="E106" s="2">
@@ -2552,11 +2552,11 @@
         <v>0.0</v>
       </c>
       <c r="C107" s="2">
-        <f>IF(B107&gt;0,ROUND(B107*$B$5/12,2),0)</f>
+        <f>IF(B107&gt;0.005,ROUND(B107*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D107" s="2">
-        <f>IF(B107&gt;0,MIN($B$6+$B$7,B107+C107),0)</f>
+        <f>IF(B107&gt;0.005,MIN($B$6+$B$7,B107+C107),0)</f>
         <v>0</v>
       </c>
       <c r="E107" s="2">
@@ -2577,11 +2577,11 @@
         <v>0.0</v>
       </c>
       <c r="C108" s="2">
-        <f>IF(B108&gt;0,ROUND(B108*$B$5/12,2),0)</f>
+        <f>IF(B108&gt;0.005,ROUND(B108*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D108" s="2">
-        <f>IF(B108&gt;0,MIN($B$6+$B$7,B108+C108),0)</f>
+        <f>IF(B108&gt;0.005,MIN($B$6+$B$7,B108+C108),0)</f>
         <v>0</v>
       </c>
       <c r="E108" s="2">
@@ -2602,11 +2602,11 @@
         <v>0.0</v>
       </c>
       <c r="C109" s="2">
-        <f>IF(B109&gt;0,ROUND(B109*$B$5/12,2),0)</f>
+        <f>IF(B109&gt;0.005,ROUND(B109*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D109" s="2">
-        <f>IF(B109&gt;0,MIN($B$6+$B$7,B109+C109),0)</f>
+        <f>IF(B109&gt;0.005,MIN($B$6+$B$7,B109+C109),0)</f>
         <v>0</v>
       </c>
       <c r="E109" s="2">
@@ -2627,11 +2627,11 @@
         <v>0.0</v>
       </c>
       <c r="C110" s="2">
-        <f>IF(B110&gt;0,ROUND(B110*$B$5/12,2),0)</f>
+        <f>IF(B110&gt;0.005,ROUND(B110*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D110" s="2">
-        <f>IF(B110&gt;0,MIN($B$6+$B$7,B110+C110),0)</f>
+        <f>IF(B110&gt;0.005,MIN($B$6+$B$7,B110+C110),0)</f>
         <v>0</v>
       </c>
       <c r="E110" s="2">
@@ -2652,11 +2652,11 @@
         <v>0.0</v>
       </c>
       <c r="C111" s="2">
-        <f>IF(B111&gt;0,ROUND(B111*$B$5/12,2),0)</f>
+        <f>IF(B111&gt;0.005,ROUND(B111*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D111" s="2">
-        <f>IF(B111&gt;0,MIN($B$6+$B$7,B111+C111),0)</f>
+        <f>IF(B111&gt;0.005,MIN($B$6+$B$7,B111+C111),0)</f>
         <v>0</v>
       </c>
       <c r="E111" s="2">
@@ -2677,11 +2677,11 @@
         <v>0.0</v>
       </c>
       <c r="C112" s="2">
-        <f>IF(B112&gt;0,ROUND(B112*$B$5/12,2),0)</f>
+        <f>IF(B112&gt;0.005,ROUND(B112*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D112" s="2">
-        <f>IF(B112&gt;0,MIN($B$6+$B$7,B112+C112),0)</f>
+        <f>IF(B112&gt;0.005,MIN($B$6+$B$7,B112+C112),0)</f>
         <v>0</v>
       </c>
       <c r="E112" s="2">
@@ -2702,11 +2702,11 @@
         <v>0.0</v>
       </c>
       <c r="C113" s="2">
-        <f>IF(B113&gt;0,ROUND(B113*$B$5/12,2),0)</f>
+        <f>IF(B113&gt;0.005,ROUND(B113*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D113" s="2">
-        <f>IF(B113&gt;0,MIN($B$6+$B$7,B113+C113),0)</f>
+        <f>IF(B113&gt;0.005,MIN($B$6+$B$7,B113+C113),0)</f>
         <v>0</v>
       </c>
       <c r="E113" s="2">
@@ -2727,11 +2727,11 @@
         <v>0.0</v>
       </c>
       <c r="C114" s="2">
-        <f>IF(B114&gt;0,ROUND(B114*$B$5/12,2),0)</f>
+        <f>IF(B114&gt;0.005,ROUND(B114*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D114" s="2">
-        <f>IF(B114&gt;0,MIN($B$6+$B$7,B114+C114),0)</f>
+        <f>IF(B114&gt;0.005,MIN($B$6+$B$7,B114+C114),0)</f>
         <v>0</v>
       </c>
       <c r="E114" s="2">
@@ -2752,11 +2752,11 @@
         <v>0.0</v>
       </c>
       <c r="C115" s="2">
-        <f>IF(B115&gt;0,ROUND(B115*$B$5/12,2),0)</f>
+        <f>IF(B115&gt;0.005,ROUND(B115*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D115" s="2">
-        <f>IF(B115&gt;0,MIN($B$6+$B$7,B115+C115),0)</f>
+        <f>IF(B115&gt;0.005,MIN($B$6+$B$7,B115+C115),0)</f>
         <v>0</v>
       </c>
       <c r="E115" s="2">
@@ -2777,11 +2777,11 @@
         <v>0.0</v>
       </c>
       <c r="C116" s="2">
-        <f>IF(B116&gt;0,ROUND(B116*$B$5/12,2),0)</f>
+        <f>IF(B116&gt;0.005,ROUND(B116*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D116" s="2">
-        <f>IF(B116&gt;0,MIN($B$6+$B$7,B116+C116),0)</f>
+        <f>IF(B116&gt;0.005,MIN($B$6+$B$7,B116+C116),0)</f>
         <v>0</v>
       </c>
       <c r="E116" s="2">
@@ -2802,11 +2802,11 @@
         <v>0.0</v>
       </c>
       <c r="C117" s="2">
-        <f>IF(B117&gt;0,ROUND(B117*$B$5/12,2),0)</f>
+        <f>IF(B117&gt;0.005,ROUND(B117*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D117" s="2">
-        <f>IF(B117&gt;0,MIN($B$6+$B$7,B117+C117),0)</f>
+        <f>IF(B117&gt;0.005,MIN($B$6+$B$7,B117+C117),0)</f>
         <v>0</v>
       </c>
       <c r="E117" s="2">
@@ -2827,11 +2827,11 @@
         <v>0.0</v>
       </c>
       <c r="C118" s="2">
-        <f>IF(B118&gt;0,ROUND(B118*$B$5/12,2),0)</f>
+        <f>IF(B118&gt;0.005,ROUND(B118*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D118" s="2">
-        <f>IF(B118&gt;0,MIN($B$6+$B$7,B118+C118),0)</f>
+        <f>IF(B118&gt;0.005,MIN($B$6+$B$7,B118+C118),0)</f>
         <v>0</v>
       </c>
       <c r="E118" s="2">
@@ -2852,11 +2852,11 @@
         <v>0.0</v>
       </c>
       <c r="C119" s="2">
-        <f>IF(B119&gt;0,ROUND(B119*$B$5/12,2),0)</f>
+        <f>IF(B119&gt;0.005,ROUND(B119*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D119" s="2">
-        <f>IF(B119&gt;0,MIN($B$6+$B$7,B119+C119),0)</f>
+        <f>IF(B119&gt;0.005,MIN($B$6+$B$7,B119+C119),0)</f>
         <v>0</v>
       </c>
       <c r="E119" s="2">
@@ -2877,11 +2877,11 @@
         <v>0.0</v>
       </c>
       <c r="C120" s="2">
-        <f>IF(B120&gt;0,ROUND(B120*$B$5/12,2),0)</f>
+        <f>IF(B120&gt;0.005,ROUND(B120*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D120" s="2">
-        <f>IF(B120&gt;0,MIN($B$6+$B$7,B120+C120),0)</f>
+        <f>IF(B120&gt;0.005,MIN($B$6+$B$7,B120+C120),0)</f>
         <v>0</v>
       </c>
       <c r="E120" s="2">
@@ -2902,11 +2902,11 @@
         <v>0.0</v>
       </c>
       <c r="C121" s="2">
-        <f>IF(B121&gt;0,ROUND(B121*$B$5/12,2),0)</f>
+        <f>IF(B121&gt;0.005,ROUND(B121*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D121" s="2">
-        <f>IF(B121&gt;0,MIN($B$6+$B$7,B121+C121),0)</f>
+        <f>IF(B121&gt;0.005,MIN($B$6+$B$7,B121+C121),0)</f>
         <v>0</v>
       </c>
       <c r="E121" s="2">
@@ -2927,11 +2927,11 @@
         <v>0.0</v>
       </c>
       <c r="C122" s="2">
-        <f>IF(B122&gt;0,ROUND(B122*$B$5/12,2),0)</f>
+        <f>IF(B122&gt;0.005,ROUND(B122*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D122" s="2">
-        <f>IF(B122&gt;0,MIN($B$6+$B$7,B122+C122),0)</f>
+        <f>IF(B122&gt;0.005,MIN($B$6+$B$7,B122+C122),0)</f>
         <v>0</v>
       </c>
       <c r="E122" s="2">
@@ -2952,11 +2952,11 @@
         <v>0.0</v>
       </c>
       <c r="C123" s="2">
-        <f>IF(B123&gt;0,ROUND(B123*$B$5/12,2),0)</f>
+        <f>IF(B123&gt;0.005,ROUND(B123*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D123" s="2">
-        <f>IF(B123&gt;0,MIN($B$6+$B$7,B123+C123),0)</f>
+        <f>IF(B123&gt;0.005,MIN($B$6+$B$7,B123+C123),0)</f>
         <v>0</v>
       </c>
       <c r="E123" s="2">
@@ -2977,11 +2977,11 @@
         <v>0.0</v>
       </c>
       <c r="C124" s="2">
-        <f>IF(B124&gt;0,ROUND(B124*$B$5/12,2),0)</f>
+        <f>IF(B124&gt;0.005,ROUND(B124*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D124" s="2">
-        <f>IF(B124&gt;0,MIN($B$6+$B$7,B124+C124),0)</f>
+        <f>IF(B124&gt;0.005,MIN($B$6+$B$7,B124+C124),0)</f>
         <v>0</v>
       </c>
       <c r="E124" s="2">
@@ -3002,11 +3002,11 @@
         <v>0.0</v>
       </c>
       <c r="C125" s="2">
-        <f>IF(B125&gt;0,ROUND(B125*$B$5/12,2),0)</f>
+        <f>IF(B125&gt;0.005,ROUND(B125*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D125" s="2">
-        <f>IF(B125&gt;0,MIN($B$6+$B$7,B125+C125),0)</f>
+        <f>IF(B125&gt;0.005,MIN($B$6+$B$7,B125+C125),0)</f>
         <v>0</v>
       </c>
       <c r="E125" s="2">
@@ -3027,11 +3027,11 @@
         <v>0.0</v>
       </c>
       <c r="C126" s="2">
-        <f>IF(B126&gt;0,ROUND(B126*$B$5/12,2),0)</f>
+        <f>IF(B126&gt;0.005,ROUND(B126*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D126" s="2">
-        <f>IF(B126&gt;0,MIN($B$6+$B$7,B126+C126),0)</f>
+        <f>IF(B126&gt;0.005,MIN($B$6+$B$7,B126+C126),0)</f>
         <v>0</v>
       </c>
       <c r="E126" s="2">
@@ -3052,11 +3052,11 @@
         <v>0.0</v>
       </c>
       <c r="C127" s="2">
-        <f>IF(B127&gt;0,ROUND(B127*$B$5/12,2),0)</f>
+        <f>IF(B127&gt;0.005,ROUND(B127*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D127" s="2">
-        <f>IF(B127&gt;0,MIN($B$6+$B$7,B127+C127),0)</f>
+        <f>IF(B127&gt;0.005,MIN($B$6+$B$7,B127+C127),0)</f>
         <v>0</v>
       </c>
       <c r="E127" s="2">
@@ -3077,11 +3077,11 @@
         <v>0.0</v>
       </c>
       <c r="C128" s="2">
-        <f>IF(B128&gt;0,ROUND(B128*$B$5/12,2),0)</f>
+        <f>IF(B128&gt;0.005,ROUND(B128*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D128" s="2">
-        <f>IF(B128&gt;0,MIN($B$6+$B$7,B128+C128),0)</f>
+        <f>IF(B128&gt;0.005,MIN($B$6+$B$7,B128+C128),0)</f>
         <v>0</v>
       </c>
       <c r="E128" s="2">
@@ -3102,11 +3102,11 @@
         <v>0.0</v>
       </c>
       <c r="C129" s="2">
-        <f>IF(B129&gt;0,ROUND(B129*$B$5/12,2),0)</f>
+        <f>IF(B129&gt;0.005,ROUND(B129*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D129" s="2">
-        <f>IF(B129&gt;0,MIN($B$6+$B$7,B129+C129),0)</f>
+        <f>IF(B129&gt;0.005,MIN($B$6+$B$7,B129+C129),0)</f>
         <v>0</v>
       </c>
       <c r="E129" s="2">
@@ -3127,11 +3127,11 @@
         <v>0.0</v>
       </c>
       <c r="C130" s="2">
-        <f>IF(B130&gt;0,ROUND(B130*$B$5/12,2),0)</f>
+        <f>IF(B130&gt;0.005,ROUND(B130*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D130" s="2">
-        <f>IF(B130&gt;0,MIN($B$6+$B$7,B130+C130),0)</f>
+        <f>IF(B130&gt;0.005,MIN($B$6+$B$7,B130+C130),0)</f>
         <v>0</v>
       </c>
       <c r="E130" s="2">
@@ -3152,11 +3152,11 @@
         <v>0.0</v>
       </c>
       <c r="C131" s="2">
-        <f>IF(B131&gt;0,ROUND(B131*$B$5/12,2),0)</f>
+        <f>IF(B131&gt;0.005,ROUND(B131*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D131" s="2">
-        <f>IF(B131&gt;0,MIN($B$6+$B$7,B131+C131),0)</f>
+        <f>IF(B131&gt;0.005,MIN($B$6+$B$7,B131+C131),0)</f>
         <v>0</v>
       </c>
       <c r="E131" s="2">
@@ -3177,11 +3177,11 @@
         <v>0.0</v>
       </c>
       <c r="C132" s="2">
-        <f>IF(B132&gt;0,ROUND(B132*$B$5/12,2),0)</f>
+        <f>IF(B132&gt;0.005,ROUND(B132*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D132" s="2">
-        <f>IF(B132&gt;0,MIN($B$6+$B$7,B132+C132),0)</f>
+        <f>IF(B132&gt;0.005,MIN($B$6+$B$7,B132+C132),0)</f>
         <v>0</v>
       </c>
       <c r="E132" s="2">
@@ -3202,11 +3202,11 @@
         <v>0.0</v>
       </c>
       <c r="C133" s="2">
-        <f>IF(B133&gt;0,ROUND(B133*$B$5/12,2),0)</f>
+        <f>IF(B133&gt;0.005,ROUND(B133*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D133" s="2">
-        <f>IF(B133&gt;0,MIN($B$6+$B$7,B133+C133),0)</f>
+        <f>IF(B133&gt;0.005,MIN($B$6+$B$7,B133+C133),0)</f>
         <v>0</v>
       </c>
       <c r="E133" s="2">
@@ -3227,11 +3227,11 @@
         <v>0.0</v>
       </c>
       <c r="C134" s="2">
-        <f>IF(B134&gt;0,ROUND(B134*$B$5/12,2),0)</f>
+        <f>IF(B134&gt;0.005,ROUND(B134*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D134" s="2">
-        <f>IF(B134&gt;0,MIN($B$6+$B$7,B134+C134),0)</f>
+        <f>IF(B134&gt;0.005,MIN($B$6+$B$7,B134+C134),0)</f>
         <v>0</v>
       </c>
       <c r="E134" s="2">
@@ -3252,11 +3252,11 @@
         <v>0.0</v>
       </c>
       <c r="C135" s="2">
-        <f>IF(B135&gt;0,ROUND(B135*$B$5/12,2),0)</f>
+        <f>IF(B135&gt;0.005,ROUND(B135*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D135" s="2">
-        <f>IF(B135&gt;0,MIN($B$6+$B$7,B135+C135),0)</f>
+        <f>IF(B135&gt;0.005,MIN($B$6+$B$7,B135+C135),0)</f>
         <v>0</v>
       </c>
       <c r="E135" s="2">
@@ -3277,11 +3277,11 @@
         <v>0.0</v>
       </c>
       <c r="C136" s="2">
-        <f>IF(B136&gt;0,ROUND(B136*$B$5/12,2),0)</f>
+        <f>IF(B136&gt;0.005,ROUND(B136*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D136" s="2">
-        <f>IF(B136&gt;0,MIN($B$6+$B$7,B136+C136),0)</f>
+        <f>IF(B136&gt;0.005,MIN($B$6+$B$7,B136+C136),0)</f>
         <v>0</v>
       </c>
       <c r="E136" s="2">
@@ -3302,11 +3302,11 @@
         <v>0.0</v>
       </c>
       <c r="C137" s="2">
-        <f>IF(B137&gt;0,ROUND(B137*$B$5/12,2),0)</f>
+        <f>IF(B137&gt;0.005,ROUND(B137*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D137" s="2">
-        <f>IF(B137&gt;0,MIN($B$6+$B$7,B137+C137),0)</f>
+        <f>IF(B137&gt;0.005,MIN($B$6+$B$7,B137+C137),0)</f>
         <v>0</v>
       </c>
       <c r="E137" s="2">
@@ -3327,11 +3327,11 @@
         <v>0.0</v>
       </c>
       <c r="C138" s="2">
-        <f>IF(B138&gt;0,ROUND(B138*$B$5/12,2),0)</f>
+        <f>IF(B138&gt;0.005,ROUND(B138*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D138" s="2">
-        <f>IF(B138&gt;0,MIN($B$6+$B$7,B138+C138),0)</f>
+        <f>IF(B138&gt;0.005,MIN($B$6+$B$7,B138+C138),0)</f>
         <v>0</v>
       </c>
       <c r="E138" s="2">
@@ -3352,11 +3352,11 @@
         <v>0.0</v>
       </c>
       <c r="C139" s="2">
-        <f>IF(B139&gt;0,ROUND(B139*$B$5/12,2),0)</f>
+        <f>IF(B139&gt;0.005,ROUND(B139*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D139" s="2">
-        <f>IF(B139&gt;0,MIN($B$6+$B$7,B139+C139),0)</f>
+        <f>IF(B139&gt;0.005,MIN($B$6+$B$7,B139+C139),0)</f>
         <v>0</v>
       </c>
       <c r="E139" s="2">
@@ -3377,11 +3377,11 @@
         <v>0.0</v>
       </c>
       <c r="C140" s="2">
-        <f>IF(B140&gt;0,ROUND(B140*$B$5/12,2),0)</f>
+        <f>IF(B140&gt;0.005,ROUND(B140*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D140" s="2">
-        <f>IF(B140&gt;0,MIN($B$6+$B$7,B140+C140),0)</f>
+        <f>IF(B140&gt;0.005,MIN($B$6+$B$7,B140+C140),0)</f>
         <v>0</v>
       </c>
       <c r="E140" s="2">
@@ -3402,11 +3402,11 @@
         <v>0.0</v>
       </c>
       <c r="C141" s="2">
-        <f>IF(B141&gt;0,ROUND(B141*$B$5/12,2),0)</f>
+        <f>IF(B141&gt;0.005,ROUND(B141*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D141" s="2">
-        <f>IF(B141&gt;0,MIN($B$6+$B$7,B141+C141),0)</f>
+        <f>IF(B141&gt;0.005,MIN($B$6+$B$7,B141+C141),0)</f>
         <v>0</v>
       </c>
       <c r="E141" s="2">
@@ -3427,11 +3427,11 @@
         <v>0.0</v>
       </c>
       <c r="C142" s="2">
-        <f>IF(B142&gt;0,ROUND(B142*$B$5/12,2),0)</f>
+        <f>IF(B142&gt;0.005,ROUND(B142*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D142" s="2">
-        <f>IF(B142&gt;0,MIN($B$6+$B$7,B142+C142),0)</f>
+        <f>IF(B142&gt;0.005,MIN($B$6+$B$7,B142+C142),0)</f>
         <v>0</v>
       </c>
       <c r="E142" s="2">
@@ -3452,11 +3452,11 @@
         <v>0.0</v>
       </c>
       <c r="C143" s="2">
-        <f>IF(B143&gt;0,ROUND(B143*$B$5/12,2),0)</f>
+        <f>IF(B143&gt;0.005,ROUND(B143*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D143" s="2">
-        <f>IF(B143&gt;0,MIN($B$6+$B$7,B143+C143),0)</f>
+        <f>IF(B143&gt;0.005,MIN($B$6+$B$7,B143+C143),0)</f>
         <v>0</v>
       </c>
       <c r="E143" s="2">
@@ -3477,11 +3477,11 @@
         <v>0.0</v>
       </c>
       <c r="C144" s="2">
-        <f>IF(B144&gt;0,ROUND(B144*$B$5/12,2),0)</f>
+        <f>IF(B144&gt;0.005,ROUND(B144*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D144" s="2">
-        <f>IF(B144&gt;0,MIN($B$6+$B$7,B144+C144),0)</f>
+        <f>IF(B144&gt;0.005,MIN($B$6+$B$7,B144+C144),0)</f>
         <v>0</v>
       </c>
       <c r="E144" s="2">
@@ -3502,11 +3502,11 @@
         <v>0.0</v>
       </c>
       <c r="C145" s="2">
-        <f>IF(B145&gt;0,ROUND(B145*$B$5/12,2),0)</f>
+        <f>IF(B145&gt;0.005,ROUND(B145*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D145" s="2">
-        <f>IF(B145&gt;0,MIN($B$6+$B$7,B145+C145),0)</f>
+        <f>IF(B145&gt;0.005,MIN($B$6+$B$7,B145+C145),0)</f>
         <v>0</v>
       </c>
       <c r="E145" s="2">
@@ -3527,11 +3527,11 @@
         <v>0.0</v>
       </c>
       <c r="C146" s="2">
-        <f>IF(B146&gt;0,ROUND(B146*$B$5/12,2),0)</f>
+        <f>IF(B146&gt;0.005,ROUND(B146*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D146" s="2">
-        <f>IF(B146&gt;0,MIN($B$6+$B$7,B146+C146),0)</f>
+        <f>IF(B146&gt;0.005,MIN($B$6+$B$7,B146+C146),0)</f>
         <v>0</v>
       </c>
       <c r="E146" s="2">
@@ -3552,11 +3552,11 @@
         <v>0.0</v>
       </c>
       <c r="C147" s="2">
-        <f>IF(B147&gt;0,ROUND(B147*$B$5/12,2),0)</f>
+        <f>IF(B147&gt;0.005,ROUND(B147*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D147" s="2">
-        <f>IF(B147&gt;0,MIN($B$6+$B$7,B147+C147),0)</f>
+        <f>IF(B147&gt;0.005,MIN($B$6+$B$7,B147+C147),0)</f>
         <v>0</v>
       </c>
       <c r="E147" s="2">
@@ -3577,11 +3577,11 @@
         <v>0.0</v>
       </c>
       <c r="C148" s="2">
-        <f>IF(B148&gt;0,ROUND(B148*$B$5/12,2),0)</f>
+        <f>IF(B148&gt;0.005,ROUND(B148*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D148" s="2">
-        <f>IF(B148&gt;0,MIN($B$6+$B$7,B148+C148),0)</f>
+        <f>IF(B148&gt;0.005,MIN($B$6+$B$7,B148+C148),0)</f>
         <v>0</v>
       </c>
       <c r="E148" s="2">
@@ -3602,11 +3602,11 @@
         <v>0.0</v>
       </c>
       <c r="C149" s="2">
-        <f>IF(B149&gt;0,ROUND(B149*$B$5/12,2),0)</f>
+        <f>IF(B149&gt;0.005,ROUND(B149*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D149" s="2">
-        <f>IF(B149&gt;0,MIN($B$6+$B$7,B149+C149),0)</f>
+        <f>IF(B149&gt;0.005,MIN($B$6+$B$7,B149+C149),0)</f>
         <v>0</v>
       </c>
       <c r="E149" s="2">
@@ -3627,11 +3627,11 @@
         <v>0.0</v>
       </c>
       <c r="C150" s="2">
-        <f>IF(B150&gt;0,ROUND(B150*$B$5/12,2),0)</f>
+        <f>IF(B150&gt;0.005,ROUND(B150*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D150" s="2">
-        <f>IF(B150&gt;0,MIN($B$6+$B$7,B150+C150),0)</f>
+        <f>IF(B150&gt;0.005,MIN($B$6+$B$7,B150+C150),0)</f>
         <v>0</v>
       </c>
       <c r="E150" s="2">
@@ -3652,11 +3652,11 @@
         <v>0.0</v>
       </c>
       <c r="C151" s="2">
-        <f>IF(B151&gt;0,ROUND(B151*$B$5/12,2),0)</f>
+        <f>IF(B151&gt;0.005,ROUND(B151*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D151" s="2">
-        <f>IF(B151&gt;0,MIN($B$6+$B$7,B151+C151),0)</f>
+        <f>IF(B151&gt;0.005,MIN($B$6+$B$7,B151+C151),0)</f>
         <v>0</v>
       </c>
       <c r="E151" s="2">
@@ -3677,11 +3677,11 @@
         <v>0.0</v>
       </c>
       <c r="C152" s="2">
-        <f>IF(B152&gt;0,ROUND(B152*$B$5/12,2),0)</f>
+        <f>IF(B152&gt;0.005,ROUND(B152*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D152" s="2">
-        <f>IF(B152&gt;0,MIN($B$6+$B$7,B152+C152),0)</f>
+        <f>IF(B152&gt;0.005,MIN($B$6+$B$7,B152+C152),0)</f>
         <v>0</v>
       </c>
       <c r="E152" s="2">
@@ -3702,11 +3702,11 @@
         <v>0.0</v>
       </c>
       <c r="C153" s="2">
-        <f>IF(B153&gt;0,ROUND(B153*$B$5/12,2),0)</f>
+        <f>IF(B153&gt;0.005,ROUND(B153*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D153" s="2">
-        <f>IF(B153&gt;0,MIN($B$6+$B$7,B153+C153),0)</f>
+        <f>IF(B153&gt;0.005,MIN($B$6+$B$7,B153+C153),0)</f>
         <v>0</v>
       </c>
       <c r="E153" s="2">
@@ -3727,11 +3727,11 @@
         <v>0.0</v>
       </c>
       <c r="C154" s="2">
-        <f>IF(B154&gt;0,ROUND(B154*$B$5/12,2),0)</f>
+        <f>IF(B154&gt;0.005,ROUND(B154*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D154" s="2">
-        <f>IF(B154&gt;0,MIN($B$6+$B$7,B154+C154),0)</f>
+        <f>IF(B154&gt;0.005,MIN($B$6+$B$7,B154+C154),0)</f>
         <v>0</v>
       </c>
       <c r="E154" s="2">
@@ -3752,11 +3752,11 @@
         <v>0.0</v>
       </c>
       <c r="C155" s="2">
-        <f>IF(B155&gt;0,ROUND(B155*$B$5/12,2),0)</f>
+        <f>IF(B155&gt;0.005,ROUND(B155*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D155" s="2">
-        <f>IF(B155&gt;0,MIN($B$6+$B$7,B155+C155),0)</f>
+        <f>IF(B155&gt;0.005,MIN($B$6+$B$7,B155+C155),0)</f>
         <v>0</v>
       </c>
       <c r="E155" s="2">
@@ -3777,11 +3777,11 @@
         <v>0.0</v>
       </c>
       <c r="C156" s="2">
-        <f>IF(B156&gt;0,ROUND(B156*$B$5/12,2),0)</f>
+        <f>IF(B156&gt;0.005,ROUND(B156*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D156" s="2">
-        <f>IF(B156&gt;0,MIN($B$6+$B$7,B156+C156),0)</f>
+        <f>IF(B156&gt;0.005,MIN($B$6+$B$7,B156+C156),0)</f>
         <v>0</v>
       </c>
       <c r="E156" s="2">
@@ -3802,11 +3802,11 @@
         <v>0.0</v>
       </c>
       <c r="C157" s="2">
-        <f>IF(B157&gt;0,ROUND(B157*$B$5/12,2),0)</f>
+        <f>IF(B157&gt;0.005,ROUND(B157*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D157" s="2">
-        <f>IF(B157&gt;0,MIN($B$6+$B$7,B157+C157),0)</f>
+        <f>IF(B157&gt;0.005,MIN($B$6+$B$7,B157+C157),0)</f>
         <v>0</v>
       </c>
       <c r="E157" s="2">
@@ -3827,11 +3827,11 @@
         <v>0.0</v>
       </c>
       <c r="C158" s="2">
-        <f>IF(B158&gt;0,ROUND(B158*$B$5/12,2),0)</f>
+        <f>IF(B158&gt;0.005,ROUND(B158*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D158" s="2">
-        <f>IF(B158&gt;0,MIN($B$6+$B$7,B158+C158),0)</f>
+        <f>IF(B158&gt;0.005,MIN($B$6+$B$7,B158+C158),0)</f>
         <v>0</v>
       </c>
       <c r="E158" s="2">
@@ -3852,11 +3852,11 @@
         <v>0.0</v>
       </c>
       <c r="C159" s="2">
-        <f>IF(B159&gt;0,ROUND(B159*$B$5/12,2),0)</f>
+        <f>IF(B159&gt;0.005,ROUND(B159*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D159" s="2">
-        <f>IF(B159&gt;0,MIN($B$6+$B$7,B159+C159),0)</f>
+        <f>IF(B159&gt;0.005,MIN($B$6+$B$7,B159+C159),0)</f>
         <v>0</v>
       </c>
       <c r="E159" s="2">
@@ -3877,11 +3877,11 @@
         <v>0.0</v>
       </c>
       <c r="C160" s="2">
-        <f>IF(B160&gt;0,ROUND(B160*$B$5/12,2),0)</f>
+        <f>IF(B160&gt;0.005,ROUND(B160*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D160" s="2">
-        <f>IF(B160&gt;0,MIN($B$6+$B$7,B160+C160),0)</f>
+        <f>IF(B160&gt;0.005,MIN($B$6+$B$7,B160+C160),0)</f>
         <v>0</v>
       </c>
       <c r="E160" s="2">
@@ -3902,11 +3902,11 @@
         <v>0.0</v>
       </c>
       <c r="C161" s="2">
-        <f>IF(B161&gt;0,ROUND(B161*$B$5/12,2),0)</f>
+        <f>IF(B161&gt;0.005,ROUND(B161*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D161" s="2">
-        <f>IF(B161&gt;0,MIN($B$6+$B$7,B161+C161),0)</f>
+        <f>IF(B161&gt;0.005,MIN($B$6+$B$7,B161+C161),0)</f>
         <v>0</v>
       </c>
       <c r="E161" s="2">
@@ -3927,11 +3927,11 @@
         <v>0.0</v>
       </c>
       <c r="C162" s="2">
-        <f>IF(B162&gt;0,ROUND(B162*$B$5/12,2),0)</f>
+        <f>IF(B162&gt;0.005,ROUND(B162*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D162" s="2">
-        <f>IF(B162&gt;0,MIN($B$6+$B$7,B162+C162),0)</f>
+        <f>IF(B162&gt;0.005,MIN($B$6+$B$7,B162+C162),0)</f>
         <v>0</v>
       </c>
       <c r="E162" s="2">
@@ -3952,11 +3952,11 @@
         <v>0.0</v>
       </c>
       <c r="C163" s="2">
-        <f>IF(B163&gt;0,ROUND(B163*$B$5/12,2),0)</f>
+        <f>IF(B163&gt;0.005,ROUND(B163*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D163" s="2">
-        <f>IF(B163&gt;0,MIN($B$6+$B$7,B163+C163),0)</f>
+        <f>IF(B163&gt;0.005,MIN($B$6+$B$7,B163+C163),0)</f>
         <v>0</v>
       </c>
       <c r="E163" s="2">
@@ -3977,11 +3977,11 @@
         <v>0.0</v>
       </c>
       <c r="C164" s="2">
-        <f>IF(B164&gt;0,ROUND(B164*$B$5/12,2),0)</f>
+        <f>IF(B164&gt;0.005,ROUND(B164*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D164" s="2">
-        <f>IF(B164&gt;0,MIN($B$6+$B$7,B164+C164),0)</f>
+        <f>IF(B164&gt;0.005,MIN($B$6+$B$7,B164+C164),0)</f>
         <v>0</v>
       </c>
       <c r="E164" s="2">
@@ -4002,11 +4002,11 @@
         <v>0.0</v>
       </c>
       <c r="C165" s="2">
-        <f>IF(B165&gt;0,ROUND(B165*$B$5/12,2),0)</f>
+        <f>IF(B165&gt;0.005,ROUND(B165*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D165" s="2">
-        <f>IF(B165&gt;0,MIN($B$6+$B$7,B165+C165),0)</f>
+        <f>IF(B165&gt;0.005,MIN($B$6+$B$7,B165+C165),0)</f>
         <v>0</v>
       </c>
       <c r="E165" s="2">
@@ -4027,11 +4027,11 @@
         <v>0.0</v>
       </c>
       <c r="C166" s="2">
-        <f>IF(B166&gt;0,ROUND(B166*$B$5/12,2),0)</f>
+        <f>IF(B166&gt;0.005,ROUND(B166*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D166" s="2">
-        <f>IF(B166&gt;0,MIN($B$6+$B$7,B166+C166),0)</f>
+        <f>IF(B166&gt;0.005,MIN($B$6+$B$7,B166+C166),0)</f>
         <v>0</v>
       </c>
       <c r="E166" s="2">
@@ -4052,11 +4052,11 @@
         <v>0.0</v>
       </c>
       <c r="C167" s="2">
-        <f>IF(B167&gt;0,ROUND(B167*$B$5/12,2),0)</f>
+        <f>IF(B167&gt;0.005,ROUND(B167*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D167" s="2">
-        <f>IF(B167&gt;0,MIN($B$6+$B$7,B167+C167),0)</f>
+        <f>IF(B167&gt;0.005,MIN($B$6+$B$7,B167+C167),0)</f>
         <v>0</v>
       </c>
       <c r="E167" s="2">
@@ -4077,11 +4077,11 @@
         <v>0.0</v>
       </c>
       <c r="C168" s="2">
-        <f>IF(B168&gt;0,ROUND(B168*$B$5/12,2),0)</f>
+        <f>IF(B168&gt;0.005,ROUND(B168*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D168" s="2">
-        <f>IF(B168&gt;0,MIN($B$6+$B$7,B168+C168),0)</f>
+        <f>IF(B168&gt;0.005,MIN($B$6+$B$7,B168+C168),0)</f>
         <v>0</v>
       </c>
       <c r="E168" s="2">
@@ -4102,11 +4102,11 @@
         <v>0.0</v>
       </c>
       <c r="C169" s="2">
-        <f>IF(B169&gt;0,ROUND(B169*$B$5/12,2),0)</f>
+        <f>IF(B169&gt;0.005,ROUND(B169*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D169" s="2">
-        <f>IF(B169&gt;0,MIN($B$6+$B$7,B169+C169),0)</f>
+        <f>IF(B169&gt;0.005,MIN($B$6+$B$7,B169+C169),0)</f>
         <v>0</v>
       </c>
       <c r="E169" s="2">
@@ -4127,11 +4127,11 @@
         <v>0.0</v>
       </c>
       <c r="C170" s="2">
-        <f>IF(B170&gt;0,ROUND(B170*$B$5/12,2),0)</f>
+        <f>IF(B170&gt;0.005,ROUND(B170*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D170" s="2">
-        <f>IF(B170&gt;0,MIN($B$6+$B$7,B170+C170),0)</f>
+        <f>IF(B170&gt;0.005,MIN($B$6+$B$7,B170+C170),0)</f>
         <v>0</v>
       </c>
       <c r="E170" s="2">
@@ -4152,11 +4152,11 @@
         <v>0.0</v>
       </c>
       <c r="C171" s="2">
-        <f>IF(B171&gt;0,ROUND(B171*$B$5/12,2),0)</f>
+        <f>IF(B171&gt;0.005,ROUND(B171*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D171" s="2">
-        <f>IF(B171&gt;0,MIN($B$6+$B$7,B171+C171),0)</f>
+        <f>IF(B171&gt;0.005,MIN($B$6+$B$7,B171+C171),0)</f>
         <v>0</v>
       </c>
       <c r="E171" s="2">
@@ -4177,11 +4177,11 @@
         <v>0.0</v>
       </c>
       <c r="C172" s="2">
-        <f>IF(B172&gt;0,ROUND(B172*$B$5/12,2),0)</f>
+        <f>IF(B172&gt;0.005,ROUND(B172*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D172" s="2">
-        <f>IF(B172&gt;0,MIN($B$6+$B$7,B172+C172),0)</f>
+        <f>IF(B172&gt;0.005,MIN($B$6+$B$7,B172+C172),0)</f>
         <v>0</v>
       </c>
       <c r="E172" s="2">
@@ -4202,11 +4202,11 @@
         <v>0.0</v>
       </c>
       <c r="C173" s="2">
-        <f>IF(B173&gt;0,ROUND(B173*$B$5/12,2),0)</f>
+        <f>IF(B173&gt;0.005,ROUND(B173*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D173" s="2">
-        <f>IF(B173&gt;0,MIN($B$6+$B$7,B173+C173),0)</f>
+        <f>IF(B173&gt;0.005,MIN($B$6+$B$7,B173+C173),0)</f>
         <v>0</v>
       </c>
       <c r="E173" s="2">
@@ -4227,11 +4227,11 @@
         <v>0.0</v>
       </c>
       <c r="C174" s="2">
-        <f>IF(B174&gt;0,ROUND(B174*$B$5/12,2),0)</f>
+        <f>IF(B174&gt;0.005,ROUND(B174*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D174" s="2">
-        <f>IF(B174&gt;0,MIN($B$6+$B$7,B174+C174),0)</f>
+        <f>IF(B174&gt;0.005,MIN($B$6+$B$7,B174+C174),0)</f>
         <v>0</v>
       </c>
       <c r="E174" s="2">
@@ -4252,11 +4252,11 @@
         <v>0.0</v>
       </c>
       <c r="C175" s="2">
-        <f>IF(B175&gt;0,ROUND(B175*$B$5/12,2),0)</f>
+        <f>IF(B175&gt;0.005,ROUND(B175*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D175" s="2">
-        <f>IF(B175&gt;0,MIN($B$6+$B$7,B175+C175),0)</f>
+        <f>IF(B175&gt;0.005,MIN($B$6+$B$7,B175+C175),0)</f>
         <v>0</v>
       </c>
       <c r="E175" s="2">
@@ -4277,11 +4277,11 @@
         <v>0.0</v>
       </c>
       <c r="C176" s="2">
-        <f>IF(B176&gt;0,ROUND(B176*$B$5/12,2),0)</f>
+        <f>IF(B176&gt;0.005,ROUND(B176*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D176" s="2">
-        <f>IF(B176&gt;0,MIN($B$6+$B$7,B176+C176),0)</f>
+        <f>IF(B176&gt;0.005,MIN($B$6+$B$7,B176+C176),0)</f>
         <v>0</v>
       </c>
       <c r="E176" s="2">
@@ -4302,11 +4302,11 @@
         <v>0.0</v>
       </c>
       <c r="C177" s="2">
-        <f>IF(B177&gt;0,ROUND(B177*$B$5/12,2),0)</f>
+        <f>IF(B177&gt;0.005,ROUND(B177*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D177" s="2">
-        <f>IF(B177&gt;0,MIN($B$6+$B$7,B177+C177),0)</f>
+        <f>IF(B177&gt;0.005,MIN($B$6+$B$7,B177+C177),0)</f>
         <v>0</v>
       </c>
       <c r="E177" s="2">
@@ -4327,11 +4327,11 @@
         <v>0.0</v>
       </c>
       <c r="C178" s="2">
-        <f>IF(B178&gt;0,ROUND(B178*$B$5/12,2),0)</f>
+        <f>IF(B178&gt;0.005,ROUND(B178*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D178" s="2">
-        <f>IF(B178&gt;0,MIN($B$6+$B$7,B178+C178),0)</f>
+        <f>IF(B178&gt;0.005,MIN($B$6+$B$7,B178+C178),0)</f>
         <v>0</v>
       </c>
       <c r="E178" s="2">
@@ -4352,11 +4352,11 @@
         <v>0.0</v>
       </c>
       <c r="C179" s="2">
-        <f>IF(B179&gt;0,ROUND(B179*$B$5/12,2),0)</f>
+        <f>IF(B179&gt;0.005,ROUND(B179*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D179" s="2">
-        <f>IF(B179&gt;0,MIN($B$6+$B$7,B179+C179),0)</f>
+        <f>IF(B179&gt;0.005,MIN($B$6+$B$7,B179+C179),0)</f>
         <v>0</v>
       </c>
       <c r="E179" s="2">
@@ -4377,11 +4377,11 @@
         <v>0.0</v>
       </c>
       <c r="C180" s="2">
-        <f>IF(B180&gt;0,ROUND(B180*$B$5/12,2),0)</f>
+        <f>IF(B180&gt;0.005,ROUND(B180*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D180" s="2">
-        <f>IF(B180&gt;0,MIN($B$6+$B$7,B180+C180),0)</f>
+        <f>IF(B180&gt;0.005,MIN($B$6+$B$7,B180+C180),0)</f>
         <v>0</v>
       </c>
       <c r="E180" s="2">
@@ -4402,11 +4402,11 @@
         <v>0.0</v>
       </c>
       <c r="C181" s="2">
-        <f>IF(B181&gt;0,ROUND(B181*$B$5/12,2),0)</f>
+        <f>IF(B181&gt;0.005,ROUND(B181*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D181" s="2">
-        <f>IF(B181&gt;0,MIN($B$6+$B$7,B181+C181),0)</f>
+        <f>IF(B181&gt;0.005,MIN($B$6+$B$7,B181+C181),0)</f>
         <v>0</v>
       </c>
       <c r="E181" s="2">
@@ -4427,11 +4427,11 @@
         <v>0.0</v>
       </c>
       <c r="C182" s="2">
-        <f>IF(B182&gt;0,ROUND(B182*$B$5/12,2),0)</f>
+        <f>IF(B182&gt;0.005,ROUND(B182*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D182" s="2">
-        <f>IF(B182&gt;0,MIN($B$6+$B$7,B182+C182),0)</f>
+        <f>IF(B182&gt;0.005,MIN($B$6+$B$7,B182+C182),0)</f>
         <v>0</v>
       </c>
       <c r="E182" s="2">
@@ -4452,11 +4452,11 @@
         <v>0.0</v>
       </c>
       <c r="C183" s="2">
-        <f>IF(B183&gt;0,ROUND(B183*$B$5/12,2),0)</f>
+        <f>IF(B183&gt;0.005,ROUND(B183*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D183" s="2">
-        <f>IF(B183&gt;0,MIN($B$6+$B$7,B183+C183),0)</f>
+        <f>IF(B183&gt;0.005,MIN($B$6+$B$7,B183+C183),0)</f>
         <v>0</v>
       </c>
       <c r="E183" s="2">
@@ -4477,11 +4477,11 @@
         <v>0.0</v>
       </c>
       <c r="C184" s="2">
-        <f>IF(B184&gt;0,ROUND(B184*$B$5/12,2),0)</f>
+        <f>IF(B184&gt;0.005,ROUND(B184*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D184" s="2">
-        <f>IF(B184&gt;0,MIN($B$6+$B$7,B184+C184),0)</f>
+        <f>IF(B184&gt;0.005,MIN($B$6+$B$7,B184+C184),0)</f>
         <v>0</v>
       </c>
       <c r="E184" s="2">
@@ -4502,11 +4502,11 @@
         <v>0.0</v>
       </c>
       <c r="C185" s="2">
-        <f>IF(B185&gt;0,ROUND(B185*$B$5/12,2),0)</f>
+        <f>IF(B185&gt;0.005,ROUND(B185*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D185" s="2">
-        <f>IF(B185&gt;0,MIN($B$6+$B$7,B185+C185),0)</f>
+        <f>IF(B185&gt;0.005,MIN($B$6+$B$7,B185+C185),0)</f>
         <v>0</v>
       </c>
       <c r="E185" s="2">
@@ -4527,11 +4527,11 @@
         <v>0.0</v>
       </c>
       <c r="C186" s="2">
-        <f>IF(B186&gt;0,ROUND(B186*$B$5/12,2),0)</f>
+        <f>IF(B186&gt;0.005,ROUND(B186*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D186" s="2">
-        <f>IF(B186&gt;0,MIN($B$6+$B$7,B186+C186),0)</f>
+        <f>IF(B186&gt;0.005,MIN($B$6+$B$7,B186+C186),0)</f>
         <v>0</v>
       </c>
       <c r="E186" s="2">
@@ -4552,11 +4552,11 @@
         <v>0.0</v>
       </c>
       <c r="C187" s="2">
-        <f>IF(B187&gt;0,ROUND(B187*$B$5/12,2),0)</f>
+        <f>IF(B187&gt;0.005,ROUND(B187*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D187" s="2">
-        <f>IF(B187&gt;0,MIN($B$6+$B$7,B187+C187),0)</f>
+        <f>IF(B187&gt;0.005,MIN($B$6+$B$7,B187+C187),0)</f>
         <v>0</v>
       </c>
       <c r="E187" s="2">
@@ -4577,11 +4577,11 @@
         <v>0.0</v>
       </c>
       <c r="C188" s="2">
-        <f>IF(B188&gt;0,ROUND(B188*$B$5/12,2),0)</f>
+        <f>IF(B188&gt;0.005,ROUND(B188*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D188" s="2">
-        <f>IF(B188&gt;0,MIN($B$6+$B$7,B188+C188),0)</f>
+        <f>IF(B188&gt;0.005,MIN($B$6+$B$7,B188+C188),0)</f>
         <v>0</v>
       </c>
       <c r="E188" s="2">
@@ -4602,11 +4602,11 @@
         <v>0.0</v>
       </c>
       <c r="C189" s="2">
-        <f>IF(B189&gt;0,ROUND(B189*$B$5/12,2),0)</f>
+        <f>IF(B189&gt;0.005,ROUND(B189*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D189" s="2">
-        <f>IF(B189&gt;0,MIN($B$6+$B$7,B189+C189),0)</f>
+        <f>IF(B189&gt;0.005,MIN($B$6+$B$7,B189+C189),0)</f>
         <v>0</v>
       </c>
       <c r="E189" s="2">
@@ -4627,11 +4627,11 @@
         <v>0.0</v>
       </c>
       <c r="C190" s="2">
-        <f>IF(B190&gt;0,ROUND(B190*$B$5/12,2),0)</f>
+        <f>IF(B190&gt;0.005,ROUND(B190*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D190" s="2">
-        <f>IF(B190&gt;0,MIN($B$6+$B$7,B190+C190),0)</f>
+        <f>IF(B190&gt;0.005,MIN($B$6+$B$7,B190+C190),0)</f>
         <v>0</v>
       </c>
       <c r="E190" s="2">
@@ -4652,11 +4652,11 @@
         <v>0.0</v>
       </c>
       <c r="C191" s="2">
-        <f>IF(B191&gt;0,ROUND(B191*$B$5/12,2),0)</f>
+        <f>IF(B191&gt;0.005,ROUND(B191*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D191" s="2">
-        <f>IF(B191&gt;0,MIN($B$6+$B$7,B191+C191),0)</f>
+        <f>IF(B191&gt;0.005,MIN($B$6+$B$7,B191+C191),0)</f>
         <v>0</v>
       </c>
       <c r="E191" s="2">
@@ -4677,11 +4677,11 @@
         <v>0.0</v>
       </c>
       <c r="C192" s="2">
-        <f>IF(B192&gt;0,ROUND(B192*$B$5/12,2),0)</f>
+        <f>IF(B192&gt;0.005,ROUND(B192*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D192" s="2">
-        <f>IF(B192&gt;0,MIN($B$6+$B$7,B192+C192),0)</f>
+        <f>IF(B192&gt;0.005,MIN($B$6+$B$7,B192+C192),0)</f>
         <v>0</v>
       </c>
       <c r="E192" s="2">
@@ -4702,11 +4702,11 @@
         <v>0.0</v>
       </c>
       <c r="C193" s="2">
-        <f>IF(B193&gt;0,ROUND(B193*$B$5/12,2),0)</f>
+        <f>IF(B193&gt;0.005,ROUND(B193*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D193" s="2">
-        <f>IF(B193&gt;0,MIN($B$6+$B$7,B193+C193),0)</f>
+        <f>IF(B193&gt;0.005,MIN($B$6+$B$7,B193+C193),0)</f>
         <v>0</v>
       </c>
       <c r="E193" s="2">
@@ -4727,11 +4727,11 @@
         <v>0.0</v>
       </c>
       <c r="C194" s="2">
-        <f>IF(B194&gt;0,ROUND(B194*$B$5/12,2),0)</f>
+        <f>IF(B194&gt;0.005,ROUND(B194*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D194" s="2">
-        <f>IF(B194&gt;0,MIN($B$6+$B$7,B194+C194),0)</f>
+        <f>IF(B194&gt;0.005,MIN($B$6+$B$7,B194+C194),0)</f>
         <v>0</v>
       </c>
       <c r="E194" s="2">
@@ -4752,11 +4752,11 @@
         <v>0.0</v>
       </c>
       <c r="C195" s="2">
-        <f>IF(B195&gt;0,ROUND(B195*$B$5/12,2),0)</f>
+        <f>IF(B195&gt;0.005,ROUND(B195*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D195" s="2">
-        <f>IF(B195&gt;0,MIN($B$6+$B$7,B195+C195),0)</f>
+        <f>IF(B195&gt;0.005,MIN($B$6+$B$7,B195+C195),0)</f>
         <v>0</v>
       </c>
       <c r="E195" s="2">
@@ -4777,11 +4777,11 @@
         <v>0.0</v>
       </c>
       <c r="C196" s="2">
-        <f>IF(B196&gt;0,ROUND(B196*$B$5/12,2),0)</f>
+        <f>IF(B196&gt;0.005,ROUND(B196*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D196" s="2">
-        <f>IF(B196&gt;0,MIN($B$6+$B$7,B196+C196),0)</f>
+        <f>IF(B196&gt;0.005,MIN($B$6+$B$7,B196+C196),0)</f>
         <v>0</v>
       </c>
       <c r="E196" s="2">
@@ -4802,11 +4802,11 @@
         <v>0.0</v>
       </c>
       <c r="C197" s="2">
-        <f>IF(B197&gt;0,ROUND(B197*$B$5/12,2),0)</f>
+        <f>IF(B197&gt;0.005,ROUND(B197*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D197" s="2">
-        <f>IF(B197&gt;0,MIN($B$6+$B$7,B197+C197),0)</f>
+        <f>IF(B197&gt;0.005,MIN($B$6+$B$7,B197+C197),0)</f>
         <v>0</v>
       </c>
       <c r="E197" s="2">
@@ -4827,11 +4827,11 @@
         <v>0.0</v>
       </c>
       <c r="C198" s="2">
-        <f>IF(B198&gt;0,ROUND(B198*$B$5/12,2),0)</f>
+        <f>IF(B198&gt;0.005,ROUND(B198*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D198" s="2">
-        <f>IF(B198&gt;0,MIN($B$6+$B$7,B198+C198),0)</f>
+        <f>IF(B198&gt;0.005,MIN($B$6+$B$7,B198+C198),0)</f>
         <v>0</v>
       </c>
       <c r="E198" s="2">
@@ -4852,11 +4852,11 @@
         <v>0.0</v>
       </c>
       <c r="C199" s="2">
-        <f>IF(B199&gt;0,ROUND(B199*$B$5/12,2),0)</f>
+        <f>IF(B199&gt;0.005,ROUND(B199*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D199" s="2">
-        <f>IF(B199&gt;0,MIN($B$6+$B$7,B199+C199),0)</f>
+        <f>IF(B199&gt;0.005,MIN($B$6+$B$7,B199+C199),0)</f>
         <v>0</v>
       </c>
       <c r="E199" s="2">
@@ -4877,11 +4877,11 @@
         <v>0.0</v>
       </c>
       <c r="C200" s="2">
-        <f>IF(B200&gt;0,ROUND(B200*$B$5/12,2),0)</f>
+        <f>IF(B200&gt;0.005,ROUND(B200*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D200" s="2">
-        <f>IF(B200&gt;0,MIN($B$6+$B$7,B200+C200),0)</f>
+        <f>IF(B200&gt;0.005,MIN($B$6+$B$7,B200+C200),0)</f>
         <v>0</v>
       </c>
       <c r="E200" s="2">
@@ -4902,11 +4902,11 @@
         <v>0.0</v>
       </c>
       <c r="C201" s="2">
-        <f>IF(B201&gt;0,ROUND(B201*$B$5/12,2),0)</f>
+        <f>IF(B201&gt;0.005,ROUND(B201*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D201" s="2">
-        <f>IF(B201&gt;0,MIN($B$6+$B$7,B201+C201),0)</f>
+        <f>IF(B201&gt;0.005,MIN($B$6+$B$7,B201+C201),0)</f>
         <v>0</v>
       </c>
       <c r="E201" s="2">
@@ -4927,11 +4927,11 @@
         <v>0.0</v>
       </c>
       <c r="C202" s="2">
-        <f>IF(B202&gt;0,ROUND(B202*$B$5/12,2),0)</f>
+        <f>IF(B202&gt;0.005,ROUND(B202*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D202" s="2">
-        <f>IF(B202&gt;0,MIN($B$6+$B$7,B202+C202),0)</f>
+        <f>IF(B202&gt;0.005,MIN($B$6+$B$7,B202+C202),0)</f>
         <v>0</v>
       </c>
       <c r="E202" s="2">
@@ -4952,11 +4952,11 @@
         <v>0.0</v>
       </c>
       <c r="C203" s="2">
-        <f>IF(B203&gt;0,ROUND(B203*$B$5/12,2),0)</f>
+        <f>IF(B203&gt;0.005,ROUND(B203*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D203" s="2">
-        <f>IF(B203&gt;0,MIN($B$6+$B$7,B203+C203),0)</f>
+        <f>IF(B203&gt;0.005,MIN($B$6+$B$7,B203+C203),0)</f>
         <v>0</v>
       </c>
       <c r="E203" s="2">
@@ -4977,11 +4977,11 @@
         <v>0.0</v>
       </c>
       <c r="C204" s="2">
-        <f>IF(B204&gt;0,ROUND(B204*$B$5/12,2),0)</f>
+        <f>IF(B204&gt;0.005,ROUND(B204*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D204" s="2">
-        <f>IF(B204&gt;0,MIN($B$6+$B$7,B204+C204),0)</f>
+        <f>IF(B204&gt;0.005,MIN($B$6+$B$7,B204+C204),0)</f>
         <v>0</v>
       </c>
       <c r="E204" s="2">
@@ -5002,11 +5002,11 @@
         <v>0.0</v>
       </c>
       <c r="C205" s="2">
-        <f>IF(B205&gt;0,ROUND(B205*$B$5/12,2),0)</f>
+        <f>IF(B205&gt;0.005,ROUND(B205*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D205" s="2">
-        <f>IF(B205&gt;0,MIN($B$6+$B$7,B205+C205),0)</f>
+        <f>IF(B205&gt;0.005,MIN($B$6+$B$7,B205+C205),0)</f>
         <v>0</v>
       </c>
       <c r="E205" s="2">
@@ -5027,11 +5027,11 @@
         <v>0.0</v>
       </c>
       <c r="C206" s="2">
-        <f>IF(B206&gt;0,ROUND(B206*$B$5/12,2),0)</f>
+        <f>IF(B206&gt;0.005,ROUND(B206*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D206" s="2">
-        <f>IF(B206&gt;0,MIN($B$6+$B$7,B206+C206),0)</f>
+        <f>IF(B206&gt;0.005,MIN($B$6+$B$7,B206+C206),0)</f>
         <v>0</v>
       </c>
       <c r="E206" s="2">
@@ -5052,11 +5052,11 @@
         <v>0.0</v>
       </c>
       <c r="C207" s="2">
-        <f>IF(B207&gt;0,ROUND(B207*$B$5/12,2),0)</f>
+        <f>IF(B207&gt;0.005,ROUND(B207*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D207" s="2">
-        <f>IF(B207&gt;0,MIN($B$6+$B$7,B207+C207),0)</f>
+        <f>IF(B207&gt;0.005,MIN($B$6+$B$7,B207+C207),0)</f>
         <v>0</v>
       </c>
       <c r="E207" s="2">
@@ -5077,11 +5077,11 @@
         <v>0.0</v>
       </c>
       <c r="C208" s="2">
-        <f>IF(B208&gt;0,ROUND(B208*$B$5/12,2),0)</f>
+        <f>IF(B208&gt;0.005,ROUND(B208*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D208" s="2">
-        <f>IF(B208&gt;0,MIN($B$6+$B$7,B208+C208),0)</f>
+        <f>IF(B208&gt;0.005,MIN($B$6+$B$7,B208+C208),0)</f>
         <v>0</v>
       </c>
       <c r="E208" s="2">
@@ -5102,11 +5102,11 @@
         <v>0.0</v>
       </c>
       <c r="C209" s="2">
-        <f>IF(B209&gt;0,ROUND(B209*$B$5/12,2),0)</f>
+        <f>IF(B209&gt;0.005,ROUND(B209*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D209" s="2">
-        <f>IF(B209&gt;0,MIN($B$6+$B$7,B209+C209),0)</f>
+        <f>IF(B209&gt;0.005,MIN($B$6+$B$7,B209+C209),0)</f>
         <v>0</v>
       </c>
       <c r="E209" s="2">
@@ -5127,11 +5127,11 @@
         <v>0.0</v>
       </c>
       <c r="C210" s="2">
-        <f>IF(B210&gt;0,ROUND(B210*$B$5/12,2),0)</f>
+        <f>IF(B210&gt;0.005,ROUND(B210*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D210" s="2">
-        <f>IF(B210&gt;0,MIN($B$6+$B$7,B210+C210),0)</f>
+        <f>IF(B210&gt;0.005,MIN($B$6+$B$7,B210+C210),0)</f>
         <v>0</v>
       </c>
       <c r="E210" s="2">
@@ -5152,11 +5152,11 @@
         <v>0.0</v>
       </c>
       <c r="C211" s="2">
-        <f>IF(B211&gt;0,ROUND(B211*$B$5/12,2),0)</f>
+        <f>IF(B211&gt;0.005,ROUND(B211*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D211" s="2">
-        <f>IF(B211&gt;0,MIN($B$6+$B$7,B211+C211),0)</f>
+        <f>IF(B211&gt;0.005,MIN($B$6+$B$7,B211+C211),0)</f>
         <v>0</v>
       </c>
       <c r="E211" s="2">
@@ -5177,11 +5177,11 @@
         <v>0.0</v>
       </c>
       <c r="C212" s="2">
-        <f>IF(B212&gt;0,ROUND(B212*$B$5/12,2),0)</f>
+        <f>IF(B212&gt;0.005,ROUND(B212*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D212" s="2">
-        <f>IF(B212&gt;0,MIN($B$6+$B$7,B212+C212),0)</f>
+        <f>IF(B212&gt;0.005,MIN($B$6+$B$7,B212+C212),0)</f>
         <v>0</v>
       </c>
       <c r="E212" s="2">
@@ -5202,11 +5202,11 @@
         <v>0.0</v>
       </c>
       <c r="C213" s="2">
-        <f>IF(B213&gt;0,ROUND(B213*$B$5/12,2),0)</f>
+        <f>IF(B213&gt;0.005,ROUND(B213*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D213" s="2">
-        <f>IF(B213&gt;0,MIN($B$6+$B$7,B213+C213),0)</f>
+        <f>IF(B213&gt;0.005,MIN($B$6+$B$7,B213+C213),0)</f>
         <v>0</v>
       </c>
       <c r="E213" s="2">
@@ -5227,11 +5227,11 @@
         <v>0.0</v>
       </c>
       <c r="C214" s="2">
-        <f>IF(B214&gt;0,ROUND(B214*$B$5/12,2),0)</f>
+        <f>IF(B214&gt;0.005,ROUND(B214*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D214" s="2">
-        <f>IF(B214&gt;0,MIN($B$6+$B$7,B214+C214),0)</f>
+        <f>IF(B214&gt;0.005,MIN($B$6+$B$7,B214+C214),0)</f>
         <v>0</v>
       </c>
       <c r="E214" s="2">
@@ -5252,11 +5252,11 @@
         <v>0.0</v>
       </c>
       <c r="C215" s="2">
-        <f>IF(B215&gt;0,ROUND(B215*$B$5/12,2),0)</f>
+        <f>IF(B215&gt;0.005,ROUND(B215*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D215" s="2">
-        <f>IF(B215&gt;0,MIN($B$6+$B$7,B215+C215),0)</f>
+        <f>IF(B215&gt;0.005,MIN($B$6+$B$7,B215+C215),0)</f>
         <v>0</v>
       </c>
       <c r="E215" s="2">
@@ -5277,11 +5277,11 @@
         <v>0.0</v>
       </c>
       <c r="C216" s="2">
-        <f>IF(B216&gt;0,ROUND(B216*$B$5/12,2),0)</f>
+        <f>IF(B216&gt;0.005,ROUND(B216*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D216" s="2">
-        <f>IF(B216&gt;0,MIN($B$6+$B$7,B216+C216),0)</f>
+        <f>IF(B216&gt;0.005,MIN($B$6+$B$7,B216+C216),0)</f>
         <v>0</v>
       </c>
       <c r="E216" s="2">
@@ -5302,11 +5302,11 @@
         <v>0.0</v>
       </c>
       <c r="C217" s="2">
-        <f>IF(B217&gt;0,ROUND(B217*$B$5/12,2),0)</f>
+        <f>IF(B217&gt;0.005,ROUND(B217*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D217" s="2">
-        <f>IF(B217&gt;0,MIN($B$6+$B$7,B217+C217),0)</f>
+        <f>IF(B217&gt;0.005,MIN($B$6+$B$7,B217+C217),0)</f>
         <v>0</v>
       </c>
       <c r="E217" s="2">
@@ -5327,11 +5327,11 @@
         <v>0.0</v>
       </c>
       <c r="C218" s="2">
-        <f>IF(B218&gt;0,ROUND(B218*$B$5/12,2),0)</f>
+        <f>IF(B218&gt;0.005,ROUND(B218*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D218" s="2">
-        <f>IF(B218&gt;0,MIN($B$6+$B$7,B218+C218),0)</f>
+        <f>IF(B218&gt;0.005,MIN($B$6+$B$7,B218+C218),0)</f>
         <v>0</v>
       </c>
       <c r="E218" s="2">
@@ -5352,11 +5352,11 @@
         <v>0.0</v>
       </c>
       <c r="C219" s="2">
-        <f>IF(B219&gt;0,ROUND(B219*$B$5/12,2),0)</f>
+        <f>IF(B219&gt;0.005,ROUND(B219*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D219" s="2">
-        <f>IF(B219&gt;0,MIN($B$6+$B$7,B219+C219),0)</f>
+        <f>IF(B219&gt;0.005,MIN($B$6+$B$7,B219+C219),0)</f>
         <v>0</v>
       </c>
       <c r="E219" s="2">
@@ -5377,11 +5377,11 @@
         <v>0.0</v>
       </c>
       <c r="C220" s="2">
-        <f>IF(B220&gt;0,ROUND(B220*$B$5/12,2),0)</f>
+        <f>IF(B220&gt;0.005,ROUND(B220*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D220" s="2">
-        <f>IF(B220&gt;0,MIN($B$6+$B$7,B220+C220),0)</f>
+        <f>IF(B220&gt;0.005,MIN($B$6+$B$7,B220+C220),0)</f>
         <v>0</v>
       </c>
       <c r="E220" s="2">
@@ -5402,11 +5402,11 @@
         <v>0.0</v>
       </c>
       <c r="C221" s="2">
-        <f>IF(B221&gt;0,ROUND(B221*$B$5/12,2),0)</f>
+        <f>IF(B221&gt;0.005,ROUND(B221*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D221" s="2">
-        <f>IF(B221&gt;0,MIN($B$6+$B$7,B221+C221),0)</f>
+        <f>IF(B221&gt;0.005,MIN($B$6+$B$7,B221+C221),0)</f>
         <v>0</v>
       </c>
       <c r="E221" s="2">
@@ -5427,11 +5427,11 @@
         <v>0.0</v>
       </c>
       <c r="C222" s="2">
-        <f>IF(B222&gt;0,ROUND(B222*$B$5/12,2),0)</f>
+        <f>IF(B222&gt;0.005,ROUND(B222*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D222" s="2">
-        <f>IF(B222&gt;0,MIN($B$6+$B$7,B222+C222),0)</f>
+        <f>IF(B222&gt;0.005,MIN($B$6+$B$7,B222+C222),0)</f>
         <v>0</v>
       </c>
       <c r="E222" s="2">
@@ -5452,11 +5452,11 @@
         <v>0.0</v>
       </c>
       <c r="C223" s="2">
-        <f>IF(B223&gt;0,ROUND(B223*$B$5/12,2),0)</f>
+        <f>IF(B223&gt;0.005,ROUND(B223*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D223" s="2">
-        <f>IF(B223&gt;0,MIN($B$6+$B$7,B223+C223),0)</f>
+        <f>IF(B223&gt;0.005,MIN($B$6+$B$7,B223+C223),0)</f>
         <v>0</v>
       </c>
       <c r="E223" s="2">
@@ -5477,11 +5477,11 @@
         <v>0.0</v>
       </c>
       <c r="C224" s="2">
-        <f>IF(B224&gt;0,ROUND(B224*$B$5/12,2),0)</f>
+        <f>IF(B224&gt;0.005,ROUND(B224*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D224" s="2">
-        <f>IF(B224&gt;0,MIN($B$6+$B$7,B224+C224),0)</f>
+        <f>IF(B224&gt;0.005,MIN($B$6+$B$7,B224+C224),0)</f>
         <v>0</v>
       </c>
       <c r="E224" s="2">
@@ -5502,11 +5502,11 @@
         <v>0.0</v>
       </c>
       <c r="C225" s="2">
-        <f>IF(B225&gt;0,ROUND(B225*$B$5/12,2),0)</f>
+        <f>IF(B225&gt;0.005,ROUND(B225*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D225" s="2">
-        <f>IF(B225&gt;0,MIN($B$6+$B$7,B225+C225),0)</f>
+        <f>IF(B225&gt;0.005,MIN($B$6+$B$7,B225+C225),0)</f>
         <v>0</v>
       </c>
       <c r="E225" s="2">
@@ -5527,11 +5527,11 @@
         <v>0.0</v>
       </c>
       <c r="C226" s="2">
-        <f>IF(B226&gt;0,ROUND(B226*$B$5/12,2),0)</f>
+        <f>IF(B226&gt;0.005,ROUND(B226*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D226" s="2">
-        <f>IF(B226&gt;0,MIN($B$6+$B$7,B226+C226),0)</f>
+        <f>IF(B226&gt;0.005,MIN($B$6+$B$7,B226+C226),0)</f>
         <v>0</v>
       </c>
       <c r="E226" s="2">
@@ -5552,11 +5552,11 @@
         <v>0.0</v>
       </c>
       <c r="C227" s="2">
-        <f>IF(B227&gt;0,ROUND(B227*$B$5/12,2),0)</f>
+        <f>IF(B227&gt;0.005,ROUND(B227*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D227" s="2">
-        <f>IF(B227&gt;0,MIN($B$6+$B$7,B227+C227),0)</f>
+        <f>IF(B227&gt;0.005,MIN($B$6+$B$7,B227+C227),0)</f>
         <v>0</v>
       </c>
       <c r="E227" s="2">
@@ -5577,11 +5577,11 @@
         <v>0.0</v>
       </c>
       <c r="C228" s="2">
-        <f>IF(B228&gt;0,ROUND(B228*$B$5/12,2),0)</f>
+        <f>IF(B228&gt;0.005,ROUND(B228*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D228" s="2">
-        <f>IF(B228&gt;0,MIN($B$6+$B$7,B228+C228),0)</f>
+        <f>IF(B228&gt;0.005,MIN($B$6+$B$7,B228+C228),0)</f>
         <v>0</v>
       </c>
       <c r="E228" s="2">
@@ -5602,11 +5602,11 @@
         <v>0.0</v>
       </c>
       <c r="C229" s="2">
-        <f>IF(B229&gt;0,ROUND(B229*$B$5/12,2),0)</f>
+        <f>IF(B229&gt;0.005,ROUND(B229*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D229" s="2">
-        <f>IF(B229&gt;0,MIN($B$6+$B$7,B229+C229),0)</f>
+        <f>IF(B229&gt;0.005,MIN($B$6+$B$7,B229+C229),0)</f>
         <v>0</v>
       </c>
       <c r="E229" s="2">
@@ -5627,11 +5627,11 @@
         <v>0.0</v>
       </c>
       <c r="C230" s="2">
-        <f>IF(B230&gt;0,ROUND(B230*$B$5/12,2),0)</f>
+        <f>IF(B230&gt;0.005,ROUND(B230*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D230" s="2">
-        <f>IF(B230&gt;0,MIN($B$6+$B$7,B230+C230),0)</f>
+        <f>IF(B230&gt;0.005,MIN($B$6+$B$7,B230+C230),0)</f>
         <v>0</v>
       </c>
       <c r="E230" s="2">
@@ -5652,11 +5652,11 @@
         <v>0.0</v>
       </c>
       <c r="C231" s="2">
-        <f>IF(B231&gt;0,ROUND(B231*$B$5/12,2),0)</f>
+        <f>IF(B231&gt;0.005,ROUND(B231*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D231" s="2">
-        <f>IF(B231&gt;0,MIN($B$6+$B$7,B231+C231),0)</f>
+        <f>IF(B231&gt;0.005,MIN($B$6+$B$7,B231+C231),0)</f>
         <v>0</v>
       </c>
       <c r="E231" s="2">
@@ -5677,11 +5677,11 @@
         <v>0.0</v>
       </c>
       <c r="C232" s="2">
-        <f>IF(B232&gt;0,ROUND(B232*$B$5/12,2),0)</f>
+        <f>IF(B232&gt;0.005,ROUND(B232*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D232" s="2">
-        <f>IF(B232&gt;0,MIN($B$6+$B$7,B232+C232),0)</f>
+        <f>IF(B232&gt;0.005,MIN($B$6+$B$7,B232+C232),0)</f>
         <v>0</v>
       </c>
       <c r="E232" s="2">
@@ -5702,11 +5702,11 @@
         <v>0.0</v>
       </c>
       <c r="C233" s="2">
-        <f>IF(B233&gt;0,ROUND(B233*$B$5/12,2),0)</f>
+        <f>IF(B233&gt;0.005,ROUND(B233*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D233" s="2">
-        <f>IF(B233&gt;0,MIN($B$6+$B$7,B233+C233),0)</f>
+        <f>IF(B233&gt;0.005,MIN($B$6+$B$7,B233+C233),0)</f>
         <v>0</v>
       </c>
       <c r="E233" s="2">
@@ -5727,11 +5727,11 @@
         <v>0.0</v>
       </c>
       <c r="C234" s="2">
-        <f>IF(B234&gt;0,ROUND(B234*$B$5/12,2),0)</f>
+        <f>IF(B234&gt;0.005,ROUND(B234*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D234" s="2">
-        <f>IF(B234&gt;0,MIN($B$6+$B$7,B234+C234),0)</f>
+        <f>IF(B234&gt;0.005,MIN($B$6+$B$7,B234+C234),0)</f>
         <v>0</v>
       </c>
       <c r="E234" s="2">
@@ -5752,11 +5752,11 @@
         <v>0.0</v>
       </c>
       <c r="C235" s="2">
-        <f>IF(B235&gt;0,ROUND(B235*$B$5/12,2),0)</f>
+        <f>IF(B235&gt;0.005,ROUND(B235*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D235" s="2">
-        <f>IF(B235&gt;0,MIN($B$6+$B$7,B235+C235),0)</f>
+        <f>IF(B235&gt;0.005,MIN($B$6+$B$7,B235+C235),0)</f>
         <v>0</v>
       </c>
       <c r="E235" s="2">
@@ -5777,11 +5777,11 @@
         <v>0.0</v>
       </c>
       <c r="C236" s="2">
-        <f>IF(B236&gt;0,ROUND(B236*$B$5/12,2),0)</f>
+        <f>IF(B236&gt;0.005,ROUND(B236*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D236" s="2">
-        <f>IF(B236&gt;0,MIN($B$6+$B$7,B236+C236),0)</f>
+        <f>IF(B236&gt;0.005,MIN($B$6+$B$7,B236+C236),0)</f>
         <v>0</v>
       </c>
       <c r="E236" s="2">
@@ -5802,11 +5802,11 @@
         <v>0.0</v>
       </c>
       <c r="C237" s="2">
-        <f>IF(B237&gt;0,ROUND(B237*$B$5/12,2),0)</f>
+        <f>IF(B237&gt;0.005,ROUND(B237*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D237" s="2">
-        <f>IF(B237&gt;0,MIN($B$6+$B$7,B237+C237),0)</f>
+        <f>IF(B237&gt;0.005,MIN($B$6+$B$7,B237+C237),0)</f>
         <v>0</v>
       </c>
       <c r="E237" s="2">
@@ -5827,11 +5827,11 @@
         <v>0.0</v>
       </c>
       <c r="C238" s="2">
-        <f>IF(B238&gt;0,ROUND(B238*$B$5/12,2),0)</f>
+        <f>IF(B238&gt;0.005,ROUND(B238*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D238" s="2">
-        <f>IF(B238&gt;0,MIN($B$6+$B$7,B238+C238),0)</f>
+        <f>IF(B238&gt;0.005,MIN($B$6+$B$7,B238+C238),0)</f>
         <v>0</v>
       </c>
       <c r="E238" s="2">
@@ -5852,11 +5852,11 @@
         <v>0.0</v>
       </c>
       <c r="C239" s="2">
-        <f>IF(B239&gt;0,ROUND(B239*$B$5/12,2),0)</f>
+        <f>IF(B239&gt;0.005,ROUND(B239*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D239" s="2">
-        <f>IF(B239&gt;0,MIN($B$6+$B$7,B239+C239),0)</f>
+        <f>IF(B239&gt;0.005,MIN($B$6+$B$7,B239+C239),0)</f>
         <v>0</v>
       </c>
       <c r="E239" s="2">
@@ -5877,11 +5877,11 @@
         <v>0.0</v>
       </c>
       <c r="C240" s="2">
-        <f>IF(B240&gt;0,ROUND(B240*$B$5/12,2),0)</f>
+        <f>IF(B240&gt;0.005,ROUND(B240*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D240" s="2">
-        <f>IF(B240&gt;0,MIN($B$6+$B$7,B240+C240),0)</f>
+        <f>IF(B240&gt;0.005,MIN($B$6+$B$7,B240+C240),0)</f>
         <v>0</v>
       </c>
       <c r="E240" s="2">
@@ -5902,11 +5902,11 @@
         <v>0.0</v>
       </c>
       <c r="C241" s="2">
-        <f>IF(B241&gt;0,ROUND(B241*$B$5/12,2),0)</f>
+        <f>IF(B241&gt;0.005,ROUND(B241*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D241" s="2">
-        <f>IF(B241&gt;0,MIN($B$6+$B$7,B241+C241),0)</f>
+        <f>IF(B241&gt;0.005,MIN($B$6+$B$7,B241+C241),0)</f>
         <v>0</v>
       </c>
       <c r="E241" s="2">
@@ -5927,11 +5927,11 @@
         <v>0.0</v>
       </c>
       <c r="C242" s="2">
-        <f>IF(B242&gt;0,ROUND(B242*$B$5/12,2),0)</f>
+        <f>IF(B242&gt;0.005,ROUND(B242*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D242" s="2">
-        <f>IF(B242&gt;0,MIN($B$6+$B$7,B242+C242),0)</f>
+        <f>IF(B242&gt;0.005,MIN($B$6+$B$7,B242+C242),0)</f>
         <v>0</v>
       </c>
       <c r="E242" s="2">
@@ -5952,11 +5952,11 @@
         <v>0.0</v>
       </c>
       <c r="C243" s="2">
-        <f>IF(B243&gt;0,ROUND(B243*$B$5/12,2),0)</f>
+        <f>IF(B243&gt;0.005,ROUND(B243*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D243" s="2">
-        <f>IF(B243&gt;0,MIN($B$6+$B$7,B243+C243),0)</f>
+        <f>IF(B243&gt;0.005,MIN($B$6+$B$7,B243+C243),0)</f>
         <v>0</v>
       </c>
       <c r="E243" s="2">
@@ -5977,11 +5977,11 @@
         <v>0.0</v>
       </c>
       <c r="C244" s="2">
-        <f>IF(B244&gt;0,ROUND(B244*$B$5/12,2),0)</f>
+        <f>IF(B244&gt;0.005,ROUND(B244*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D244" s="2">
-        <f>IF(B244&gt;0,MIN($B$6+$B$7,B244+C244),0)</f>
+        <f>IF(B244&gt;0.005,MIN($B$6+$B$7,B244+C244),0)</f>
         <v>0</v>
       </c>
       <c r="E244" s="2">
@@ -6002,11 +6002,11 @@
         <v>0.0</v>
       </c>
       <c r="C245" s="2">
-        <f>IF(B245&gt;0,ROUND(B245*$B$5/12,2),0)</f>
+        <f>IF(B245&gt;0.005,ROUND(B245*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D245" s="2">
-        <f>IF(B245&gt;0,MIN($B$6+$B$7,B245+C245),0)</f>
+        <f>IF(B245&gt;0.005,MIN($B$6+$B$7,B245+C245),0)</f>
         <v>0</v>
       </c>
       <c r="E245" s="2">
@@ -6027,11 +6027,11 @@
         <v>0.0</v>
       </c>
       <c r="C246" s="2">
-        <f>IF(B246&gt;0,ROUND(B246*$B$5/12,2),0)</f>
+        <f>IF(B246&gt;0.005,ROUND(B246*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D246" s="2">
-        <f>IF(B246&gt;0,MIN($B$6+$B$7,B246+C246),0)</f>
+        <f>IF(B246&gt;0.005,MIN($B$6+$B$7,B246+C246),0)</f>
         <v>0</v>
       </c>
       <c r="E246" s="2">
@@ -6052,11 +6052,11 @@
         <v>0.0</v>
       </c>
       <c r="C247" s="2">
-        <f>IF(B247&gt;0,ROUND(B247*$B$5/12,2),0)</f>
+        <f>IF(B247&gt;0.005,ROUND(B247*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D247" s="2">
-        <f>IF(B247&gt;0,MIN($B$6+$B$7,B247+C247),0)</f>
+        <f>IF(B247&gt;0.005,MIN($B$6+$B$7,B247+C247),0)</f>
         <v>0</v>
       </c>
       <c r="E247" s="2">
@@ -6077,11 +6077,11 @@
         <v>0.0</v>
       </c>
       <c r="C248" s="2">
-        <f>IF(B248&gt;0,ROUND(B248*$B$5/12,2),0)</f>
+        <f>IF(B248&gt;0.005,ROUND(B248*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D248" s="2">
-        <f>IF(B248&gt;0,MIN($B$6+$B$7,B248+C248),0)</f>
+        <f>IF(B248&gt;0.005,MIN($B$6+$B$7,B248+C248),0)</f>
         <v>0</v>
       </c>
       <c r="E248" s="2">
@@ -6102,11 +6102,11 @@
         <v>0.0</v>
       </c>
       <c r="C249" s="2">
-        <f>IF(B249&gt;0,ROUND(B249*$B$5/12,2),0)</f>
+        <f>IF(B249&gt;0.005,ROUND(B249*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D249" s="2">
-        <f>IF(B249&gt;0,MIN($B$6+$B$7,B249+C249),0)</f>
+        <f>IF(B249&gt;0.005,MIN($B$6+$B$7,B249+C249),0)</f>
         <v>0</v>
       </c>
       <c r="E249" s="2">
@@ -6127,11 +6127,11 @@
         <v>0.0</v>
       </c>
       <c r="C250" s="2">
-        <f>IF(B250&gt;0,ROUND(B250*$B$5/12,2),0)</f>
+        <f>IF(B250&gt;0.005,ROUND(B250*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D250" s="2">
-        <f>IF(B250&gt;0,MIN($B$6+$B$7,B250+C250),0)</f>
+        <f>IF(B250&gt;0.005,MIN($B$6+$B$7,B250+C250),0)</f>
         <v>0</v>
       </c>
       <c r="E250" s="2">
@@ -6152,11 +6152,11 @@
         <v>0.0</v>
       </c>
       <c r="C251" s="2">
-        <f>IF(B251&gt;0,ROUND(B251*$B$5/12,2),0)</f>
+        <f>IF(B251&gt;0.005,ROUND(B251*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D251" s="2">
-        <f>IF(B251&gt;0,MIN($B$6+$B$7,B251+C251),0)</f>
+        <f>IF(B251&gt;0.005,MIN($B$6+$B$7,B251+C251),0)</f>
         <v>0</v>
       </c>
       <c r="E251" s="2">
@@ -6177,11 +6177,11 @@
         <v>0.0</v>
       </c>
       <c r="C252" s="2">
-        <f>IF(B252&gt;0,ROUND(B252*$B$5/12,2),0)</f>
+        <f>IF(B252&gt;0.005,ROUND(B252*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D252" s="2">
-        <f>IF(B252&gt;0,MIN($B$6+$B$7,B252+C252),0)</f>
+        <f>IF(B252&gt;0.005,MIN($B$6+$B$7,B252+C252),0)</f>
         <v>0</v>
       </c>
       <c r="E252" s="2">
@@ -6202,11 +6202,11 @@
         <v>0.0</v>
       </c>
       <c r="C253" s="2">
-        <f>IF(B253&gt;0,ROUND(B253*$B$5/12,2),0)</f>
+        <f>IF(B253&gt;0.005,ROUND(B253*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D253" s="2">
-        <f>IF(B253&gt;0,MIN($B$6+$B$7,B253+C253),0)</f>
+        <f>IF(B253&gt;0.005,MIN($B$6+$B$7,B253+C253),0)</f>
         <v>0</v>
       </c>
       <c r="E253" s="2">
@@ -6227,11 +6227,11 @@
         <v>0.0</v>
       </c>
       <c r="C254" s="2">
-        <f>IF(B254&gt;0,ROUND(B254*$B$5/12,2),0)</f>
+        <f>IF(B254&gt;0.005,ROUND(B254*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D254" s="2">
-        <f>IF(B254&gt;0,MIN($B$6+$B$7,B254+C254),0)</f>
+        <f>IF(B254&gt;0.005,MIN($B$6+$B$7,B254+C254),0)</f>
         <v>0</v>
       </c>
       <c r="E254" s="2">
@@ -6252,11 +6252,11 @@
         <v>0.0</v>
       </c>
       <c r="C255" s="2">
-        <f>IF(B255&gt;0,ROUND(B255*$B$5/12,2),0)</f>
+        <f>IF(B255&gt;0.005,ROUND(B255*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D255" s="2">
-        <f>IF(B255&gt;0,MIN($B$6+$B$7,B255+C255),0)</f>
+        <f>IF(B255&gt;0.005,MIN($B$6+$B$7,B255+C255),0)</f>
         <v>0</v>
       </c>
       <c r="E255" s="2">
@@ -6277,11 +6277,11 @@
         <v>0.0</v>
       </c>
       <c r="C256" s="2">
-        <f>IF(B256&gt;0,ROUND(B256*$B$5/12,2),0)</f>
+        <f>IF(B256&gt;0.005,ROUND(B256*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D256" s="2">
-        <f>IF(B256&gt;0,MIN($B$6+$B$7,B256+C256),0)</f>
+        <f>IF(B256&gt;0.005,MIN($B$6+$B$7,B256+C256),0)</f>
         <v>0</v>
       </c>
       <c r="E256" s="2">
@@ -6302,11 +6302,11 @@
         <v>0.0</v>
       </c>
       <c r="C257" s="2">
-        <f>IF(B257&gt;0,ROUND(B257*$B$5/12,2),0)</f>
+        <f>IF(B257&gt;0.005,ROUND(B257*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D257" s="2">
-        <f>IF(B257&gt;0,MIN($B$6+$B$7,B257+C257),0)</f>
+        <f>IF(B257&gt;0.005,MIN($B$6+$B$7,B257+C257),0)</f>
         <v>0</v>
       </c>
       <c r="E257" s="2">
@@ -6327,11 +6327,11 @@
         <v>0.0</v>
       </c>
       <c r="C258" s="2">
-        <f>IF(B258&gt;0,ROUND(B258*$B$5/12,2),0)</f>
+        <f>IF(B258&gt;0.005,ROUND(B258*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D258" s="2">
-        <f>IF(B258&gt;0,MIN($B$6+$B$7,B258+C258),0)</f>
+        <f>IF(B258&gt;0.005,MIN($B$6+$B$7,B258+C258),0)</f>
         <v>0</v>
       </c>
       <c r="E258" s="2">
@@ -6352,11 +6352,11 @@
         <v>0.0</v>
       </c>
       <c r="C259" s="2">
-        <f>IF(B259&gt;0,ROUND(B259*$B$5/12,2),0)</f>
+        <f>IF(B259&gt;0.005,ROUND(B259*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D259" s="2">
-        <f>IF(B259&gt;0,MIN($B$6+$B$7,B259+C259),0)</f>
+        <f>IF(B259&gt;0.005,MIN($B$6+$B$7,B259+C259),0)</f>
         <v>0</v>
       </c>
       <c r="E259" s="2">
@@ -6377,11 +6377,11 @@
         <v>0.0</v>
       </c>
       <c r="C260" s="2">
-        <f>IF(B260&gt;0,ROUND(B260*$B$5/12,2),0)</f>
+        <f>IF(B260&gt;0.005,ROUND(B260*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D260" s="2">
-        <f>IF(B260&gt;0,MIN($B$6+$B$7,B260+C260),0)</f>
+        <f>IF(B260&gt;0.005,MIN($B$6+$B$7,B260+C260),0)</f>
         <v>0</v>
       </c>
       <c r="E260" s="2">
@@ -6402,11 +6402,11 @@
         <v>0.0</v>
       </c>
       <c r="C261" s="2">
-        <f>IF(B261&gt;0,ROUND(B261*$B$5/12,2),0)</f>
+        <f>IF(B261&gt;0.005,ROUND(B261*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D261" s="2">
-        <f>IF(B261&gt;0,MIN($B$6+$B$7,B261+C261),0)</f>
+        <f>IF(B261&gt;0.005,MIN($B$6+$B$7,B261+C261),0)</f>
         <v>0</v>
       </c>
       <c r="E261" s="2">
@@ -6427,11 +6427,11 @@
         <v>0.0</v>
       </c>
       <c r="C262" s="2">
-        <f>IF(B262&gt;0,ROUND(B262*$B$5/12,2),0)</f>
+        <f>IF(B262&gt;0.005,ROUND(B262*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D262" s="2">
-        <f>IF(B262&gt;0,MIN($B$6+$B$7,B262+C262),0)</f>
+        <f>IF(B262&gt;0.005,MIN($B$6+$B$7,B262+C262),0)</f>
         <v>0</v>
       </c>
       <c r="E262" s="2">
@@ -6452,11 +6452,11 @@
         <v>0.0</v>
       </c>
       <c r="C263" s="2">
-        <f>IF(B263&gt;0,ROUND(B263*$B$5/12,2),0)</f>
+        <f>IF(B263&gt;0.005,ROUND(B263*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D263" s="2">
-        <f>IF(B263&gt;0,MIN($B$6+$B$7,B263+C263),0)</f>
+        <f>IF(B263&gt;0.005,MIN($B$6+$B$7,B263+C263),0)</f>
         <v>0</v>
       </c>
       <c r="E263" s="2">
@@ -6477,11 +6477,11 @@
         <v>0.0</v>
       </c>
       <c r="C264" s="2">
-        <f>IF(B264&gt;0,ROUND(B264*$B$5/12,2),0)</f>
+        <f>IF(B264&gt;0.005,ROUND(B264*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D264" s="2">
-        <f>IF(B264&gt;0,MIN($B$6+$B$7,B264+C264),0)</f>
+        <f>IF(B264&gt;0.005,MIN($B$6+$B$7,B264+C264),0)</f>
         <v>0</v>
       </c>
       <c r="E264" s="2">
@@ -6502,11 +6502,11 @@
         <v>0.0</v>
       </c>
       <c r="C265" s="2">
-        <f>IF(B265&gt;0,ROUND(B265*$B$5/12,2),0)</f>
+        <f>IF(B265&gt;0.005,ROUND(B265*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D265" s="2">
-        <f>IF(B265&gt;0,MIN($B$6+$B$7,B265+C265),0)</f>
+        <f>IF(B265&gt;0.005,MIN($B$6+$B$7,B265+C265),0)</f>
         <v>0</v>
       </c>
       <c r="E265" s="2">
@@ -6527,11 +6527,11 @@
         <v>0.0</v>
       </c>
       <c r="C266" s="2">
-        <f>IF(B266&gt;0,ROUND(B266*$B$5/12,2),0)</f>
+        <f>IF(B266&gt;0.005,ROUND(B266*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D266" s="2">
-        <f>IF(B266&gt;0,MIN($B$6+$B$7,B266+C266),0)</f>
+        <f>IF(B266&gt;0.005,MIN($B$6+$B$7,B266+C266),0)</f>
         <v>0</v>
       </c>
       <c r="E266" s="2">
@@ -6552,11 +6552,11 @@
         <v>0.0</v>
       </c>
       <c r="C267" s="2">
-        <f>IF(B267&gt;0,ROUND(B267*$B$5/12,2),0)</f>
+        <f>IF(B267&gt;0.005,ROUND(B267*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D267" s="2">
-        <f>IF(B267&gt;0,MIN($B$6+$B$7,B267+C267),0)</f>
+        <f>IF(B267&gt;0.005,MIN($B$6+$B$7,B267+C267),0)</f>
         <v>0</v>
       </c>
       <c r="E267" s="2">
@@ -6577,11 +6577,11 @@
         <v>0.0</v>
       </c>
       <c r="C268" s="2">
-        <f>IF(B268&gt;0,ROUND(B268*$B$5/12,2),0)</f>
+        <f>IF(B268&gt;0.005,ROUND(B268*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D268" s="2">
-        <f>IF(B268&gt;0,MIN($B$6+$B$7,B268+C268),0)</f>
+        <f>IF(B268&gt;0.005,MIN($B$6+$B$7,B268+C268),0)</f>
         <v>0</v>
       </c>
       <c r="E268" s="2">
@@ -6602,11 +6602,11 @@
         <v>0.0</v>
       </c>
       <c r="C269" s="2">
-        <f>IF(B269&gt;0,ROUND(B269*$B$5/12,2),0)</f>
+        <f>IF(B269&gt;0.005,ROUND(B269*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D269" s="2">
-        <f>IF(B269&gt;0,MIN($B$6+$B$7,B269+C269),0)</f>
+        <f>IF(B269&gt;0.005,MIN($B$6+$B$7,B269+C269),0)</f>
         <v>0</v>
       </c>
       <c r="E269" s="2">
@@ -6627,11 +6627,11 @@
         <v>0.0</v>
       </c>
       <c r="C270" s="2">
-        <f>IF(B270&gt;0,ROUND(B270*$B$5/12,2),0)</f>
+        <f>IF(B270&gt;0.005,ROUND(B270*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D270" s="2">
-        <f>IF(B270&gt;0,MIN($B$6+$B$7,B270+C270),0)</f>
+        <f>IF(B270&gt;0.005,MIN($B$6+$B$7,B270+C270),0)</f>
         <v>0</v>
       </c>
       <c r="E270" s="2">
@@ -6652,11 +6652,11 @@
         <v>0.0</v>
       </c>
       <c r="C271" s="2">
-        <f>IF(B271&gt;0,ROUND(B271*$B$5/12,2),0)</f>
+        <f>IF(B271&gt;0.005,ROUND(B271*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D271" s="2">
-        <f>IF(B271&gt;0,MIN($B$6+$B$7,B271+C271),0)</f>
+        <f>IF(B271&gt;0.005,MIN($B$6+$B$7,B271+C271),0)</f>
         <v>0</v>
       </c>
       <c r="E271" s="2">
@@ -6677,11 +6677,11 @@
         <v>0.0</v>
       </c>
       <c r="C272" s="2">
-        <f>IF(B272&gt;0,ROUND(B272*$B$5/12,2),0)</f>
+        <f>IF(B272&gt;0.005,ROUND(B272*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D272" s="2">
-        <f>IF(B272&gt;0,MIN($B$6+$B$7,B272+C272),0)</f>
+        <f>IF(B272&gt;0.005,MIN($B$6+$B$7,B272+C272),0)</f>
         <v>0</v>
       </c>
       <c r="E272" s="2">
@@ -6702,11 +6702,11 @@
         <v>0.0</v>
       </c>
       <c r="C273" s="2">
-        <f>IF(B273&gt;0,ROUND(B273*$B$5/12,2),0)</f>
+        <f>IF(B273&gt;0.005,ROUND(B273*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D273" s="2">
-        <f>IF(B273&gt;0,MIN($B$6+$B$7,B273+C273),0)</f>
+        <f>IF(B273&gt;0.005,MIN($B$6+$B$7,B273+C273),0)</f>
         <v>0</v>
       </c>
       <c r="E273" s="2">
@@ -6727,11 +6727,11 @@
         <v>0.0</v>
       </c>
       <c r="C274" s="2">
-        <f>IF(B274&gt;0,ROUND(B274*$B$5/12,2),0)</f>
+        <f>IF(B274&gt;0.005,ROUND(B274*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D274" s="2">
-        <f>IF(B274&gt;0,MIN($B$6+$B$7,B274+C274),0)</f>
+        <f>IF(B274&gt;0.005,MIN($B$6+$B$7,B274+C274),0)</f>
         <v>0</v>
       </c>
       <c r="E274" s="2">
@@ -6752,11 +6752,11 @@
         <v>0.0</v>
       </c>
       <c r="C275" s="2">
-        <f>IF(B275&gt;0,ROUND(B275*$B$5/12,2),0)</f>
+        <f>IF(B275&gt;0.005,ROUND(B275*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D275" s="2">
-        <f>IF(B275&gt;0,MIN($B$6+$B$7,B275+C275),0)</f>
+        <f>IF(B275&gt;0.005,MIN($B$6+$B$7,B275+C275),0)</f>
         <v>0</v>
       </c>
       <c r="E275" s="2">
@@ -6777,11 +6777,11 @@
         <v>0.0</v>
       </c>
       <c r="C276" s="2">
-        <f>IF(B276&gt;0,ROUND(B276*$B$5/12,2),0)</f>
+        <f>IF(B276&gt;0.005,ROUND(B276*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D276" s="2">
-        <f>IF(B276&gt;0,MIN($B$6+$B$7,B276+C276),0)</f>
+        <f>IF(B276&gt;0.005,MIN($B$6+$B$7,B276+C276),0)</f>
         <v>0</v>
       </c>
       <c r="E276" s="2">
@@ -6802,11 +6802,11 @@
         <v>0.0</v>
       </c>
       <c r="C277" s="2">
-        <f>IF(B277&gt;0,ROUND(B277*$B$5/12,2),0)</f>
+        <f>IF(B277&gt;0.005,ROUND(B277*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D277" s="2">
-        <f>IF(B277&gt;0,MIN($B$6+$B$7,B277+C277),0)</f>
+        <f>IF(B277&gt;0.005,MIN($B$6+$B$7,B277+C277),0)</f>
         <v>0</v>
       </c>
       <c r="E277" s="2">
@@ -6827,11 +6827,11 @@
         <v>0.0</v>
       </c>
       <c r="C278" s="2">
-        <f>IF(B278&gt;0,ROUND(B278*$B$5/12,2),0)</f>
+        <f>IF(B278&gt;0.005,ROUND(B278*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D278" s="2">
-        <f>IF(B278&gt;0,MIN($B$6+$B$7,B278+C278),0)</f>
+        <f>IF(B278&gt;0.005,MIN($B$6+$B$7,B278+C278),0)</f>
         <v>0</v>
       </c>
       <c r="E278" s="2">
@@ -6852,11 +6852,11 @@
         <v>0.0</v>
       </c>
       <c r="C279" s="2">
-        <f>IF(B279&gt;0,ROUND(B279*$B$5/12,2),0)</f>
+        <f>IF(B279&gt;0.005,ROUND(B279*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D279" s="2">
-        <f>IF(B279&gt;0,MIN($B$6+$B$7,B279+C279),0)</f>
+        <f>IF(B279&gt;0.005,MIN($B$6+$B$7,B279+C279),0)</f>
         <v>0</v>
       </c>
       <c r="E279" s="2">
@@ -6877,11 +6877,11 @@
         <v>0.0</v>
       </c>
       <c r="C280" s="2">
-        <f>IF(B280&gt;0,ROUND(B280*$B$5/12,2),0)</f>
+        <f>IF(B280&gt;0.005,ROUND(B280*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D280" s="2">
-        <f>IF(B280&gt;0,MIN($B$6+$B$7,B280+C280),0)</f>
+        <f>IF(B280&gt;0.005,MIN($B$6+$B$7,B280+C280),0)</f>
         <v>0</v>
       </c>
       <c r="E280" s="2">
@@ -6902,11 +6902,11 @@
         <v>0.0</v>
       </c>
       <c r="C281" s="2">
-        <f>IF(B281&gt;0,ROUND(B281*$B$5/12,2),0)</f>
+        <f>IF(B281&gt;0.005,ROUND(B281*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D281" s="2">
-        <f>IF(B281&gt;0,MIN($B$6+$B$7,B281+C281),0)</f>
+        <f>IF(B281&gt;0.005,MIN($B$6+$B$7,B281+C281),0)</f>
         <v>0</v>
       </c>
       <c r="E281" s="2">
@@ -6927,11 +6927,11 @@
         <v>0.0</v>
       </c>
       <c r="C282" s="2">
-        <f>IF(B282&gt;0,ROUND(B282*$B$5/12,2),0)</f>
+        <f>IF(B282&gt;0.005,ROUND(B282*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D282" s="2">
-        <f>IF(B282&gt;0,MIN($B$6+$B$7,B282+C282),0)</f>
+        <f>IF(B282&gt;0.005,MIN($B$6+$B$7,B282+C282),0)</f>
         <v>0</v>
       </c>
       <c r="E282" s="2">
@@ -6952,11 +6952,11 @@
         <v>0.0</v>
       </c>
       <c r="C283" s="2">
-        <f>IF(B283&gt;0,ROUND(B283*$B$5/12,2),0)</f>
+        <f>IF(B283&gt;0.005,ROUND(B283*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D283" s="2">
-        <f>IF(B283&gt;0,MIN($B$6+$B$7,B283+C283),0)</f>
+        <f>IF(B283&gt;0.005,MIN($B$6+$B$7,B283+C283),0)</f>
         <v>0</v>
       </c>
       <c r="E283" s="2">
@@ -6977,11 +6977,11 @@
         <v>0.0</v>
       </c>
       <c r="C284" s="2">
-        <f>IF(B284&gt;0,ROUND(B284*$B$5/12,2),0)</f>
+        <f>IF(B284&gt;0.005,ROUND(B284*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D284" s="2">
-        <f>IF(B284&gt;0,MIN($B$6+$B$7,B284+C284),0)</f>
+        <f>IF(B284&gt;0.005,MIN($B$6+$B$7,B284+C284),0)</f>
         <v>0</v>
       </c>
       <c r="E284" s="2">
@@ -7002,11 +7002,11 @@
         <v>0.0</v>
       </c>
       <c r="C285" s="2">
-        <f>IF(B285&gt;0,ROUND(B285*$B$5/12,2),0)</f>
+        <f>IF(B285&gt;0.005,ROUND(B285*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D285" s="2">
-        <f>IF(B285&gt;0,MIN($B$6+$B$7,B285+C285),0)</f>
+        <f>IF(B285&gt;0.005,MIN($B$6+$B$7,B285+C285),0)</f>
         <v>0</v>
       </c>
       <c r="E285" s="2">
@@ -7027,11 +7027,11 @@
         <v>0.0</v>
       </c>
       <c r="C286" s="2">
-        <f>IF(B286&gt;0,ROUND(B286*$B$5/12,2),0)</f>
+        <f>IF(B286&gt;0.005,ROUND(B286*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D286" s="2">
-        <f>IF(B286&gt;0,MIN($B$6+$B$7,B286+C286),0)</f>
+        <f>IF(B286&gt;0.005,MIN($B$6+$B$7,B286+C286),0)</f>
         <v>0</v>
       </c>
       <c r="E286" s="2">
@@ -7052,11 +7052,11 @@
         <v>0.0</v>
       </c>
       <c r="C287" s="2">
-        <f>IF(B287&gt;0,ROUND(B287*$B$5/12,2),0)</f>
+        <f>IF(B287&gt;0.005,ROUND(B287*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D287" s="2">
-        <f>IF(B287&gt;0,MIN($B$6+$B$7,B287+C287),0)</f>
+        <f>IF(B287&gt;0.005,MIN($B$6+$B$7,B287+C287),0)</f>
         <v>0</v>
       </c>
       <c r="E287" s="2">
@@ -7077,11 +7077,11 @@
         <v>0.0</v>
       </c>
       <c r="C288" s="2">
-        <f>IF(B288&gt;0,ROUND(B288*$B$5/12,2),0)</f>
+        <f>IF(B288&gt;0.005,ROUND(B288*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D288" s="2">
-        <f>IF(B288&gt;0,MIN($B$6+$B$7,B288+C288),0)</f>
+        <f>IF(B288&gt;0.005,MIN($B$6+$B$7,B288+C288),0)</f>
         <v>0</v>
       </c>
       <c r="E288" s="2">
@@ -7102,11 +7102,11 @@
         <v>0.0</v>
       </c>
       <c r="C289" s="2">
-        <f>IF(B289&gt;0,ROUND(B289*$B$5/12,2),0)</f>
+        <f>IF(B289&gt;0.005,ROUND(B289*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D289" s="2">
-        <f>IF(B289&gt;0,MIN($B$6+$B$7,B289+C289),0)</f>
+        <f>IF(B289&gt;0.005,MIN($B$6+$B$7,B289+C289),0)</f>
         <v>0</v>
       </c>
       <c r="E289" s="2">
@@ -7127,11 +7127,11 @@
         <v>0.0</v>
       </c>
       <c r="C290" s="2">
-        <f>IF(B290&gt;0,ROUND(B290*$B$5/12,2),0)</f>
+        <f>IF(B290&gt;0.005,ROUND(B290*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D290" s="2">
-        <f>IF(B290&gt;0,MIN($B$6+$B$7,B290+C290),0)</f>
+        <f>IF(B290&gt;0.005,MIN($B$6+$B$7,B290+C290),0)</f>
         <v>0</v>
       </c>
       <c r="E290" s="2">
@@ -7152,11 +7152,11 @@
         <v>0.0</v>
       </c>
       <c r="C291" s="2">
-        <f>IF(B291&gt;0,ROUND(B291*$B$5/12,2),0)</f>
+        <f>IF(B291&gt;0.005,ROUND(B291*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D291" s="2">
-        <f>IF(B291&gt;0,MIN($B$6+$B$7,B291+C291),0)</f>
+        <f>IF(B291&gt;0.005,MIN($B$6+$B$7,B291+C291),0)</f>
         <v>0</v>
       </c>
       <c r="E291" s="2">
@@ -7177,11 +7177,11 @@
         <v>0.0</v>
       </c>
       <c r="C292" s="2">
-        <f>IF(B292&gt;0,ROUND(B292*$B$5/12,2),0)</f>
+        <f>IF(B292&gt;0.005,ROUND(B292*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D292" s="2">
-        <f>IF(B292&gt;0,MIN($B$6+$B$7,B292+C292),0)</f>
+        <f>IF(B292&gt;0.005,MIN($B$6+$B$7,B292+C292),0)</f>
         <v>0</v>
       </c>
       <c r="E292" s="2">
@@ -7202,11 +7202,11 @@
         <v>0.0</v>
       </c>
       <c r="C293" s="2">
-        <f>IF(B293&gt;0,ROUND(B293*$B$5/12,2),0)</f>
+        <f>IF(B293&gt;0.005,ROUND(B293*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D293" s="2">
-        <f>IF(B293&gt;0,MIN($B$6+$B$7,B293+C293),0)</f>
+        <f>IF(B293&gt;0.005,MIN($B$6+$B$7,B293+C293),0)</f>
         <v>0</v>
       </c>
       <c r="E293" s="2">
@@ -7227,11 +7227,11 @@
         <v>0.0</v>
       </c>
       <c r="C294" s="2">
-        <f>IF(B294&gt;0,ROUND(B294*$B$5/12,2),0)</f>
+        <f>IF(B294&gt;0.005,ROUND(B294*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D294" s="2">
-        <f>IF(B294&gt;0,MIN($B$6+$B$7,B294+C294),0)</f>
+        <f>IF(B294&gt;0.005,MIN($B$6+$B$7,B294+C294),0)</f>
         <v>0</v>
       </c>
       <c r="E294" s="2">
@@ -7252,11 +7252,11 @@
         <v>0.0</v>
       </c>
       <c r="C295" s="2">
-        <f>IF(B295&gt;0,ROUND(B295*$B$5/12,2),0)</f>
+        <f>IF(B295&gt;0.005,ROUND(B295*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D295" s="2">
-        <f>IF(B295&gt;0,MIN($B$6+$B$7,B295+C295),0)</f>
+        <f>IF(B295&gt;0.005,MIN($B$6+$B$7,B295+C295),0)</f>
         <v>0</v>
       </c>
       <c r="E295" s="2">
@@ -7277,11 +7277,11 @@
         <v>0.0</v>
       </c>
       <c r="C296" s="2">
-        <f>IF(B296&gt;0,ROUND(B296*$B$5/12,2),0)</f>
+        <f>IF(B296&gt;0.005,ROUND(B296*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D296" s="2">
-        <f>IF(B296&gt;0,MIN($B$6+$B$7,B296+C296),0)</f>
+        <f>IF(B296&gt;0.005,MIN($B$6+$B$7,B296+C296),0)</f>
         <v>0</v>
       </c>
       <c r="E296" s="2">
@@ -7302,11 +7302,11 @@
         <v>0.0</v>
       </c>
       <c r="C297" s="2">
-        <f>IF(B297&gt;0,ROUND(B297*$B$5/12,2),0)</f>
+        <f>IF(B297&gt;0.005,ROUND(B297*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D297" s="2">
-        <f>IF(B297&gt;0,MIN($B$6+$B$7,B297+C297),0)</f>
+        <f>IF(B297&gt;0.005,MIN($B$6+$B$7,B297+C297),0)</f>
         <v>0</v>
       </c>
       <c r="E297" s="2">
@@ -7327,11 +7327,11 @@
         <v>0.0</v>
       </c>
       <c r="C298" s="2">
-        <f>IF(B298&gt;0,ROUND(B298*$B$5/12,2),0)</f>
+        <f>IF(B298&gt;0.005,ROUND(B298*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D298" s="2">
-        <f>IF(B298&gt;0,MIN($B$6+$B$7,B298+C298),0)</f>
+        <f>IF(B298&gt;0.005,MIN($B$6+$B$7,B298+C298),0)</f>
         <v>0</v>
       </c>
       <c r="E298" s="2">
@@ -7352,11 +7352,11 @@
         <v>0.0</v>
       </c>
       <c r="C299" s="2">
-        <f>IF(B299&gt;0,ROUND(B299*$B$5/12,2),0)</f>
+        <f>IF(B299&gt;0.005,ROUND(B299*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D299" s="2">
-        <f>IF(B299&gt;0,MIN($B$6+$B$7,B299+C299),0)</f>
+        <f>IF(B299&gt;0.005,MIN($B$6+$B$7,B299+C299),0)</f>
         <v>0</v>
       </c>
       <c r="E299" s="2">
@@ -7377,11 +7377,11 @@
         <v>0.0</v>
       </c>
       <c r="C300" s="2">
-        <f>IF(B300&gt;0,ROUND(B300*$B$5/12,2),0)</f>
+        <f>IF(B300&gt;0.005,ROUND(B300*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D300" s="2">
-        <f>IF(B300&gt;0,MIN($B$6+$B$7,B300+C300),0)</f>
+        <f>IF(B300&gt;0.005,MIN($B$6+$B$7,B300+C300),0)</f>
         <v>0</v>
       </c>
       <c r="E300" s="2">
@@ -7402,11 +7402,11 @@
         <v>0.0</v>
       </c>
       <c r="C301" s="2">
-        <f>IF(B301&gt;0,ROUND(B301*$B$5/12,2),0)</f>
+        <f>IF(B301&gt;0.005,ROUND(B301*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D301" s="2">
-        <f>IF(B301&gt;0,MIN($B$6+$B$7,B301+C301),0)</f>
+        <f>IF(B301&gt;0.005,MIN($B$6+$B$7,B301+C301),0)</f>
         <v>0</v>
       </c>
       <c r="E301" s="2">
@@ -7427,11 +7427,11 @@
         <v>0.0</v>
       </c>
       <c r="C302" s="2">
-        <f>IF(B302&gt;0,ROUND(B302*$B$5/12,2),0)</f>
+        <f>IF(B302&gt;0.005,ROUND(B302*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D302" s="2">
-        <f>IF(B302&gt;0,MIN($B$6+$B$7,B302+C302),0)</f>
+        <f>IF(B302&gt;0.005,MIN($B$6+$B$7,B302+C302),0)</f>
         <v>0</v>
       </c>
       <c r="E302" s="2">
@@ -7452,11 +7452,11 @@
         <v>0.0</v>
       </c>
       <c r="C303" s="2">
-        <f>IF(B303&gt;0,ROUND(B303*$B$5/12,2),0)</f>
+        <f>IF(B303&gt;0.005,ROUND(B303*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D303" s="2">
-        <f>IF(B303&gt;0,MIN($B$6+$B$7,B303+C303),0)</f>
+        <f>IF(B303&gt;0.005,MIN($B$6+$B$7,B303+C303),0)</f>
         <v>0</v>
       </c>
       <c r="E303" s="2">
@@ -7477,11 +7477,11 @@
         <v>0.0</v>
       </c>
       <c r="C304" s="2">
-        <f>IF(B304&gt;0,ROUND(B304*$B$5/12,2),0)</f>
+        <f>IF(B304&gt;0.005,ROUND(B304*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D304" s="2">
-        <f>IF(B304&gt;0,MIN($B$6+$B$7,B304+C304),0)</f>
+        <f>IF(B304&gt;0.005,MIN($B$6+$B$7,B304+C304),0)</f>
         <v>0</v>
       </c>
       <c r="E304" s="2">
@@ -7502,11 +7502,11 @@
         <v>0.0</v>
       </c>
       <c r="C305" s="2">
-        <f>IF(B305&gt;0,ROUND(B305*$B$5/12,2),0)</f>
+        <f>IF(B305&gt;0.005,ROUND(B305*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D305" s="2">
-        <f>IF(B305&gt;0,MIN($B$6+$B$7,B305+C305),0)</f>
+        <f>IF(B305&gt;0.005,MIN($B$6+$B$7,B305+C305),0)</f>
         <v>0</v>
       </c>
       <c r="E305" s="2">
@@ -7527,11 +7527,11 @@
         <v>0.0</v>
       </c>
       <c r="C306" s="2">
-        <f>IF(B306&gt;0,ROUND(B306*$B$5/12,2),0)</f>
+        <f>IF(B306&gt;0.005,ROUND(B306*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D306" s="2">
-        <f>IF(B306&gt;0,MIN($B$6+$B$7,B306+C306),0)</f>
+        <f>IF(B306&gt;0.005,MIN($B$6+$B$7,B306+C306),0)</f>
         <v>0</v>
       </c>
       <c r="E306" s="2">
@@ -7552,11 +7552,11 @@
         <v>0.0</v>
       </c>
       <c r="C307" s="2">
-        <f>IF(B307&gt;0,ROUND(B307*$B$5/12,2),0)</f>
+        <f>IF(B307&gt;0.005,ROUND(B307*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D307" s="2">
-        <f>IF(B307&gt;0,MIN($B$6+$B$7,B307+C307),0)</f>
+        <f>IF(B307&gt;0.005,MIN($B$6+$B$7,B307+C307),0)</f>
         <v>0</v>
       </c>
       <c r="E307" s="2">
@@ -7577,11 +7577,11 @@
         <v>0.0</v>
       </c>
       <c r="C308" s="2">
-        <f>IF(B308&gt;0,ROUND(B308*$B$5/12,2),0)</f>
+        <f>IF(B308&gt;0.005,ROUND(B308*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D308" s="2">
-        <f>IF(B308&gt;0,MIN($B$6+$B$7,B308+C308),0)</f>
+        <f>IF(B308&gt;0.005,MIN($B$6+$B$7,B308+C308),0)</f>
         <v>0</v>
       </c>
       <c r="E308" s="2">
@@ -7602,11 +7602,11 @@
         <v>0.0</v>
       </c>
       <c r="C309" s="2">
-        <f>IF(B309&gt;0,ROUND(B309*$B$5/12,2),0)</f>
+        <f>IF(B309&gt;0.005,ROUND(B309*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D309" s="2">
-        <f>IF(B309&gt;0,MIN($B$6+$B$7,B309+C309),0)</f>
+        <f>IF(B309&gt;0.005,MIN($B$6+$B$7,B309+C309),0)</f>
         <v>0</v>
       </c>
       <c r="E309" s="2">
@@ -7627,11 +7627,11 @@
         <v>0.0</v>
       </c>
       <c r="C310" s="2">
-        <f>IF(B310&gt;0,ROUND(B310*$B$5/12,2),0)</f>
+        <f>IF(B310&gt;0.005,ROUND(B310*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D310" s="2">
-        <f>IF(B310&gt;0,MIN($B$6+$B$7,B310+C310),0)</f>
+        <f>IF(B310&gt;0.005,MIN($B$6+$B$7,B310+C310),0)</f>
         <v>0</v>
       </c>
       <c r="E310" s="2">
@@ -7652,11 +7652,11 @@
         <v>0.0</v>
       </c>
       <c r="C311" s="2">
-        <f>IF(B311&gt;0,ROUND(B311*$B$5/12,2),0)</f>
+        <f>IF(B311&gt;0.005,ROUND(B311*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D311" s="2">
-        <f>IF(B311&gt;0,MIN($B$6+$B$7,B311+C311),0)</f>
+        <f>IF(B311&gt;0.005,MIN($B$6+$B$7,B311+C311),0)</f>
         <v>0</v>
       </c>
       <c r="E311" s="2">
@@ -7677,11 +7677,11 @@
         <v>0.0</v>
       </c>
       <c r="C312" s="2">
-        <f>IF(B312&gt;0,ROUND(B312*$B$5/12,2),0)</f>
+        <f>IF(B312&gt;0.005,ROUND(B312*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D312" s="2">
-        <f>IF(B312&gt;0,MIN($B$6+$B$7,B312+C312),0)</f>
+        <f>IF(B312&gt;0.005,MIN($B$6+$B$7,B312+C312),0)</f>
         <v>0</v>
       </c>
       <c r="E312" s="2">
@@ -7702,11 +7702,11 @@
         <v>0.0</v>
       </c>
       <c r="C313" s="2">
-        <f>IF(B313&gt;0,ROUND(B313*$B$5/12,2),0)</f>
+        <f>IF(B313&gt;0.005,ROUND(B313*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D313" s="2">
-        <f>IF(B313&gt;0,MIN($B$6+$B$7,B313+C313),0)</f>
+        <f>IF(B313&gt;0.005,MIN($B$6+$B$7,B313+C313),0)</f>
         <v>0</v>
       </c>
       <c r="E313" s="2">
@@ -7727,11 +7727,11 @@
         <v>0.0</v>
       </c>
       <c r="C314" s="2">
-        <f>IF(B314&gt;0,ROUND(B314*$B$5/12,2),0)</f>
+        <f>IF(B314&gt;0.005,ROUND(B314*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D314" s="2">
-        <f>IF(B314&gt;0,MIN($B$6+$B$7,B314+C314),0)</f>
+        <f>IF(B314&gt;0.005,MIN($B$6+$B$7,B314+C314),0)</f>
         <v>0</v>
       </c>
       <c r="E314" s="2">
@@ -7752,11 +7752,11 @@
         <v>0.0</v>
       </c>
       <c r="C315" s="2">
-        <f>IF(B315&gt;0,ROUND(B315*$B$5/12,2),0)</f>
+        <f>IF(B315&gt;0.005,ROUND(B315*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D315" s="2">
-        <f>IF(B315&gt;0,MIN($B$6+$B$7,B315+C315),0)</f>
+        <f>IF(B315&gt;0.005,MIN($B$6+$B$7,B315+C315),0)</f>
         <v>0</v>
       </c>
       <c r="E315" s="2">
@@ -7777,11 +7777,11 @@
         <v>0.0</v>
       </c>
       <c r="C316" s="2">
-        <f>IF(B316&gt;0,ROUND(B316*$B$5/12,2),0)</f>
+        <f>IF(B316&gt;0.005,ROUND(B316*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D316" s="2">
-        <f>IF(B316&gt;0,MIN($B$6+$B$7,B316+C316),0)</f>
+        <f>IF(B316&gt;0.005,MIN($B$6+$B$7,B316+C316),0)</f>
         <v>0</v>
       </c>
       <c r="E316" s="2">
@@ -7802,11 +7802,11 @@
         <v>0.0</v>
       </c>
       <c r="C317" s="2">
-        <f>IF(B317&gt;0,ROUND(B317*$B$5/12,2),0)</f>
+        <f>IF(B317&gt;0.005,ROUND(B317*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D317" s="2">
-        <f>IF(B317&gt;0,MIN($B$6+$B$7,B317+C317),0)</f>
+        <f>IF(B317&gt;0.005,MIN($B$6+$B$7,B317+C317),0)</f>
         <v>0</v>
       </c>
       <c r="E317" s="2">
@@ -7827,11 +7827,11 @@
         <v>0.0</v>
       </c>
       <c r="C318" s="2">
-        <f>IF(B318&gt;0,ROUND(B318*$B$5/12,2),0)</f>
+        <f>IF(B318&gt;0.005,ROUND(B318*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D318" s="2">
-        <f>IF(B318&gt;0,MIN($B$6+$B$7,B318+C318),0)</f>
+        <f>IF(B318&gt;0.005,MIN($B$6+$B$7,B318+C318),0)</f>
         <v>0</v>
       </c>
       <c r="E318" s="2">
@@ -7852,11 +7852,11 @@
         <v>0.0</v>
       </c>
       <c r="C319" s="2">
-        <f>IF(B319&gt;0,ROUND(B319*$B$5/12,2),0)</f>
+        <f>IF(B319&gt;0.005,ROUND(B319*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D319" s="2">
-        <f>IF(B319&gt;0,MIN($B$6+$B$7,B319+C319),0)</f>
+        <f>IF(B319&gt;0.005,MIN($B$6+$B$7,B319+C319),0)</f>
         <v>0</v>
       </c>
       <c r="E319" s="2">
@@ -7877,11 +7877,11 @@
         <v>0.0</v>
       </c>
       <c r="C320" s="2">
-        <f>IF(B320&gt;0,ROUND(B320*$B$5/12,2),0)</f>
+        <f>IF(B320&gt;0.005,ROUND(B320*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D320" s="2">
-        <f>IF(B320&gt;0,MIN($B$6+$B$7,B320+C320),0)</f>
+        <f>IF(B320&gt;0.005,MIN($B$6+$B$7,B320+C320),0)</f>
         <v>0</v>
       </c>
       <c r="E320" s="2">
@@ -7902,11 +7902,11 @@
         <v>0.0</v>
       </c>
       <c r="C321" s="2">
-        <f>IF(B321&gt;0,ROUND(B321*$B$5/12,2),0)</f>
+        <f>IF(B321&gt;0.005,ROUND(B321*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D321" s="2">
-        <f>IF(B321&gt;0,MIN($B$6+$B$7,B321+C321),0)</f>
+        <f>IF(B321&gt;0.005,MIN($B$6+$B$7,B321+C321),0)</f>
         <v>0</v>
       </c>
       <c r="E321" s="2">
@@ -7927,11 +7927,11 @@
         <v>0.0</v>
       </c>
       <c r="C322" s="2">
-        <f>IF(B322&gt;0,ROUND(B322*$B$5/12,2),0)</f>
+        <f>IF(B322&gt;0.005,ROUND(B322*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D322" s="2">
-        <f>IF(B322&gt;0,MIN($B$6+$B$7,B322+C322),0)</f>
+        <f>IF(B322&gt;0.005,MIN($B$6+$B$7,B322+C322),0)</f>
         <v>0</v>
       </c>
       <c r="E322" s="2">
@@ -7952,11 +7952,11 @@
         <v>0.0</v>
       </c>
       <c r="C323" s="2">
-        <f>IF(B323&gt;0,ROUND(B323*$B$5/12,2),0)</f>
+        <f>IF(B323&gt;0.005,ROUND(B323*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D323" s="2">
-        <f>IF(B323&gt;0,MIN($B$6+$B$7,B323+C323),0)</f>
+        <f>IF(B323&gt;0.005,MIN($B$6+$B$7,B323+C323),0)</f>
         <v>0</v>
       </c>
       <c r="E323" s="2">
@@ -7977,11 +7977,11 @@
         <v>0.0</v>
       </c>
       <c r="C324" s="2">
-        <f>IF(B324&gt;0,ROUND(B324*$B$5/12,2),0)</f>
+        <f>IF(B324&gt;0.005,ROUND(B324*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D324" s="2">
-        <f>IF(B324&gt;0,MIN($B$6+$B$7,B324+C324),0)</f>
+        <f>IF(B324&gt;0.005,MIN($B$6+$B$7,B324+C324),0)</f>
         <v>0</v>
       </c>
       <c r="E324" s="2">
@@ -8002,11 +8002,11 @@
         <v>0.0</v>
       </c>
       <c r="C325" s="2">
-        <f>IF(B325&gt;0,ROUND(B325*$B$5/12,2),0)</f>
+        <f>IF(B325&gt;0.005,ROUND(B325*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D325" s="2">
-        <f>IF(B325&gt;0,MIN($B$6+$B$7,B325+C325),0)</f>
+        <f>IF(B325&gt;0.005,MIN($B$6+$B$7,B325+C325),0)</f>
         <v>0</v>
       </c>
       <c r="E325" s="2">
@@ -8027,11 +8027,11 @@
         <v>0.0</v>
       </c>
       <c r="C326" s="2">
-        <f>IF(B326&gt;0,ROUND(B326*$B$5/12,2),0)</f>
+        <f>IF(B326&gt;0.005,ROUND(B326*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D326" s="2">
-        <f>IF(B326&gt;0,MIN($B$6+$B$7,B326+C326),0)</f>
+        <f>IF(B326&gt;0.005,MIN($B$6+$B$7,B326+C326),0)</f>
         <v>0</v>
       </c>
       <c r="E326" s="2">
@@ -8052,11 +8052,11 @@
         <v>0.0</v>
       </c>
       <c r="C327" s="2">
-        <f>IF(B327&gt;0,ROUND(B327*$B$5/12,2),0)</f>
+        <f>IF(B327&gt;0.005,ROUND(B327*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D327" s="2">
-        <f>IF(B327&gt;0,MIN($B$6+$B$7,B327+C327),0)</f>
+        <f>IF(B327&gt;0.005,MIN($B$6+$B$7,B327+C327),0)</f>
         <v>0</v>
       </c>
       <c r="E327" s="2">
@@ -8077,11 +8077,11 @@
         <v>0.0</v>
       </c>
       <c r="C328" s="2">
-        <f>IF(B328&gt;0,ROUND(B328*$B$5/12,2),0)</f>
+        <f>IF(B328&gt;0.005,ROUND(B328*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D328" s="2">
-        <f>IF(B328&gt;0,MIN($B$6+$B$7,B328+C328),0)</f>
+        <f>IF(B328&gt;0.005,MIN($B$6+$B$7,B328+C328),0)</f>
         <v>0</v>
       </c>
       <c r="E328" s="2">
@@ -8102,11 +8102,11 @@
         <v>0.0</v>
       </c>
       <c r="C329" s="2">
-        <f>IF(B329&gt;0,ROUND(B329*$B$5/12,2),0)</f>
+        <f>IF(B329&gt;0.005,ROUND(B329*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D329" s="2">
-        <f>IF(B329&gt;0,MIN($B$6+$B$7,B329+C329),0)</f>
+        <f>IF(B329&gt;0.005,MIN($B$6+$B$7,B329+C329),0)</f>
         <v>0</v>
       </c>
       <c r="E329" s="2">
@@ -8127,11 +8127,11 @@
         <v>0.0</v>
       </c>
       <c r="C330" s="2">
-        <f>IF(B330&gt;0,ROUND(B330*$B$5/12,2),0)</f>
+        <f>IF(B330&gt;0.005,ROUND(B330*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D330" s="2">
-        <f>IF(B330&gt;0,MIN($B$6+$B$7,B330+C330),0)</f>
+        <f>IF(B330&gt;0.005,MIN($B$6+$B$7,B330+C330),0)</f>
         <v>0</v>
       </c>
       <c r="E330" s="2">
@@ -8152,11 +8152,11 @@
         <v>0.0</v>
       </c>
       <c r="C331" s="2">
-        <f>IF(B331&gt;0,ROUND(B331*$B$5/12,2),0)</f>
+        <f>IF(B331&gt;0.005,ROUND(B331*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D331" s="2">
-        <f>IF(B331&gt;0,MIN($B$6+$B$7,B331+C331),0)</f>
+        <f>IF(B331&gt;0.005,MIN($B$6+$B$7,B331+C331),0)</f>
         <v>0</v>
       </c>
       <c r="E331" s="2">
@@ -8177,11 +8177,11 @@
         <v>0.0</v>
       </c>
       <c r="C332" s="2">
-        <f>IF(B332&gt;0,ROUND(B332*$B$5/12,2),0)</f>
+        <f>IF(B332&gt;0.005,ROUND(B332*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D332" s="2">
-        <f>IF(B332&gt;0,MIN($B$6+$B$7,B332+C332),0)</f>
+        <f>IF(B332&gt;0.005,MIN($B$6+$B$7,B332+C332),0)</f>
         <v>0</v>
       </c>
       <c r="E332" s="2">
@@ -8202,11 +8202,11 @@
         <v>0.0</v>
       </c>
       <c r="C333" s="2">
-        <f>IF(B333&gt;0,ROUND(B333*$B$5/12,2),0)</f>
+        <f>IF(B333&gt;0.005,ROUND(B333*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D333" s="2">
-        <f>IF(B333&gt;0,MIN($B$6+$B$7,B333+C333),0)</f>
+        <f>IF(B333&gt;0.005,MIN($B$6+$B$7,B333+C333),0)</f>
         <v>0</v>
       </c>
       <c r="E333" s="2">
@@ -8227,11 +8227,11 @@
         <v>0.0</v>
       </c>
       <c r="C334" s="2">
-        <f>IF(B334&gt;0,ROUND(B334*$B$5/12,2),0)</f>
+        <f>IF(B334&gt;0.005,ROUND(B334*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D334" s="2">
-        <f>IF(B334&gt;0,MIN($B$6+$B$7,B334+C334),0)</f>
+        <f>IF(B334&gt;0.005,MIN($B$6+$B$7,B334+C334),0)</f>
         <v>0</v>
       </c>
       <c r="E334" s="2">
@@ -8252,11 +8252,11 @@
         <v>0.0</v>
       </c>
       <c r="C335" s="2">
-        <f>IF(B335&gt;0,ROUND(B335*$B$5/12,2),0)</f>
+        <f>IF(B335&gt;0.005,ROUND(B335*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D335" s="2">
-        <f>IF(B335&gt;0,MIN($B$6+$B$7,B335+C335),0)</f>
+        <f>IF(B335&gt;0.005,MIN($B$6+$B$7,B335+C335),0)</f>
         <v>0</v>
       </c>
       <c r="E335" s="2">
@@ -8277,11 +8277,11 @@
         <v>0.0</v>
       </c>
       <c r="C336" s="2">
-        <f>IF(B336&gt;0,ROUND(B336*$B$5/12,2),0)</f>
+        <f>IF(B336&gt;0.005,ROUND(B336*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D336" s="2">
-        <f>IF(B336&gt;0,MIN($B$6+$B$7,B336+C336),0)</f>
+        <f>IF(B336&gt;0.005,MIN($B$6+$B$7,B336+C336),0)</f>
         <v>0</v>
       </c>
       <c r="E336" s="2">
@@ -8302,11 +8302,11 @@
         <v>0.0</v>
       </c>
       <c r="C337" s="2">
-        <f>IF(B337&gt;0,ROUND(B337*$B$5/12,2),0)</f>
+        <f>IF(B337&gt;0.005,ROUND(B337*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D337" s="2">
-        <f>IF(B337&gt;0,MIN($B$6+$B$7,B337+C337),0)</f>
+        <f>IF(B337&gt;0.005,MIN($B$6+$B$7,B337+C337),0)</f>
         <v>0</v>
       </c>
       <c r="E337" s="2">
@@ -8327,11 +8327,11 @@
         <v>0.0</v>
       </c>
       <c r="C338" s="2">
-        <f>IF(B338&gt;0,ROUND(B338*$B$5/12,2),0)</f>
+        <f>IF(B338&gt;0.005,ROUND(B338*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D338" s="2">
-        <f>IF(B338&gt;0,MIN($B$6+$B$7,B338+C338),0)</f>
+        <f>IF(B338&gt;0.005,MIN($B$6+$B$7,B338+C338),0)</f>
         <v>0</v>
       </c>
       <c r="E338" s="2">
@@ -8352,11 +8352,11 @@
         <v>0.0</v>
       </c>
       <c r="C339" s="2">
-        <f>IF(B339&gt;0,ROUND(B339*$B$5/12,2),0)</f>
+        <f>IF(B339&gt;0.005,ROUND(B339*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D339" s="2">
-        <f>IF(B339&gt;0,MIN($B$6+$B$7,B339+C339),0)</f>
+        <f>IF(B339&gt;0.005,MIN($B$6+$B$7,B339+C339),0)</f>
         <v>0</v>
       </c>
       <c r="E339" s="2">
@@ -8377,11 +8377,11 @@
         <v>0.0</v>
       </c>
       <c r="C340" s="2">
-        <f>IF(B340&gt;0,ROUND(B340*$B$5/12,2),0)</f>
+        <f>IF(B340&gt;0.005,ROUND(B340*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D340" s="2">
-        <f>IF(B340&gt;0,MIN($B$6+$B$7,B340+C340),0)</f>
+        <f>IF(B340&gt;0.005,MIN($B$6+$B$7,B340+C340),0)</f>
         <v>0</v>
       </c>
       <c r="E340" s="2">
@@ -8402,11 +8402,11 @@
         <v>0.0</v>
       </c>
       <c r="C341" s="2">
-        <f>IF(B341&gt;0,ROUND(B341*$B$5/12,2),0)</f>
+        <f>IF(B341&gt;0.005,ROUND(B341*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D341" s="2">
-        <f>IF(B341&gt;0,MIN($B$6+$B$7,B341+C341),0)</f>
+        <f>IF(B341&gt;0.005,MIN($B$6+$B$7,B341+C341),0)</f>
         <v>0</v>
       </c>
       <c r="E341" s="2">
@@ -8427,11 +8427,11 @@
         <v>0.0</v>
       </c>
       <c r="C342" s="2">
-        <f>IF(B342&gt;0,ROUND(B342*$B$5/12,2),0)</f>
+        <f>IF(B342&gt;0.005,ROUND(B342*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D342" s="2">
-        <f>IF(B342&gt;0,MIN($B$6+$B$7,B342+C342),0)</f>
+        <f>IF(B342&gt;0.005,MIN($B$6+$B$7,B342+C342),0)</f>
         <v>0</v>
       </c>
       <c r="E342" s="2">
@@ -8452,11 +8452,11 @@
         <v>0.0</v>
       </c>
       <c r="C343" s="2">
-        <f>IF(B343&gt;0,ROUND(B343*$B$5/12,2),0)</f>
+        <f>IF(B343&gt;0.005,ROUND(B343*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D343" s="2">
-        <f>IF(B343&gt;0,MIN($B$6+$B$7,B343+C343),0)</f>
+        <f>IF(B343&gt;0.005,MIN($B$6+$B$7,B343+C343),0)</f>
         <v>0</v>
       </c>
       <c r="E343" s="2">
@@ -8477,11 +8477,11 @@
         <v>0.0</v>
       </c>
       <c r="C344" s="2">
-        <f>IF(B344&gt;0,ROUND(B344*$B$5/12,2),0)</f>
+        <f>IF(B344&gt;0.005,ROUND(B344*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D344" s="2">
-        <f>IF(B344&gt;0,MIN($B$6+$B$7,B344+C344),0)</f>
+        <f>IF(B344&gt;0.005,MIN($B$6+$B$7,B344+C344),0)</f>
         <v>0</v>
       </c>
       <c r="E344" s="2">
@@ -8502,11 +8502,11 @@
         <v>0.0</v>
       </c>
       <c r="C345" s="2">
-        <f>IF(B345&gt;0,ROUND(B345*$B$5/12,2),0)</f>
+        <f>IF(B345&gt;0.005,ROUND(B345*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D345" s="2">
-        <f>IF(B345&gt;0,MIN($B$6+$B$7,B345+C345),0)</f>
+        <f>IF(B345&gt;0.005,MIN($B$6+$B$7,B345+C345),0)</f>
         <v>0</v>
       </c>
       <c r="E345" s="2">
@@ -8527,11 +8527,11 @@
         <v>0.0</v>
       </c>
       <c r="C346" s="2">
-        <f>IF(B346&gt;0,ROUND(B346*$B$5/12,2),0)</f>
+        <f>IF(B346&gt;0.005,ROUND(B346*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D346" s="2">
-        <f>IF(B346&gt;0,MIN($B$6+$B$7,B346+C346),0)</f>
+        <f>IF(B346&gt;0.005,MIN($B$6+$B$7,B346+C346),0)</f>
         <v>0</v>
       </c>
       <c r="E346" s="2">
@@ -8552,11 +8552,11 @@
         <v>0.0</v>
       </c>
       <c r="C347" s="2">
-        <f>IF(B347&gt;0,ROUND(B347*$B$5/12,2),0)</f>
+        <f>IF(B347&gt;0.005,ROUND(B347*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D347" s="2">
-        <f>IF(B347&gt;0,MIN($B$6+$B$7,B347+C347),0)</f>
+        <f>IF(B347&gt;0.005,MIN($B$6+$B$7,B347+C347),0)</f>
         <v>0</v>
       </c>
       <c r="E347" s="2">
@@ -8577,11 +8577,11 @@
         <v>0.0</v>
       </c>
       <c r="C348" s="2">
-        <f>IF(B348&gt;0,ROUND(B348*$B$5/12,2),0)</f>
+        <f>IF(B348&gt;0.005,ROUND(B348*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D348" s="2">
-        <f>IF(B348&gt;0,MIN($B$6+$B$7,B348+C348),0)</f>
+        <f>IF(B348&gt;0.005,MIN($B$6+$B$7,B348+C348),0)</f>
         <v>0</v>
       </c>
       <c r="E348" s="2">
@@ -8602,11 +8602,11 @@
         <v>0.0</v>
       </c>
       <c r="C349" s="2">
-        <f>IF(B349&gt;0,ROUND(B349*$B$5/12,2),0)</f>
+        <f>IF(B349&gt;0.005,ROUND(B349*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D349" s="2">
-        <f>IF(B349&gt;0,MIN($B$6+$B$7,B349+C349),0)</f>
+        <f>IF(B349&gt;0.005,MIN($B$6+$B$7,B349+C349),0)</f>
         <v>0</v>
       </c>
       <c r="E349" s="2">
@@ -8627,11 +8627,11 @@
         <v>0.0</v>
       </c>
       <c r="C350" s="2">
-        <f>IF(B350&gt;0,ROUND(B350*$B$5/12,2),0)</f>
+        <f>IF(B350&gt;0.005,ROUND(B350*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D350" s="2">
-        <f>IF(B350&gt;0,MIN($B$6+$B$7,B350+C350),0)</f>
+        <f>IF(B350&gt;0.005,MIN($B$6+$B$7,B350+C350),0)</f>
         <v>0</v>
       </c>
       <c r="E350" s="2">
@@ -8652,11 +8652,11 @@
         <v>0.0</v>
       </c>
       <c r="C351" s="2">
-        <f>IF(B351&gt;0,ROUND(B351*$B$5/12,2),0)</f>
+        <f>IF(B351&gt;0.005,ROUND(B351*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D351" s="2">
-        <f>IF(B351&gt;0,MIN($B$6+$B$7,B351+C351),0)</f>
+        <f>IF(B351&gt;0.005,MIN($B$6+$B$7,B351+C351),0)</f>
         <v>0</v>
       </c>
       <c r="E351" s="2">
@@ -8677,11 +8677,11 @@
         <v>0.0</v>
       </c>
       <c r="C352" s="2">
-        <f>IF(B352&gt;0,ROUND(B352*$B$5/12,2),0)</f>
+        <f>IF(B352&gt;0.005,ROUND(B352*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D352" s="2">
-        <f>IF(B352&gt;0,MIN($B$6+$B$7,B352+C352),0)</f>
+        <f>IF(B352&gt;0.005,MIN($B$6+$B$7,B352+C352),0)</f>
         <v>0</v>
       </c>
       <c r="E352" s="2">
@@ -8702,11 +8702,11 @@
         <v>0.0</v>
       </c>
       <c r="C353" s="2">
-        <f>IF(B353&gt;0,ROUND(B353*$B$5/12,2),0)</f>
+        <f>IF(B353&gt;0.005,ROUND(B353*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D353" s="2">
-        <f>IF(B353&gt;0,MIN($B$6+$B$7,B353+C353),0)</f>
+        <f>IF(B353&gt;0.005,MIN($B$6+$B$7,B353+C353),0)</f>
         <v>0</v>
       </c>
       <c r="E353" s="2">
@@ -8727,11 +8727,11 @@
         <v>0.0</v>
       </c>
       <c r="C354" s="2">
-        <f>IF(B354&gt;0,ROUND(B354*$B$5/12,2),0)</f>
+        <f>IF(B354&gt;0.005,ROUND(B354*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D354" s="2">
-        <f>IF(B354&gt;0,MIN($B$6+$B$7,B354+C354),0)</f>
+        <f>IF(B354&gt;0.005,MIN($B$6+$B$7,B354+C354),0)</f>
         <v>0</v>
       </c>
       <c r="E354" s="2">
@@ -8752,11 +8752,11 @@
         <v>0.0</v>
       </c>
       <c r="C355" s="2">
-        <f>IF(B355&gt;0,ROUND(B355*$B$5/12,2),0)</f>
+        <f>IF(B355&gt;0.005,ROUND(B355*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D355" s="2">
-        <f>IF(B355&gt;0,MIN($B$6+$B$7,B355+C355),0)</f>
+        <f>IF(B355&gt;0.005,MIN($B$6+$B$7,B355+C355),0)</f>
         <v>0</v>
       </c>
       <c r="E355" s="2">
@@ -8777,11 +8777,11 @@
         <v>0.0</v>
       </c>
       <c r="C356" s="2">
-        <f>IF(B356&gt;0,ROUND(B356*$B$5/12,2),0)</f>
+        <f>IF(B356&gt;0.005,ROUND(B356*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D356" s="2">
-        <f>IF(B356&gt;0,MIN($B$6+$B$7,B356+C356),0)</f>
+        <f>IF(B356&gt;0.005,MIN($B$6+$B$7,B356+C356),0)</f>
         <v>0</v>
       </c>
       <c r="E356" s="2">
@@ -8802,11 +8802,11 @@
         <v>0.0</v>
       </c>
       <c r="C357" s="2">
-        <f>IF(B357&gt;0,ROUND(B357*$B$5/12,2),0)</f>
+        <f>IF(B357&gt;0.005,ROUND(B357*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D357" s="2">
-        <f>IF(B357&gt;0,MIN($B$6+$B$7,B357+C357),0)</f>
+        <f>IF(B357&gt;0.005,MIN($B$6+$B$7,B357+C357),0)</f>
         <v>0</v>
       </c>
       <c r="E357" s="2">
@@ -8827,11 +8827,11 @@
         <v>0.0</v>
       </c>
       <c r="C358" s="2">
-        <f>IF(B358&gt;0,ROUND(B358*$B$5/12,2),0)</f>
+        <f>IF(B358&gt;0.005,ROUND(B358*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D358" s="2">
-        <f>IF(B358&gt;0,MIN($B$6+$B$7,B358+C358),0)</f>
+        <f>IF(B358&gt;0.005,MIN($B$6+$B$7,B358+C358),0)</f>
         <v>0</v>
       </c>
       <c r="E358" s="2">
@@ -8852,11 +8852,11 @@
         <v>0.0</v>
       </c>
       <c r="C359" s="2">
-        <f>IF(B359&gt;0,ROUND(B359*$B$5/12,2),0)</f>
+        <f>IF(B359&gt;0.005,ROUND(B359*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D359" s="2">
-        <f>IF(B359&gt;0,MIN($B$6+$B$7,B359+C359),0)</f>
+        <f>IF(B359&gt;0.005,MIN($B$6+$B$7,B359+C359),0)</f>
         <v>0</v>
       </c>
       <c r="E359" s="2">
@@ -8877,11 +8877,11 @@
         <v>0.0</v>
       </c>
       <c r="C360" s="2">
-        <f>IF(B360&gt;0,ROUND(B360*$B$5/12,2),0)</f>
+        <f>IF(B360&gt;0.005,ROUND(B360*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D360" s="2">
-        <f>IF(B360&gt;0,MIN($B$6+$B$7,B360+C360),0)</f>
+        <f>IF(B360&gt;0.005,MIN($B$6+$B$7,B360+C360),0)</f>
         <v>0</v>
       </c>
       <c r="E360" s="2">
@@ -8902,11 +8902,11 @@
         <v>0.0</v>
       </c>
       <c r="C361" s="2">
-        <f>IF(B361&gt;0,ROUND(B361*$B$5/12,2),0)</f>
+        <f>IF(B361&gt;0.005,ROUND(B361*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D361" s="2">
-        <f>IF(B361&gt;0,MIN($B$6+$B$7,B361+C361),0)</f>
+        <f>IF(B361&gt;0.005,MIN($B$6+$B$7,B361+C361),0)</f>
         <v>0</v>
       </c>
       <c r="E361" s="2">
@@ -8927,11 +8927,11 @@
         <v>0.0</v>
       </c>
       <c r="C362" s="2">
-        <f>IF(B362&gt;0,ROUND(B362*$B$5/12,2),0)</f>
+        <f>IF(B362&gt;0.005,ROUND(B362*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D362" s="2">
-        <f>IF(B362&gt;0,MIN($B$6+$B$7,B362+C362),0)</f>
+        <f>IF(B362&gt;0.005,MIN($B$6+$B$7,B362+C362),0)</f>
         <v>0</v>
       </c>
       <c r="E362" s="2">
@@ -8952,11 +8952,11 @@
         <v>0.0</v>
       </c>
       <c r="C363" s="2">
-        <f>IF(B363&gt;0,ROUND(B363*$B$5/12,2),0)</f>
+        <f>IF(B363&gt;0.005,ROUND(B363*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D363" s="2">
-        <f>IF(B363&gt;0,MIN($B$6+$B$7,B363+C363),0)</f>
+        <f>IF(B363&gt;0.005,MIN($B$6+$B$7,B363+C363),0)</f>
         <v>0</v>
       </c>
       <c r="E363" s="2">
@@ -8977,11 +8977,11 @@
         <v>0.0</v>
       </c>
       <c r="C364" s="2">
-        <f>IF(B364&gt;0,ROUND(B364*$B$5/12,2),0)</f>
+        <f>IF(B364&gt;0.005,ROUND(B364*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D364" s="2">
-        <f>IF(B364&gt;0,MIN($B$6+$B$7,B364+C364),0)</f>
+        <f>IF(B364&gt;0.005,MIN($B$6+$B$7,B364+C364),0)</f>
         <v>0</v>
       </c>
       <c r="E364" s="2">
@@ -9002,11 +9002,11 @@
         <v>0.0</v>
       </c>
       <c r="C365" s="2">
-        <f>IF(B365&gt;0,ROUND(B365*$B$5/12,2),0)</f>
+        <f>IF(B365&gt;0.005,ROUND(B365*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D365" s="2">
-        <f>IF(B365&gt;0,MIN($B$6+$B$7,B365+C365),0)</f>
+        <f>IF(B365&gt;0.005,MIN($B$6+$B$7,B365+C365),0)</f>
         <v>0</v>
       </c>
       <c r="E365" s="2">
@@ -9027,11 +9027,11 @@
         <v>0.0</v>
       </c>
       <c r="C366" s="2">
-        <f>IF(B366&gt;0,ROUND(B366*$B$5/12,2),0)</f>
+        <f>IF(B366&gt;0.005,ROUND(B366*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D366" s="2">
-        <f>IF(B366&gt;0,MIN($B$6+$B$7,B366+C366),0)</f>
+        <f>IF(B366&gt;0.005,MIN($B$6+$B$7,B366+C366),0)</f>
         <v>0</v>
       </c>
       <c r="E366" s="2">
@@ -9052,11 +9052,11 @@
         <v>0.0</v>
       </c>
       <c r="C367" s="2">
-        <f>IF(B367&gt;0,ROUND(B367*$B$5/12,2),0)</f>
+        <f>IF(B367&gt;0.005,ROUND(B367*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D367" s="2">
-        <f>IF(B367&gt;0,MIN($B$6+$B$7,B367+C367),0)</f>
+        <f>IF(B367&gt;0.005,MIN($B$6+$B$7,B367+C367),0)</f>
         <v>0</v>
       </c>
       <c r="E367" s="2">
@@ -9077,11 +9077,11 @@
         <v>0.0</v>
       </c>
       <c r="C368" s="2">
-        <f>IF(B368&gt;0,ROUND(B368*$B$5/12,2),0)</f>
+        <f>IF(B368&gt;0.005,ROUND(B368*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D368" s="2">
-        <f>IF(B368&gt;0,MIN($B$6+$B$7,B368+C368),0)</f>
+        <f>IF(B368&gt;0.005,MIN($B$6+$B$7,B368+C368),0)</f>
         <v>0</v>
       </c>
       <c r="E368" s="2">
@@ -9102,11 +9102,11 @@
         <v>0.0</v>
       </c>
       <c r="C369" s="2">
-        <f>IF(B369&gt;0,ROUND(B369*$B$5/12,2),0)</f>
+        <f>IF(B369&gt;0.005,ROUND(B369*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D369" s="2">
-        <f>IF(B369&gt;0,MIN($B$6+$B$7,B369+C369),0)</f>
+        <f>IF(B369&gt;0.005,MIN($B$6+$B$7,B369+C369),0)</f>
         <v>0</v>
       </c>
       <c r="E369" s="2">
@@ -9127,11 +9127,11 @@
         <v>0.0</v>
       </c>
       <c r="C370" s="2">
-        <f>IF(B370&gt;0,ROUND(B370*$B$5/12,2),0)</f>
+        <f>IF(B370&gt;0.005,ROUND(B370*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D370" s="2">
-        <f>IF(B370&gt;0,MIN($B$6+$B$7,B370+C370),0)</f>
+        <f>IF(B370&gt;0.005,MIN($B$6+$B$7,B370+C370),0)</f>
         <v>0</v>
       </c>
       <c r="E370" s="2">
@@ -9152,11 +9152,11 @@
         <v>0.0</v>
       </c>
       <c r="C371" s="2">
-        <f>IF(B371&gt;0,ROUND(B371*$B$5/12,2),0)</f>
+        <f>IF(B371&gt;0.005,ROUND(B371*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D371" s="2">
-        <f>IF(B371&gt;0,MIN($B$6+$B$7,B371+C371),0)</f>
+        <f>IF(B371&gt;0.005,MIN($B$6+$B$7,B371+C371),0)</f>
         <v>0</v>
       </c>
       <c r="E371" s="2">
@@ -9177,11 +9177,11 @@
         <v>0.0</v>
       </c>
       <c r="C372" s="2">
-        <f>IF(B372&gt;0,ROUND(B372*$B$5/12,2),0)</f>
+        <f>IF(B372&gt;0.005,ROUND(B372*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D372" s="2">
-        <f>IF(B372&gt;0,MIN($B$6+$B$7,B372+C372),0)</f>
+        <f>IF(B372&gt;0.005,MIN($B$6+$B$7,B372+C372),0)</f>
         <v>0</v>
       </c>
       <c r="E372" s="2">
@@ -9202,11 +9202,11 @@
         <v>0.0</v>
       </c>
       <c r="C373" s="2">
-        <f>IF(B373&gt;0,ROUND(B373*$B$5/12,2),0)</f>
+        <f>IF(B373&gt;0.005,ROUND(B373*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D373" s="2">
-        <f>IF(B373&gt;0,MIN($B$6+$B$7,B373+C373),0)</f>
+        <f>IF(B373&gt;0.005,MIN($B$6+$B$7,B373+C373),0)</f>
         <v>0</v>
       </c>
       <c r="E373" s="2">
@@ -9227,11 +9227,11 @@
         <v>0.0</v>
       </c>
       <c r="C374" s="2">
-        <f>IF(B374&gt;0,ROUND(B374*$B$5/12,2),0)</f>
+        <f>IF(B374&gt;0.005,ROUND(B374*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D374" s="2">
-        <f>IF(B374&gt;0,MIN($B$6+$B$7,B374+C374),0)</f>
+        <f>IF(B374&gt;0.005,MIN($B$6+$B$7,B374+C374),0)</f>
         <v>0</v>
       </c>
       <c r="E374" s="2">
@@ -9252,11 +9252,11 @@
         <v>0.0</v>
       </c>
       <c r="C375" s="2">
-        <f>IF(B375&gt;0,ROUND(B375*$B$5/12,2),0)</f>
+        <f>IF(B375&gt;0.005,ROUND(B375*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D375" s="2">
-        <f>IF(B375&gt;0,MIN($B$6+$B$7,B375+C375),0)</f>
+        <f>IF(B375&gt;0.005,MIN($B$6+$B$7,B375+C375),0)</f>
         <v>0</v>
       </c>
       <c r="E375" s="2">
@@ -9277,11 +9277,11 @@
         <v>0.0</v>
       </c>
       <c r="C376" s="2">
-        <f>IF(B376&gt;0,ROUND(B376*$B$5/12,2),0)</f>
+        <f>IF(B376&gt;0.005,ROUND(B376*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D376" s="2">
-        <f>IF(B376&gt;0,MIN($B$6+$B$7,B376+C376),0)</f>
+        <f>IF(B376&gt;0.005,MIN($B$6+$B$7,B376+C376),0)</f>
         <v>0</v>
       </c>
       <c r="E376" s="2">
@@ -9302,11 +9302,11 @@
         <v>0.0</v>
       </c>
       <c r="C377" s="2">
-        <f>IF(B377&gt;0,ROUND(B377*$B$5/12,2),0)</f>
+        <f>IF(B377&gt;0.005,ROUND(B377*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D377" s="2">
-        <f>IF(B377&gt;0,MIN($B$6+$B$7,B377+C377),0)</f>
+        <f>IF(B377&gt;0.005,MIN($B$6+$B$7,B377+C377),0)</f>
         <v>0</v>
       </c>
       <c r="E377" s="2">
@@ -9327,11 +9327,11 @@
         <v>0.0</v>
       </c>
       <c r="C378" s="2">
-        <f>IF(B378&gt;0,ROUND(B378*$B$5/12,2),0)</f>
+        <f>IF(B378&gt;0.005,ROUND(B378*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D378" s="2">
-        <f>IF(B378&gt;0,MIN($B$6+$B$7,B378+C378),0)</f>
+        <f>IF(B378&gt;0.005,MIN($B$6+$B$7,B378+C378),0)</f>
         <v>0</v>
       </c>
       <c r="E378" s="2">
@@ -9352,11 +9352,11 @@
         <v>0.0</v>
       </c>
       <c r="C379" s="2">
-        <f>IF(B379&gt;0,ROUND(B379*$B$5/12,2),0)</f>
+        <f>IF(B379&gt;0.005,ROUND(B379*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D379" s="2">
-        <f>IF(B379&gt;0,MIN($B$6+$B$7,B379+C379),0)</f>
+        <f>IF(B379&gt;0.005,MIN($B$6+$B$7,B379+C379),0)</f>
         <v>0</v>
       </c>
       <c r="E379" s="2">
@@ -9377,11 +9377,11 @@
         <v>0.0</v>
       </c>
       <c r="C380" s="2">
-        <f>IF(B380&gt;0,ROUND(B380*$B$5/12,2),0)</f>
+        <f>IF(B380&gt;0.005,ROUND(B380*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D380" s="2">
-        <f>IF(B380&gt;0,MIN($B$6+$B$7,B380+C380),0)</f>
+        <f>IF(B380&gt;0.005,MIN($B$6+$B$7,B380+C380),0)</f>
         <v>0</v>
       </c>
       <c r="E380" s="2">
@@ -9402,11 +9402,11 @@
         <v>0.0</v>
       </c>
       <c r="C381" s="2">
-        <f>IF(B381&gt;0,ROUND(B381*$B$5/12,2),0)</f>
+        <f>IF(B381&gt;0.005,ROUND(B381*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D381" s="2">
-        <f>IF(B381&gt;0,MIN($B$6+$B$7,B381+C381),0)</f>
+        <f>IF(B381&gt;0.005,MIN($B$6+$B$7,B381+C381),0)</f>
         <v>0</v>
       </c>
       <c r="E381" s="2">
@@ -9427,11 +9427,11 @@
         <v>0.0</v>
       </c>
       <c r="C382" s="2">
-        <f>IF(B382&gt;0,ROUND(B382*$B$5/12,2),0)</f>
+        <f>IF(B382&gt;0.005,ROUND(B382*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D382" s="2">
-        <f>IF(B382&gt;0,MIN($B$6+$B$7,B382+C382),0)</f>
+        <f>IF(B382&gt;0.005,MIN($B$6+$B$7,B382+C382),0)</f>
         <v>0</v>
       </c>
       <c r="E382" s="2">
@@ -9452,11 +9452,11 @@
         <v>0.0</v>
       </c>
       <c r="C383" s="2">
-        <f>IF(B383&gt;0,ROUND(B383*$B$5/12,2),0)</f>
+        <f>IF(B383&gt;0.005,ROUND(B383*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D383" s="2">
-        <f>IF(B383&gt;0,MIN($B$6+$B$7,B383+C383),0)</f>
+        <f>IF(B383&gt;0.005,MIN($B$6+$B$7,B383+C383),0)</f>
         <v>0</v>
       </c>
       <c r="E383" s="2">
@@ -9477,11 +9477,11 @@
         <v>0.0</v>
       </c>
       <c r="C384" s="2">
-        <f>IF(B384&gt;0,ROUND(B384*$B$5/12,2),0)</f>
+        <f>IF(B384&gt;0.005,ROUND(B384*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D384" s="2">
-        <f>IF(B384&gt;0,MIN($B$6+$B$7,B384+C384),0)</f>
+        <f>IF(B384&gt;0.005,MIN($B$6+$B$7,B384+C384),0)</f>
         <v>0</v>
       </c>
       <c r="E384" s="2">
@@ -9502,11 +9502,11 @@
         <v>0.0</v>
       </c>
       <c r="C385" s="2">
-        <f>IF(B385&gt;0,ROUND(B385*$B$5/12,2),0)</f>
+        <f>IF(B385&gt;0.005,ROUND(B385*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D385" s="2">
-        <f>IF(B385&gt;0,MIN($B$6+$B$7,B385+C385),0)</f>
+        <f>IF(B385&gt;0.005,MIN($B$6+$B$7,B385+C385),0)</f>
         <v>0</v>
       </c>
       <c r="E385" s="2">
@@ -9527,11 +9527,11 @@
         <v>0.0</v>
       </c>
       <c r="C386" s="2">
-        <f>IF(B386&gt;0,ROUND(B386*$B$5/12,2),0)</f>
+        <f>IF(B386&gt;0.005,ROUND(B386*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D386" s="2">
-        <f>IF(B386&gt;0,MIN($B$6+$B$7,B386+C386),0)</f>
+        <f>IF(B386&gt;0.005,MIN($B$6+$B$7,B386+C386),0)</f>
         <v>0</v>
       </c>
       <c r="E386" s="2">
@@ -9552,11 +9552,11 @@
         <v>0.0</v>
       </c>
       <c r="C387" s="2">
-        <f>IF(B387&gt;0,ROUND(B387*$B$5/12,2),0)</f>
+        <f>IF(B387&gt;0.005,ROUND(B387*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D387" s="2">
-        <f>IF(B387&gt;0,MIN($B$6+$B$7,B387+C387),0)</f>
+        <f>IF(B387&gt;0.005,MIN($B$6+$B$7,B387+C387),0)</f>
         <v>0</v>
       </c>
       <c r="E387" s="2">
@@ -9577,11 +9577,11 @@
         <v>0.0</v>
       </c>
       <c r="C388" s="2">
-        <f>IF(B388&gt;0,ROUND(B388*$B$5/12,2),0)</f>
+        <f>IF(B388&gt;0.005,ROUND(B388*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D388" s="2">
-        <f>IF(B388&gt;0,MIN($B$6+$B$7,B388+C388),0)</f>
+        <f>IF(B388&gt;0.005,MIN($B$6+$B$7,B388+C388),0)</f>
         <v>0</v>
       </c>
       <c r="E388" s="2">
@@ -9602,11 +9602,11 @@
         <v>0.0</v>
       </c>
       <c r="C389" s="2">
-        <f>IF(B389&gt;0,ROUND(B389*$B$5/12,2),0)</f>
+        <f>IF(B389&gt;0.005,ROUND(B389*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D389" s="2">
-        <f>IF(B389&gt;0,MIN($B$6+$B$7,B389+C389),0)</f>
+        <f>IF(B389&gt;0.005,MIN($B$6+$B$7,B389+C389),0)</f>
         <v>0</v>
       </c>
       <c r="E389" s="2">
@@ -9627,11 +9627,11 @@
         <v>0.0</v>
       </c>
       <c r="C390" s="2">
-        <f>IF(B390&gt;0,ROUND(B390*$B$5/12,2),0)</f>
+        <f>IF(B390&gt;0.005,ROUND(B390*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D390" s="2">
-        <f>IF(B390&gt;0,MIN($B$6+$B$7,B390+C390),0)</f>
+        <f>IF(B390&gt;0.005,MIN($B$6+$B$7,B390+C390),0)</f>
         <v>0</v>
       </c>
       <c r="E390" s="2">
@@ -9652,11 +9652,11 @@
         <v>0.0</v>
       </c>
       <c r="C391" s="2">
-        <f>IF(B391&gt;0,ROUND(B391*$B$5/12,2),0)</f>
+        <f>IF(B391&gt;0.005,ROUND(B391*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D391" s="2">
-        <f>IF(B391&gt;0,MIN($B$6+$B$7,B391+C391),0)</f>
+        <f>IF(B391&gt;0.005,MIN($B$6+$B$7,B391+C391),0)</f>
         <v>0</v>
       </c>
       <c r="E391" s="2">
@@ -9677,11 +9677,11 @@
         <v>0.0</v>
       </c>
       <c r="C392" s="2">
-        <f>IF(B392&gt;0,ROUND(B392*$B$5/12,2),0)</f>
+        <f>IF(B392&gt;0.005,ROUND(B392*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D392" s="2">
-        <f>IF(B392&gt;0,MIN($B$6+$B$7,B392+C392),0)</f>
+        <f>IF(B392&gt;0.005,MIN($B$6+$B$7,B392+C392),0)</f>
         <v>0</v>
       </c>
       <c r="E392" s="2">
@@ -9702,11 +9702,11 @@
         <v>0.0</v>
       </c>
       <c r="C393" s="2">
-        <f>IF(B393&gt;0,ROUND(B393*$B$5/12,2),0)</f>
+        <f>IF(B393&gt;0.005,ROUND(B393*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D393" s="2">
-        <f>IF(B393&gt;0,MIN($B$6+$B$7,B393+C393),0)</f>
+        <f>IF(B393&gt;0.005,MIN($B$6+$B$7,B393+C393),0)</f>
         <v>0</v>
       </c>
       <c r="E393" s="2">
@@ -9727,11 +9727,11 @@
         <v>0.0</v>
       </c>
       <c r="C394" s="2">
-        <f>IF(B394&gt;0,ROUND(B394*$B$5/12,2),0)</f>
+        <f>IF(B394&gt;0.005,ROUND(B394*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D394" s="2">
-        <f>IF(B394&gt;0,MIN($B$6+$B$7,B394+C394),0)</f>
+        <f>IF(B394&gt;0.005,MIN($B$6+$B$7,B394+C394),0)</f>
         <v>0</v>
       </c>
       <c r="E394" s="2">
@@ -9752,11 +9752,11 @@
         <v>0.0</v>
       </c>
       <c r="C395" s="2">
-        <f>IF(B395&gt;0,ROUND(B395*$B$5/12,2),0)</f>
+        <f>IF(B395&gt;0.005,ROUND(B395*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D395" s="2">
-        <f>IF(B395&gt;0,MIN($B$6+$B$7,B395+C395),0)</f>
+        <f>IF(B395&gt;0.005,MIN($B$6+$B$7,B395+C395),0)</f>
         <v>0</v>
       </c>
       <c r="E395" s="2">
@@ -9777,11 +9777,11 @@
         <v>0.0</v>
       </c>
       <c r="C396" s="2">
-        <f>IF(B396&gt;0,ROUND(B396*$B$5/12,2),0)</f>
+        <f>IF(B396&gt;0.005,ROUND(B396*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D396" s="2">
-        <f>IF(B396&gt;0,MIN($B$6+$B$7,B396+C396),0)</f>
+        <f>IF(B396&gt;0.005,MIN($B$6+$B$7,B396+C396),0)</f>
         <v>0</v>
       </c>
       <c r="E396" s="2">
@@ -9802,11 +9802,11 @@
         <v>0.0</v>
       </c>
       <c r="C397" s="2">
-        <f>IF(B397&gt;0,ROUND(B397*$B$5/12,2),0)</f>
+        <f>IF(B397&gt;0.005,ROUND(B397*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D397" s="2">
-        <f>IF(B397&gt;0,MIN($B$6+$B$7,B397+C397),0)</f>
+        <f>IF(B397&gt;0.005,MIN($B$6+$B$7,B397+C397),0)</f>
         <v>0</v>
       </c>
       <c r="E397" s="2">
@@ -9827,11 +9827,11 @@
         <v>0.0</v>
       </c>
       <c r="C398" s="2">
-        <f>IF(B398&gt;0,ROUND(B398*$B$5/12,2),0)</f>
+        <f>IF(B398&gt;0.005,ROUND(B398*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D398" s="2">
-        <f>IF(B398&gt;0,MIN($B$6+$B$7,B398+C398),0)</f>
+        <f>IF(B398&gt;0.005,MIN($B$6+$B$7,B398+C398),0)</f>
         <v>0</v>
       </c>
       <c r="E398" s="2">
@@ -9852,11 +9852,11 @@
         <v>0.0</v>
       </c>
       <c r="C399" s="2">
-        <f>IF(B399&gt;0,ROUND(B399*$B$5/12,2),0)</f>
+        <f>IF(B399&gt;0.005,ROUND(B399*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D399" s="2">
-        <f>IF(B399&gt;0,MIN($B$6+$B$7,B399+C399),0)</f>
+        <f>IF(B399&gt;0.005,MIN($B$6+$B$7,B399+C399),0)</f>
         <v>0</v>
       </c>
       <c r="E399" s="2">
@@ -9877,11 +9877,11 @@
         <v>0.0</v>
       </c>
       <c r="C400" s="2">
-        <f>IF(B400&gt;0,ROUND(B400*$B$5/12,2),0)</f>
+        <f>IF(B400&gt;0.005,ROUND(B400*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D400" s="2">
-        <f>IF(B400&gt;0,MIN($B$6+$B$7,B400+C400),0)</f>
+        <f>IF(B400&gt;0.005,MIN($B$6+$B$7,B400+C400),0)</f>
         <v>0</v>
       </c>
       <c r="E400" s="2">
@@ -9902,11 +9902,11 @@
         <v>0.0</v>
       </c>
       <c r="C401" s="2">
-        <f>IF(B401&gt;0,ROUND(B401*$B$5/12,2),0)</f>
+        <f>IF(B401&gt;0.005,ROUND(B401*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D401" s="2">
-        <f>IF(B401&gt;0,MIN($B$6+$B$7,B401+C401),0)</f>
+        <f>IF(B401&gt;0.005,MIN($B$6+$B$7,B401+C401),0)</f>
         <v>0</v>
       </c>
       <c r="E401" s="2">
@@ -9927,11 +9927,11 @@
         <v>0.0</v>
       </c>
       <c r="C402" s="2">
-        <f>IF(B402&gt;0,ROUND(B402*$B$5/12,2),0)</f>
+        <f>IF(B402&gt;0.005,ROUND(B402*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D402" s="2">
-        <f>IF(B402&gt;0,MIN($B$6+$B$7,B402+C402),0)</f>
+        <f>IF(B402&gt;0.005,MIN($B$6+$B$7,B402+C402),0)</f>
         <v>0</v>
       </c>
       <c r="E402" s="2">
@@ -9952,11 +9952,11 @@
         <v>0.0</v>
       </c>
       <c r="C403" s="2">
-        <f>IF(B403&gt;0,ROUND(B403*$B$5/12,2),0)</f>
+        <f>IF(B403&gt;0.005,ROUND(B403*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D403" s="2">
-        <f>IF(B403&gt;0,MIN($B$6+$B$7,B403+C403),0)</f>
+        <f>IF(B403&gt;0.005,MIN($B$6+$B$7,B403+C403),0)</f>
         <v>0</v>
       </c>
       <c r="E403" s="2">
@@ -9977,11 +9977,11 @@
         <v>0.0</v>
       </c>
       <c r="C404" s="2">
-        <f>IF(B404&gt;0,ROUND(B404*$B$5/12,2),0)</f>
+        <f>IF(B404&gt;0.005,ROUND(B404*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D404" s="2">
-        <f>IF(B404&gt;0,MIN($B$6+$B$7,B404+C404),0)</f>
+        <f>IF(B404&gt;0.005,MIN($B$6+$B$7,B404+C404),0)</f>
         <v>0</v>
       </c>
       <c r="E404" s="2">
@@ -10002,11 +10002,11 @@
         <v>0.0</v>
       </c>
       <c r="C405" s="2">
-        <f>IF(B405&gt;0,ROUND(B405*$B$5/12,2),0)</f>
+        <f>IF(B405&gt;0.005,ROUND(B405*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D405" s="2">
-        <f>IF(B405&gt;0,MIN($B$6+$B$7,B405+C405),0)</f>
+        <f>IF(B405&gt;0.005,MIN($B$6+$B$7,B405+C405),0)</f>
         <v>0</v>
       </c>
       <c r="E405" s="2">
@@ -10027,11 +10027,11 @@
         <v>0.0</v>
       </c>
       <c r="C406" s="2">
-        <f>IF(B406&gt;0,ROUND(B406*$B$5/12,2),0)</f>
+        <f>IF(B406&gt;0.005,ROUND(B406*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D406" s="2">
-        <f>IF(B406&gt;0,MIN($B$6+$B$7,B406+C406),0)</f>
+        <f>IF(B406&gt;0.005,MIN($B$6+$B$7,B406+C406),0)</f>
         <v>0</v>
       </c>
       <c r="E406" s="2">
@@ -10052,11 +10052,11 @@
         <v>0.0</v>
       </c>
       <c r="C407" s="2">
-        <f>IF(B407&gt;0,ROUND(B407*$B$5/12,2),0)</f>
+        <f>IF(B407&gt;0.005,ROUND(B407*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D407" s="2">
-        <f>IF(B407&gt;0,MIN($B$6+$B$7,B407+C407),0)</f>
+        <f>IF(B407&gt;0.005,MIN($B$6+$B$7,B407+C407),0)</f>
         <v>0</v>
       </c>
       <c r="E407" s="2">
@@ -10077,11 +10077,11 @@
         <v>0.0</v>
       </c>
       <c r="C408" s="2">
-        <f>IF(B408&gt;0,ROUND(B408*$B$5/12,2),0)</f>
+        <f>IF(B408&gt;0.005,ROUND(B408*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D408" s="2">
-        <f>IF(B408&gt;0,MIN($B$6+$B$7,B408+C408),0)</f>
+        <f>IF(B408&gt;0.005,MIN($B$6+$B$7,B408+C408),0)</f>
         <v>0</v>
       </c>
       <c r="E408" s="2">
@@ -10102,11 +10102,11 @@
         <v>0.0</v>
       </c>
       <c r="C409" s="2">
-        <f>IF(B409&gt;0,ROUND(B409*$B$5/12,2),0)</f>
+        <f>IF(B409&gt;0.005,ROUND(B409*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D409" s="2">
-        <f>IF(B409&gt;0,MIN($B$6+$B$7,B409+C409),0)</f>
+        <f>IF(B409&gt;0.005,MIN($B$6+$B$7,B409+C409),0)</f>
         <v>0</v>
       </c>
       <c r="E409" s="2">
@@ -10127,11 +10127,11 @@
         <v>0.0</v>
       </c>
       <c r="C410" s="2">
-        <f>IF(B410&gt;0,ROUND(B410*$B$5/12,2),0)</f>
+        <f>IF(B410&gt;0.005,ROUND(B410*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D410" s="2">
-        <f>IF(B410&gt;0,MIN($B$6+$B$7,B410+C410),0)</f>
+        <f>IF(B410&gt;0.005,MIN($B$6+$B$7,B410+C410),0)</f>
         <v>0</v>
       </c>
       <c r="E410" s="2">
@@ -10152,11 +10152,11 @@
         <v>0.0</v>
       </c>
       <c r="C411" s="2">
-        <f>IF(B411&gt;0,ROUND(B411*$B$5/12,2),0)</f>
+        <f>IF(B411&gt;0.005,ROUND(B411*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D411" s="2">
-        <f>IF(B411&gt;0,MIN($B$6+$B$7,B411+C411),0)</f>
+        <f>IF(B411&gt;0.005,MIN($B$6+$B$7,B411+C411),0)</f>
         <v>0</v>
       </c>
       <c r="E411" s="2">
@@ -10177,11 +10177,11 @@
         <v>0.0</v>
       </c>
       <c r="C412" s="2">
-        <f>IF(B412&gt;0,ROUND(B412*$B$5/12,2),0)</f>
+        <f>IF(B412&gt;0.005,ROUND(B412*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D412" s="2">
-        <f>IF(B412&gt;0,MIN($B$6+$B$7,B412+C412),0)</f>
+        <f>IF(B412&gt;0.005,MIN($B$6+$B$7,B412+C412),0)</f>
         <v>0</v>
       </c>
       <c r="E412" s="2">
@@ -10202,11 +10202,11 @@
         <v>0.0</v>
       </c>
       <c r="C413" s="2">
-        <f>IF(B413&gt;0,ROUND(B413*$B$5/12,2),0)</f>
+        <f>IF(B413&gt;0.005,ROUND(B413*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D413" s="2">
-        <f>IF(B413&gt;0,MIN($B$6+$B$7,B413+C413),0)</f>
+        <f>IF(B413&gt;0.005,MIN($B$6+$B$7,B413+C413),0)</f>
         <v>0</v>
       </c>
       <c r="E413" s="2">
@@ -10227,11 +10227,11 @@
         <v>0.0</v>
       </c>
       <c r="C414" s="2">
-        <f>IF(B414&gt;0,ROUND(B414*$B$5/12,2),0)</f>
+        <f>IF(B414&gt;0.005,ROUND(B414*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D414" s="2">
-        <f>IF(B414&gt;0,MIN($B$6+$B$7,B414+C414),0)</f>
+        <f>IF(B414&gt;0.005,MIN($B$6+$B$7,B414+C414),0)</f>
         <v>0</v>
       </c>
       <c r="E414" s="2">
@@ -10252,11 +10252,11 @@
         <v>0.0</v>
       </c>
       <c r="C415" s="2">
-        <f>IF(B415&gt;0,ROUND(B415*$B$5/12,2),0)</f>
+        <f>IF(B415&gt;0.005,ROUND(B415*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D415" s="2">
-        <f>IF(B415&gt;0,MIN($B$6+$B$7,B415+C415),0)</f>
+        <f>IF(B415&gt;0.005,MIN($B$6+$B$7,B415+C415),0)</f>
         <v>0</v>
       </c>
       <c r="E415" s="2">
@@ -10277,11 +10277,11 @@
         <v>0.0</v>
       </c>
       <c r="C416" s="2">
-        <f>IF(B416&gt;0,ROUND(B416*$B$5/12,2),0)</f>
+        <f>IF(B416&gt;0.005,ROUND(B416*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D416" s="2">
-        <f>IF(B416&gt;0,MIN($B$6+$B$7,B416+C416),0)</f>
+        <f>IF(B416&gt;0.005,MIN($B$6+$B$7,B416+C416),0)</f>
         <v>0</v>
       </c>
       <c r="E416" s="2">
@@ -10302,11 +10302,11 @@
         <v>0.0</v>
       </c>
       <c r="C417" s="2">
-        <f>IF(B417&gt;0,ROUND(B417*$B$5/12,2),0)</f>
+        <f>IF(B417&gt;0.005,ROUND(B417*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D417" s="2">
-        <f>IF(B417&gt;0,MIN($B$6+$B$7,B417+C417),0)</f>
+        <f>IF(B417&gt;0.005,MIN($B$6+$B$7,B417+C417),0)</f>
         <v>0</v>
       </c>
       <c r="E417" s="2">
@@ -10327,11 +10327,11 @@
         <v>0.0</v>
       </c>
       <c r="C418" s="2">
-        <f>IF(B418&gt;0,ROUND(B418*$B$5/12,2),0)</f>
+        <f>IF(B418&gt;0.005,ROUND(B418*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D418" s="2">
-        <f>IF(B418&gt;0,MIN($B$6+$B$7,B418+C418),0)</f>
+        <f>IF(B418&gt;0.005,MIN($B$6+$B$7,B418+C418),0)</f>
         <v>0</v>
       </c>
       <c r="E418" s="2">
@@ -10352,11 +10352,11 @@
         <v>0.0</v>
       </c>
       <c r="C419" s="2">
-        <f>IF(B419&gt;0,ROUND(B419*$B$5/12,2),0)</f>
+        <f>IF(B419&gt;0.005,ROUND(B419*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D419" s="2">
-        <f>IF(B419&gt;0,MIN($B$6+$B$7,B419+C419),0)</f>
+        <f>IF(B419&gt;0.005,MIN($B$6+$B$7,B419+C419),0)</f>
         <v>0</v>
       </c>
       <c r="E419" s="2">
@@ -10377,11 +10377,11 @@
         <v>0.0</v>
       </c>
       <c r="C420" s="2">
-        <f>IF(B420&gt;0,ROUND(B420*$B$5/12,2),0)</f>
+        <f>IF(B420&gt;0.005,ROUND(B420*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D420" s="2">
-        <f>IF(B420&gt;0,MIN($B$6+$B$7,B420+C420),0)</f>
+        <f>IF(B420&gt;0.005,MIN($B$6+$B$7,B420+C420),0)</f>
         <v>0</v>
       </c>
       <c r="E420" s="2">
@@ -10402,11 +10402,11 @@
         <v>0.0</v>
       </c>
       <c r="C421" s="2">
-        <f>IF(B421&gt;0,ROUND(B421*$B$5/12,2),0)</f>
+        <f>IF(B421&gt;0.005,ROUND(B421*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D421" s="2">
-        <f>IF(B421&gt;0,MIN($B$6+$B$7,B421+C421),0)</f>
+        <f>IF(B421&gt;0.005,MIN($B$6+$B$7,B421+C421),0)</f>
         <v>0</v>
       </c>
       <c r="E421" s="2">
@@ -10427,11 +10427,11 @@
         <v>0.0</v>
       </c>
       <c r="C422" s="2">
-        <f>IF(B422&gt;0,ROUND(B422*$B$5/12,2),0)</f>
+        <f>IF(B422&gt;0.005,ROUND(B422*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D422" s="2">
-        <f>IF(B422&gt;0,MIN($B$6+$B$7,B422+C422),0)</f>
+        <f>IF(B422&gt;0.005,MIN($B$6+$B$7,B422+C422),0)</f>
         <v>0</v>
       </c>
       <c r="E422" s="2">
@@ -10452,11 +10452,11 @@
         <v>0.0</v>
       </c>
       <c r="C423" s="2">
-        <f>IF(B423&gt;0,ROUND(B423*$B$5/12,2),0)</f>
+        <f>IF(B423&gt;0.005,ROUND(B423*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D423" s="2">
-        <f>IF(B423&gt;0,MIN($B$6+$B$7,B423+C423),0)</f>
+        <f>IF(B423&gt;0.005,MIN($B$6+$B$7,B423+C423),0)</f>
         <v>0</v>
       </c>
       <c r="E423" s="2">
@@ -10477,11 +10477,11 @@
         <v>0.0</v>
       </c>
       <c r="C424" s="2">
-        <f>IF(B424&gt;0,ROUND(B424*$B$5/12,2),0)</f>
+        <f>IF(B424&gt;0.005,ROUND(B424*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D424" s="2">
-        <f>IF(B424&gt;0,MIN($B$6+$B$7,B424+C424),0)</f>
+        <f>IF(B424&gt;0.005,MIN($B$6+$B$7,B424+C424),0)</f>
         <v>0</v>
       </c>
       <c r="E424" s="2">
@@ -10502,11 +10502,11 @@
         <v>0.0</v>
       </c>
       <c r="C425" s="2">
-        <f>IF(B425&gt;0,ROUND(B425*$B$5/12,2),0)</f>
+        <f>IF(B425&gt;0.005,ROUND(B425*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D425" s="2">
-        <f>IF(B425&gt;0,MIN($B$6+$B$7,B425+C425),0)</f>
+        <f>IF(B425&gt;0.005,MIN($B$6+$B$7,B425+C425),0)</f>
         <v>0</v>
       </c>
       <c r="E425" s="2">
@@ -10527,11 +10527,11 @@
         <v>0.0</v>
       </c>
       <c r="C426" s="2">
-        <f>IF(B426&gt;0,ROUND(B426*$B$5/12,2),0)</f>
+        <f>IF(B426&gt;0.005,ROUND(B426*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D426" s="2">
-        <f>IF(B426&gt;0,MIN($B$6+$B$7,B426+C426),0)</f>
+        <f>IF(B426&gt;0.005,MIN($B$6+$B$7,B426+C426),0)</f>
         <v>0</v>
       </c>
       <c r="E426" s="2">
@@ -10552,11 +10552,11 @@
         <v>0.0</v>
       </c>
       <c r="C427" s="2">
-        <f>IF(B427&gt;0,ROUND(B427*$B$5/12,2),0)</f>
+        <f>IF(B427&gt;0.005,ROUND(B427*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D427" s="2">
-        <f>IF(B427&gt;0,MIN($B$6+$B$7,B427+C427),0)</f>
+        <f>IF(B427&gt;0.005,MIN($B$6+$B$7,B427+C427),0)</f>
         <v>0</v>
       </c>
       <c r="E427" s="2">
@@ -10577,11 +10577,11 @@
         <v>0.0</v>
       </c>
       <c r="C428" s="2">
-        <f>IF(B428&gt;0,ROUND(B428*$B$5/12,2),0)</f>
+        <f>IF(B428&gt;0.005,ROUND(B428*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D428" s="2">
-        <f>IF(B428&gt;0,MIN($B$6+$B$7,B428+C428),0)</f>
+        <f>IF(B428&gt;0.005,MIN($B$6+$B$7,B428+C428),0)</f>
         <v>0</v>
       </c>
       <c r="E428" s="2">
@@ -10602,11 +10602,11 @@
         <v>0.0</v>
       </c>
       <c r="C429" s="2">
-        <f>IF(B429&gt;0,ROUND(B429*$B$5/12,2),0)</f>
+        <f>IF(B429&gt;0.005,ROUND(B429*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D429" s="2">
-        <f>IF(B429&gt;0,MIN($B$6+$B$7,B429+C429),0)</f>
+        <f>IF(B429&gt;0.005,MIN($B$6+$B$7,B429+C429),0)</f>
         <v>0</v>
       </c>
       <c r="E429" s="2">
@@ -10627,11 +10627,11 @@
         <v>0.0</v>
       </c>
       <c r="C430" s="2">
-        <f>IF(B430&gt;0,ROUND(B430*$B$5/12,2),0)</f>
+        <f>IF(B430&gt;0.005,ROUND(B430*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D430" s="2">
-        <f>IF(B430&gt;0,MIN($B$6+$B$7,B430+C430),0)</f>
+        <f>IF(B430&gt;0.005,MIN($B$6+$B$7,B430+C430),0)</f>
         <v>0</v>
       </c>
       <c r="E430" s="2">
@@ -10652,11 +10652,11 @@
         <v>0.0</v>
       </c>
       <c r="C431" s="2">
-        <f>IF(B431&gt;0,ROUND(B431*$B$5/12,2),0)</f>
+        <f>IF(B431&gt;0.005,ROUND(B431*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D431" s="2">
-        <f>IF(B431&gt;0,MIN($B$6+$B$7,B431+C431),0)</f>
+        <f>IF(B431&gt;0.005,MIN($B$6+$B$7,B431+C431),0)</f>
         <v>0</v>
       </c>
       <c r="E431" s="2">
@@ -10677,11 +10677,11 @@
         <v>0.0</v>
       </c>
       <c r="C432" s="2">
-        <f>IF(B432&gt;0,ROUND(B432*$B$5/12,2),0)</f>
+        <f>IF(B432&gt;0.005,ROUND(B432*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D432" s="2">
-        <f>IF(B432&gt;0,MIN($B$6+$B$7,B432+C432),0)</f>
+        <f>IF(B432&gt;0.005,MIN($B$6+$B$7,B432+C432),0)</f>
         <v>0</v>
       </c>
       <c r="E432" s="2">
@@ -10702,11 +10702,11 @@
         <v>0.0</v>
       </c>
       <c r="C433" s="2">
-        <f>IF(B433&gt;0,ROUND(B433*$B$5/12,2),0)</f>
+        <f>IF(B433&gt;0.005,ROUND(B433*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D433" s="2">
-        <f>IF(B433&gt;0,MIN($B$6+$B$7,B433+C433),0)</f>
+        <f>IF(B433&gt;0.005,MIN($B$6+$B$7,B433+C433),0)</f>
         <v>0</v>
       </c>
       <c r="E433" s="2">
@@ -10727,11 +10727,11 @@
         <v>0.0</v>
       </c>
       <c r="C434" s="2">
-        <f>IF(B434&gt;0,ROUND(B434*$B$5/12,2),0)</f>
+        <f>IF(B434&gt;0.005,ROUND(B434*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D434" s="2">
-        <f>IF(B434&gt;0,MIN($B$6+$B$7,B434+C434),0)</f>
+        <f>IF(B434&gt;0.005,MIN($B$6+$B$7,B434+C434),0)</f>
         <v>0</v>
       </c>
       <c r="E434" s="2">
@@ -10752,11 +10752,11 @@
         <v>0.0</v>
       </c>
       <c r="C435" s="2">
-        <f>IF(B435&gt;0,ROUND(B435*$B$5/12,2),0)</f>
+        <f>IF(B435&gt;0.005,ROUND(B435*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D435" s="2">
-        <f>IF(B435&gt;0,MIN($B$6+$B$7,B435+C435),0)</f>
+        <f>IF(B435&gt;0.005,MIN($B$6+$B$7,B435+C435),0)</f>
         <v>0</v>
       </c>
       <c r="E435" s="2">
@@ -10777,11 +10777,11 @@
         <v>0.0</v>
       </c>
       <c r="C436" s="2">
-        <f>IF(B436&gt;0,ROUND(B436*$B$5/12,2),0)</f>
+        <f>IF(B436&gt;0.005,ROUND(B436*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D436" s="2">
-        <f>IF(B436&gt;0,MIN($B$6+$B$7,B436+C436),0)</f>
+        <f>IF(B436&gt;0.005,MIN($B$6+$B$7,B436+C436),0)</f>
         <v>0</v>
       </c>
       <c r="E436" s="2">
@@ -10802,11 +10802,11 @@
         <v>0.0</v>
       </c>
       <c r="C437" s="2">
-        <f>IF(B437&gt;0,ROUND(B437*$B$5/12,2),0)</f>
+        <f>IF(B437&gt;0.005,ROUND(B437*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D437" s="2">
-        <f>IF(B437&gt;0,MIN($B$6+$B$7,B437+C437),0)</f>
+        <f>IF(B437&gt;0.005,MIN($B$6+$B$7,B437+C437),0)</f>
         <v>0</v>
       </c>
       <c r="E437" s="2">
@@ -10827,11 +10827,11 @@
         <v>0.0</v>
       </c>
       <c r="C438" s="2">
-        <f>IF(B438&gt;0,ROUND(B438*$B$5/12,2),0)</f>
+        <f>IF(B438&gt;0.005,ROUND(B438*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D438" s="2">
-        <f>IF(B438&gt;0,MIN($B$6+$B$7,B438+C438),0)</f>
+        <f>IF(B438&gt;0.005,MIN($B$6+$B$7,B438+C438),0)</f>
         <v>0</v>
       </c>
       <c r="E438" s="2">
@@ -10852,11 +10852,11 @@
         <v>0.0</v>
       </c>
       <c r="C439" s="2">
-        <f>IF(B439&gt;0,ROUND(B439*$B$5/12,2),0)</f>
+        <f>IF(B439&gt;0.005,ROUND(B439*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D439" s="2">
-        <f>IF(B439&gt;0,MIN($B$6+$B$7,B439+C439),0)</f>
+        <f>IF(B439&gt;0.005,MIN($B$6+$B$7,B439+C439),0)</f>
         <v>0</v>
       </c>
       <c r="E439" s="2">
@@ -10877,11 +10877,11 @@
         <v>0.0</v>
       </c>
       <c r="C440" s="2">
-        <f>IF(B440&gt;0,ROUND(B440*$B$5/12,2),0)</f>
+        <f>IF(B440&gt;0.005,ROUND(B440*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D440" s="2">
-        <f>IF(B440&gt;0,MIN($B$6+$B$7,B440+C440),0)</f>
+        <f>IF(B440&gt;0.005,MIN($B$6+$B$7,B440+C440),0)</f>
         <v>0</v>
       </c>
       <c r="E440" s="2">
@@ -10902,11 +10902,11 @@
         <v>0.0</v>
       </c>
       <c r="C441" s="2">
-        <f>IF(B441&gt;0,ROUND(B441*$B$5/12,2),0)</f>
+        <f>IF(B441&gt;0.005,ROUND(B441*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D441" s="2">
-        <f>IF(B441&gt;0,MIN($B$6+$B$7,B441+C441),0)</f>
+        <f>IF(B441&gt;0.005,MIN($B$6+$B$7,B441+C441),0)</f>
         <v>0</v>
       </c>
       <c r="E441" s="2">
@@ -10927,11 +10927,11 @@
         <v>0.0</v>
       </c>
       <c r="C442" s="2">
-        <f>IF(B442&gt;0,ROUND(B442*$B$5/12,2),0)</f>
+        <f>IF(B442&gt;0.005,ROUND(B442*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D442" s="2">
-        <f>IF(B442&gt;0,MIN($B$6+$B$7,B442+C442),0)</f>
+        <f>IF(B442&gt;0.005,MIN($B$6+$B$7,B442+C442),0)</f>
         <v>0</v>
       </c>
       <c r="E442" s="2">
@@ -10952,11 +10952,11 @@
         <v>0.0</v>
       </c>
       <c r="C443" s="2">
-        <f>IF(B443&gt;0,ROUND(B443*$B$5/12,2),0)</f>
+        <f>IF(B443&gt;0.005,ROUND(B443*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D443" s="2">
-        <f>IF(B443&gt;0,MIN($B$6+$B$7,B443+C443),0)</f>
+        <f>IF(B443&gt;0.005,MIN($B$6+$B$7,B443+C443),0)</f>
         <v>0</v>
       </c>
       <c r="E443" s="2">
@@ -10977,11 +10977,11 @@
         <v>0.0</v>
       </c>
       <c r="C444" s="2">
-        <f>IF(B444&gt;0,ROUND(B444*$B$5/12,2),0)</f>
+        <f>IF(B444&gt;0.005,ROUND(B444*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D444" s="2">
-        <f>IF(B444&gt;0,MIN($B$6+$B$7,B444+C444),0)</f>
+        <f>IF(B444&gt;0.005,MIN($B$6+$B$7,B444+C444),0)</f>
         <v>0</v>
       </c>
       <c r="E444" s="2">
@@ -11002,11 +11002,11 @@
         <v>0.0</v>
       </c>
       <c r="C445" s="2">
-        <f>IF(B445&gt;0,ROUND(B445*$B$5/12,2),0)</f>
+        <f>IF(B445&gt;0.005,ROUND(B445*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D445" s="2">
-        <f>IF(B445&gt;0,MIN($B$6+$B$7,B445+C445),0)</f>
+        <f>IF(B445&gt;0.005,MIN($B$6+$B$7,B445+C445),0)</f>
         <v>0</v>
       </c>
       <c r="E445" s="2">
@@ -11027,11 +11027,11 @@
         <v>0.0</v>
       </c>
       <c r="C446" s="2">
-        <f>IF(B446&gt;0,ROUND(B446*$B$5/12,2),0)</f>
+        <f>IF(B446&gt;0.005,ROUND(B446*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D446" s="2">
-        <f>IF(B446&gt;0,MIN($B$6+$B$7,B446+C446),0)</f>
+        <f>IF(B446&gt;0.005,MIN($B$6+$B$7,B446+C446),0)</f>
         <v>0</v>
       </c>
       <c r="E446" s="2">
@@ -11052,11 +11052,11 @@
         <v>0.0</v>
       </c>
       <c r="C447" s="2">
-        <f>IF(B447&gt;0,ROUND(B447*$B$5/12,2),0)</f>
+        <f>IF(B447&gt;0.005,ROUND(B447*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D447" s="2">
-        <f>IF(B447&gt;0,MIN($B$6+$B$7,B447+C447),0)</f>
+        <f>IF(B447&gt;0.005,MIN($B$6+$B$7,B447+C447),0)</f>
         <v>0</v>
       </c>
       <c r="E447" s="2">
@@ -11077,11 +11077,11 @@
         <v>0.0</v>
       </c>
       <c r="C448" s="2">
-        <f>IF(B448&gt;0,ROUND(B448*$B$5/12,2),0)</f>
+        <f>IF(B448&gt;0.005,ROUND(B448*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D448" s="2">
-        <f>IF(B448&gt;0,MIN($B$6+$B$7,B448+C448),0)</f>
+        <f>IF(B448&gt;0.005,MIN($B$6+$B$7,B448+C448),0)</f>
         <v>0</v>
       </c>
       <c r="E448" s="2">
@@ -11102,11 +11102,11 @@
         <v>0.0</v>
       </c>
       <c r="C449" s="2">
-        <f>IF(B449&gt;0,ROUND(B449*$B$5/12,2),0)</f>
+        <f>IF(B449&gt;0.005,ROUND(B449*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D449" s="2">
-        <f>IF(B449&gt;0,MIN($B$6+$B$7,B449+C449),0)</f>
+        <f>IF(B449&gt;0.005,MIN($B$6+$B$7,B449+C449),0)</f>
         <v>0</v>
       </c>
       <c r="E449" s="2">
@@ -11127,11 +11127,11 @@
         <v>0.0</v>
       </c>
       <c r="C450" s="2">
-        <f>IF(B450&gt;0,ROUND(B450*$B$5/12,2),0)</f>
+        <f>IF(B450&gt;0.005,ROUND(B450*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D450" s="2">
-        <f>IF(B450&gt;0,MIN($B$6+$B$7,B450+C450),0)</f>
+        <f>IF(B450&gt;0.005,MIN($B$6+$B$7,B450+C450),0)</f>
         <v>0</v>
       </c>
       <c r="E450" s="2">
@@ -11152,11 +11152,11 @@
         <v>0.0</v>
       </c>
       <c r="C451" s="2">
-        <f>IF(B451&gt;0,ROUND(B451*$B$5/12,2),0)</f>
+        <f>IF(B451&gt;0.005,ROUND(B451*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D451" s="2">
-        <f>IF(B451&gt;0,MIN($B$6+$B$7,B451+C451),0)</f>
+        <f>IF(B451&gt;0.005,MIN($B$6+$B$7,B451+C451),0)</f>
         <v>0</v>
       </c>
       <c r="E451" s="2">
@@ -11177,11 +11177,11 @@
         <v>0.0</v>
       </c>
       <c r="C452" s="2">
-        <f>IF(B452&gt;0,ROUND(B452*$B$5/12,2),0)</f>
+        <f>IF(B452&gt;0.005,ROUND(B452*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D452" s="2">
-        <f>IF(B452&gt;0,MIN($B$6+$B$7,B452+C452),0)</f>
+        <f>IF(B452&gt;0.005,MIN($B$6+$B$7,B452+C452),0)</f>
         <v>0</v>
       </c>
       <c r="E452" s="2">
@@ -11202,11 +11202,11 @@
         <v>0.0</v>
       </c>
       <c r="C453" s="2">
-        <f>IF(B453&gt;0,ROUND(B453*$B$5/12,2),0)</f>
+        <f>IF(B453&gt;0.005,ROUND(B453*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D453" s="2">
-        <f>IF(B453&gt;0,MIN($B$6+$B$7,B453+C453),0)</f>
+        <f>IF(B453&gt;0.005,MIN($B$6+$B$7,B453+C453),0)</f>
         <v>0</v>
       </c>
       <c r="E453" s="2">
@@ -11227,11 +11227,11 @@
         <v>0.0</v>
       </c>
       <c r="C454" s="2">
-        <f>IF(B454&gt;0,ROUND(B454*$B$5/12,2),0)</f>
+        <f>IF(B454&gt;0.005,ROUND(B454*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D454" s="2">
-        <f>IF(B454&gt;0,MIN($B$6+$B$7,B454+C454),0)</f>
+        <f>IF(B454&gt;0.005,MIN($B$6+$B$7,B454+C454),0)</f>
         <v>0</v>
       </c>
       <c r="E454" s="2">
@@ -11252,11 +11252,11 @@
         <v>0.0</v>
       </c>
       <c r="C455" s="2">
-        <f>IF(B455&gt;0,ROUND(B455*$B$5/12,2),0)</f>
+        <f>IF(B455&gt;0.005,ROUND(B455*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D455" s="2">
-        <f>IF(B455&gt;0,MIN($B$6+$B$7,B455+C455),0)</f>
+        <f>IF(B455&gt;0.005,MIN($B$6+$B$7,B455+C455),0)</f>
         <v>0</v>
       </c>
       <c r="E455" s="2">
@@ -11277,11 +11277,11 @@
         <v>0.0</v>
       </c>
       <c r="C456" s="2">
-        <f>IF(B456&gt;0,ROUND(B456*$B$5/12,2),0)</f>
+        <f>IF(B456&gt;0.005,ROUND(B456*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D456" s="2">
-        <f>IF(B456&gt;0,MIN($B$6+$B$7,B456+C456),0)</f>
+        <f>IF(B456&gt;0.005,MIN($B$6+$B$7,B456+C456),0)</f>
         <v>0</v>
       </c>
       <c r="E456" s="2">
@@ -11302,11 +11302,11 @@
         <v>0.0</v>
       </c>
       <c r="C457" s="2">
-        <f>IF(B457&gt;0,ROUND(B457*$B$5/12,2),0)</f>
+        <f>IF(B457&gt;0.005,ROUND(B457*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D457" s="2">
-        <f>IF(B457&gt;0,MIN($B$6+$B$7,B457+C457),0)</f>
+        <f>IF(B457&gt;0.005,MIN($B$6+$B$7,B457+C457),0)</f>
         <v>0</v>
       </c>
       <c r="E457" s="2">
@@ -11327,11 +11327,11 @@
         <v>0.0</v>
       </c>
       <c r="C458" s="2">
-        <f>IF(B458&gt;0,ROUND(B458*$B$5/12,2),0)</f>
+        <f>IF(B458&gt;0.005,ROUND(B458*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D458" s="2">
-        <f>IF(B458&gt;0,MIN($B$6+$B$7,B458+C458),0)</f>
+        <f>IF(B458&gt;0.005,MIN($B$6+$B$7,B458+C458),0)</f>
         <v>0</v>
       </c>
       <c r="E458" s="2">
@@ -11352,11 +11352,11 @@
         <v>0.0</v>
       </c>
       <c r="C459" s="2">
-        <f>IF(B459&gt;0,ROUND(B459*$B$5/12,2),0)</f>
+        <f>IF(B459&gt;0.005,ROUND(B459*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D459" s="2">
-        <f>IF(B459&gt;0,MIN($B$6+$B$7,B459+C459),0)</f>
+        <f>IF(B459&gt;0.005,MIN($B$6+$B$7,B459+C459),0)</f>
         <v>0</v>
       </c>
       <c r="E459" s="2">
@@ -11377,11 +11377,11 @@
         <v>0.0</v>
       </c>
       <c r="C460" s="2">
-        <f>IF(B460&gt;0,ROUND(B460*$B$5/12,2),0)</f>
+        <f>IF(B460&gt;0.005,ROUND(B460*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D460" s="2">
-        <f>IF(B460&gt;0,MIN($B$6+$B$7,B460+C460),0)</f>
+        <f>IF(B460&gt;0.005,MIN($B$6+$B$7,B460+C460),0)</f>
         <v>0</v>
       </c>
       <c r="E460" s="2">
@@ -11402,11 +11402,11 @@
         <v>0.0</v>
       </c>
       <c r="C461" s="2">
-        <f>IF(B461&gt;0,ROUND(B461*$B$5/12,2),0)</f>
+        <f>IF(B461&gt;0.005,ROUND(B461*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D461" s="2">
-        <f>IF(B461&gt;0,MIN($B$6+$B$7,B461+C461),0)</f>
+        <f>IF(B461&gt;0.005,MIN($B$6+$B$7,B461+C461),0)</f>
         <v>0</v>
       </c>
       <c r="E461" s="2">
@@ -11427,11 +11427,11 @@
         <v>0.0</v>
       </c>
       <c r="C462" s="2">
-        <f>IF(B462&gt;0,ROUND(B462*$B$5/12,2),0)</f>
+        <f>IF(B462&gt;0.005,ROUND(B462*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D462" s="2">
-        <f>IF(B462&gt;0,MIN($B$6+$B$7,B462+C462),0)</f>
+        <f>IF(B462&gt;0.005,MIN($B$6+$B$7,B462+C462),0)</f>
         <v>0</v>
       </c>
       <c r="E462" s="2">
@@ -11452,11 +11452,11 @@
         <v>0.0</v>
       </c>
       <c r="C463" s="2">
-        <f>IF(B463&gt;0,ROUND(B463*$B$5/12,2),0)</f>
+        <f>IF(B463&gt;0.005,ROUND(B463*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D463" s="2">
-        <f>IF(B463&gt;0,MIN($B$6+$B$7,B463+C463),0)</f>
+        <f>IF(B463&gt;0.005,MIN($B$6+$B$7,B463+C463),0)</f>
         <v>0</v>
       </c>
       <c r="E463" s="2">
@@ -11477,11 +11477,11 @@
         <v>0.0</v>
       </c>
       <c r="C464" s="2">
-        <f>IF(B464&gt;0,ROUND(B464*$B$5/12,2),0)</f>
+        <f>IF(B464&gt;0.005,ROUND(B464*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D464" s="2">
-        <f>IF(B464&gt;0,MIN($B$6+$B$7,B464+C464),0)</f>
+        <f>IF(B464&gt;0.005,MIN($B$6+$B$7,B464+C464),0)</f>
         <v>0</v>
       </c>
       <c r="E464" s="2">
@@ -11502,11 +11502,11 @@
         <v>0.0</v>
       </c>
       <c r="C465" s="2">
-        <f>IF(B465&gt;0,ROUND(B465*$B$5/12,2),0)</f>
+        <f>IF(B465&gt;0.005,ROUND(B465*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D465" s="2">
-        <f>IF(B465&gt;0,MIN($B$6+$B$7,B465+C465),0)</f>
+        <f>IF(B465&gt;0.005,MIN($B$6+$B$7,B465+C465),0)</f>
         <v>0</v>
       </c>
       <c r="E465" s="2">
@@ -11527,11 +11527,11 @@
         <v>0.0</v>
       </c>
       <c r="C466" s="2">
-        <f>IF(B466&gt;0,ROUND(B466*$B$5/12,2),0)</f>
+        <f>IF(B466&gt;0.005,ROUND(B466*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D466" s="2">
-        <f>IF(B466&gt;0,MIN($B$6+$B$7,B466+C466),0)</f>
+        <f>IF(B466&gt;0.005,MIN($B$6+$B$7,B466+C466),0)</f>
         <v>0</v>
       </c>
       <c r="E466" s="2">
@@ -11552,11 +11552,11 @@
         <v>0.0</v>
       </c>
       <c r="C467" s="2">
-        <f>IF(B467&gt;0,ROUND(B467*$B$5/12,2),0)</f>
+        <f>IF(B467&gt;0.005,ROUND(B467*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D467" s="2">
-        <f>IF(B467&gt;0,MIN($B$6+$B$7,B467+C467),0)</f>
+        <f>IF(B467&gt;0.005,MIN($B$6+$B$7,B467+C467),0)</f>
         <v>0</v>
       </c>
       <c r="E467" s="2">
@@ -11577,11 +11577,11 @@
         <v>0.0</v>
       </c>
       <c r="C468" s="2">
-        <f>IF(B468&gt;0,ROUND(B468*$B$5/12,2),0)</f>
+        <f>IF(B468&gt;0.005,ROUND(B468*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D468" s="2">
-        <f>IF(B468&gt;0,MIN($B$6+$B$7,B468+C468),0)</f>
+        <f>IF(B468&gt;0.005,MIN($B$6+$B$7,B468+C468),0)</f>
         <v>0</v>
       </c>
       <c r="E468" s="2">
@@ -11602,11 +11602,11 @@
         <v>0.0</v>
       </c>
       <c r="C469" s="2">
-        <f>IF(B469&gt;0,ROUND(B469*$B$5/12,2),0)</f>
+        <f>IF(B469&gt;0.005,ROUND(B469*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D469" s="2">
-        <f>IF(B469&gt;0,MIN($B$6+$B$7,B469+C469),0)</f>
+        <f>IF(B469&gt;0.005,MIN($B$6+$B$7,B469+C469),0)</f>
         <v>0</v>
       </c>
       <c r="E469" s="2">
@@ -11627,11 +11627,11 @@
         <v>0.0</v>
       </c>
       <c r="C470" s="2">
-        <f>IF(B470&gt;0,ROUND(B470*$B$5/12,2),0)</f>
+        <f>IF(B470&gt;0.005,ROUND(B470*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D470" s="2">
-        <f>IF(B470&gt;0,MIN($B$6+$B$7,B470+C470),0)</f>
+        <f>IF(B470&gt;0.005,MIN($B$6+$B$7,B470+C470),0)</f>
         <v>0</v>
       </c>
       <c r="E470" s="2">
@@ -11652,11 +11652,11 @@
         <v>0.0</v>
       </c>
       <c r="C471" s="2">
-        <f>IF(B471&gt;0,ROUND(B471*$B$5/12,2),0)</f>
+        <f>IF(B471&gt;0.005,ROUND(B471*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D471" s="2">
-        <f>IF(B471&gt;0,MIN($B$6+$B$7,B471+C471),0)</f>
+        <f>IF(B471&gt;0.005,MIN($B$6+$B$7,B471+C471),0)</f>
         <v>0</v>
       </c>
       <c r="E471" s="2">
@@ -11677,11 +11677,11 @@
         <v>0.0</v>
       </c>
       <c r="C472" s="2">
-        <f>IF(B472&gt;0,ROUND(B472*$B$5/12,2),0)</f>
+        <f>IF(B472&gt;0.005,ROUND(B472*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D472" s="2">
-        <f>IF(B472&gt;0,MIN($B$6+$B$7,B472+C472),0)</f>
+        <f>IF(B472&gt;0.005,MIN($B$6+$B$7,B472+C472),0)</f>
         <v>0</v>
       </c>
       <c r="E472" s="2">
@@ -11702,11 +11702,11 @@
         <v>0.0</v>
       </c>
       <c r="C473" s="2">
-        <f>IF(B473&gt;0,ROUND(B473*$B$5/12,2),0)</f>
+        <f>IF(B473&gt;0.005,ROUND(B473*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D473" s="2">
-        <f>IF(B473&gt;0,MIN($B$6+$B$7,B473+C473),0)</f>
+        <f>IF(B473&gt;0.005,MIN($B$6+$B$7,B473+C473),0)</f>
         <v>0</v>
       </c>
       <c r="E473" s="2">
@@ -11727,11 +11727,11 @@
         <v>0.0</v>
       </c>
       <c r="C474" s="2">
-        <f>IF(B474&gt;0,ROUND(B474*$B$5/12,2),0)</f>
+        <f>IF(B474&gt;0.005,ROUND(B474*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D474" s="2">
-        <f>IF(B474&gt;0,MIN($B$6+$B$7,B474+C474),0)</f>
+        <f>IF(B474&gt;0.005,MIN($B$6+$B$7,B474+C474),0)</f>
         <v>0</v>
       </c>
       <c r="E474" s="2">
@@ -11752,11 +11752,11 @@
         <v>0.0</v>
       </c>
       <c r="C475" s="2">
-        <f>IF(B475&gt;0,ROUND(B475*$B$5/12,2),0)</f>
+        <f>IF(B475&gt;0.005,ROUND(B475*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D475" s="2">
-        <f>IF(B475&gt;0,MIN($B$6+$B$7,B475+C475),0)</f>
+        <f>IF(B475&gt;0.005,MIN($B$6+$B$7,B475+C475),0)</f>
         <v>0</v>
       </c>
       <c r="E475" s="2">
@@ -11777,11 +11777,11 @@
         <v>0.0</v>
       </c>
       <c r="C476" s="2">
-        <f>IF(B476&gt;0,ROUND(B476*$B$5/12,2),0)</f>
+        <f>IF(B476&gt;0.005,ROUND(B476*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D476" s="2">
-        <f>IF(B476&gt;0,MIN($B$6+$B$7,B476+C476),0)</f>
+        <f>IF(B476&gt;0.005,MIN($B$6+$B$7,B476+C476),0)</f>
         <v>0</v>
       </c>
       <c r="E476" s="2">
@@ -11802,11 +11802,11 @@
         <v>0.0</v>
       </c>
       <c r="C477" s="2">
-        <f>IF(B477&gt;0,ROUND(B477*$B$5/12,2),0)</f>
+        <f>IF(B477&gt;0.005,ROUND(B477*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D477" s="2">
-        <f>IF(B477&gt;0,MIN($B$6+$B$7,B477+C477),0)</f>
+        <f>IF(B477&gt;0.005,MIN($B$6+$B$7,B477+C477),0)</f>
         <v>0</v>
       </c>
       <c r="E477" s="2">
@@ -11827,11 +11827,11 @@
         <v>0.0</v>
       </c>
       <c r="C478" s="2">
-        <f>IF(B478&gt;0,ROUND(B478*$B$5/12,2),0)</f>
+        <f>IF(B478&gt;0.005,ROUND(B478*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D478" s="2">
-        <f>IF(B478&gt;0,MIN($B$6+$B$7,B478+C478),0)</f>
+        <f>IF(B478&gt;0.005,MIN($B$6+$B$7,B478+C478),0)</f>
         <v>0</v>
       </c>
       <c r="E478" s="2">
@@ -11852,11 +11852,11 @@
         <v>0.0</v>
       </c>
       <c r="C479" s="2">
-        <f>IF(B479&gt;0,ROUND(B479*$B$5/12,2),0)</f>
+        <f>IF(B479&gt;0.005,ROUND(B479*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D479" s="2">
-        <f>IF(B479&gt;0,MIN($B$6+$B$7,B479+C479),0)</f>
+        <f>IF(B479&gt;0.005,MIN($B$6+$B$7,B479+C479),0)</f>
         <v>0</v>
       </c>
       <c r="E479" s="2">
@@ -11877,11 +11877,11 @@
         <v>0.0</v>
       </c>
       <c r="C480" s="2">
-        <f>IF(B480&gt;0,ROUND(B480*$B$5/12,2),0)</f>
+        <f>IF(B480&gt;0.005,ROUND(B480*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D480" s="2">
-        <f>IF(B480&gt;0,MIN($B$6+$B$7,B480+C480),0)</f>
+        <f>IF(B480&gt;0.005,MIN($B$6+$B$7,B480+C480),0)</f>
         <v>0</v>
       </c>
       <c r="E480" s="2">
@@ -11902,11 +11902,11 @@
         <v>0.0</v>
       </c>
       <c r="C481" s="2">
-        <f>IF(B481&gt;0,ROUND(B481*$B$5/12,2),0)</f>
+        <f>IF(B481&gt;0.005,ROUND(B481*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D481" s="2">
-        <f>IF(B481&gt;0,MIN($B$6+$B$7,B481+C481),0)</f>
+        <f>IF(B481&gt;0.005,MIN($B$6+$B$7,B481+C481),0)</f>
         <v>0</v>
       </c>
       <c r="E481" s="2">
@@ -11927,11 +11927,11 @@
         <v>0.0</v>
       </c>
       <c r="C482" s="2">
-        <f>IF(B482&gt;0,ROUND(B482*$B$5/12,2),0)</f>
+        <f>IF(B482&gt;0.005,ROUND(B482*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D482" s="2">
-        <f>IF(B482&gt;0,MIN($B$6+$B$7,B482+C482),0)</f>
+        <f>IF(B482&gt;0.005,MIN($B$6+$B$7,B482+C482),0)</f>
         <v>0</v>
       </c>
       <c r="E482" s="2">
@@ -11952,11 +11952,11 @@
         <v>0.0</v>
       </c>
       <c r="C483" s="2">
-        <f>IF(B483&gt;0,ROUND(B483*$B$5/12,2),0)</f>
+        <f>IF(B483&gt;0.005,ROUND(B483*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D483" s="2">
-        <f>IF(B483&gt;0,MIN($B$6+$B$7,B483+C483),0)</f>
+        <f>IF(B483&gt;0.005,MIN($B$6+$B$7,B483+C483),0)</f>
         <v>0</v>
       </c>
       <c r="E483" s="2">
@@ -11977,11 +11977,11 @@
         <v>0.0</v>
       </c>
       <c r="C484" s="2">
-        <f>IF(B484&gt;0,ROUND(B484*$B$5/12,2),0)</f>
+        <f>IF(B484&gt;0.005,ROUND(B484*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D484" s="2">
-        <f>IF(B484&gt;0,MIN($B$6+$B$7,B484+C484),0)</f>
+        <f>IF(B484&gt;0.005,MIN($B$6+$B$7,B484+C484),0)</f>
         <v>0</v>
       </c>
       <c r="E484" s="2">
@@ -12002,11 +12002,11 @@
         <v>0.0</v>
       </c>
       <c r="C485" s="2">
-        <f>IF(B485&gt;0,ROUND(B485*$B$5/12,2),0)</f>
+        <f>IF(B485&gt;0.005,ROUND(B485*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D485" s="2">
-        <f>IF(B485&gt;0,MIN($B$6+$B$7,B485+C485),0)</f>
+        <f>IF(B485&gt;0.005,MIN($B$6+$B$7,B485+C485),0)</f>
         <v>0</v>
       </c>
       <c r="E485" s="2">
@@ -12027,11 +12027,11 @@
         <v>0.0</v>
       </c>
       <c r="C486" s="2">
-        <f>IF(B486&gt;0,ROUND(B486*$B$5/12,2),0)</f>
+        <f>IF(B486&gt;0.005,ROUND(B486*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D486" s="2">
-        <f>IF(B486&gt;0,MIN($B$6+$B$7,B486+C486),0)</f>
+        <f>IF(B486&gt;0.005,MIN($B$6+$B$7,B486+C486),0)</f>
         <v>0</v>
       </c>
       <c r="E486" s="2">
@@ -12052,11 +12052,11 @@
         <v>0.0</v>
       </c>
       <c r="C487" s="2">
-        <f>IF(B487&gt;0,ROUND(B487*$B$5/12,2),0)</f>
+        <f>IF(B487&gt;0.005,ROUND(B487*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D487" s="2">
-        <f>IF(B487&gt;0,MIN($B$6+$B$7,B487+C487),0)</f>
+        <f>IF(B487&gt;0.005,MIN($B$6+$B$7,B487+C487),0)</f>
         <v>0</v>
       </c>
       <c r="E487" s="2">
@@ -12077,11 +12077,11 @@
         <v>0.0</v>
       </c>
       <c r="C488" s="2">
-        <f>IF(B488&gt;0,ROUND(B488*$B$5/12,2),0)</f>
+        <f>IF(B488&gt;0.005,ROUND(B488*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D488" s="2">
-        <f>IF(B488&gt;0,MIN($B$6+$B$7,B488+C488),0)</f>
+        <f>IF(B488&gt;0.005,MIN($B$6+$B$7,B488+C488),0)</f>
         <v>0</v>
       </c>
       <c r="E488" s="2">
@@ -12102,11 +12102,11 @@
         <v>0.0</v>
       </c>
       <c r="C489" s="2">
-        <f>IF(B489&gt;0,ROUND(B489*$B$5/12,2),0)</f>
+        <f>IF(B489&gt;0.005,ROUND(B489*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D489" s="2">
-        <f>IF(B489&gt;0,MIN($B$6+$B$7,B489+C489),0)</f>
+        <f>IF(B489&gt;0.005,MIN($B$6+$B$7,B489+C489),0)</f>
         <v>0</v>
       </c>
       <c r="E489" s="2">
@@ -12127,11 +12127,11 @@
         <v>0.0</v>
       </c>
       <c r="C490" s="2">
-        <f>IF(B490&gt;0,ROUND(B490*$B$5/12,2),0)</f>
+        <f>IF(B490&gt;0.005,ROUND(B490*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D490" s="2">
-        <f>IF(B490&gt;0,MIN($B$6+$B$7,B490+C490),0)</f>
+        <f>IF(B490&gt;0.005,MIN($B$6+$B$7,B490+C490),0)</f>
         <v>0</v>
       </c>
       <c r="E490" s="2">
@@ -12152,11 +12152,11 @@
         <v>0.0</v>
       </c>
       <c r="C491" s="2">
-        <f>IF(B491&gt;0,ROUND(B491*$B$5/12,2),0)</f>
+        <f>IF(B491&gt;0.005,ROUND(B491*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D491" s="2">
-        <f>IF(B491&gt;0,MIN($B$6+$B$7,B491+C491),0)</f>
+        <f>IF(B491&gt;0.005,MIN($B$6+$B$7,B491+C491),0)</f>
         <v>0</v>
       </c>
       <c r="E491" s="2">
@@ -12177,11 +12177,11 @@
         <v>0.0</v>
       </c>
       <c r="C492" s="2">
-        <f>IF(B492&gt;0,ROUND(B492*$B$5/12,2),0)</f>
+        <f>IF(B492&gt;0.005,ROUND(B492*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D492" s="2">
-        <f>IF(B492&gt;0,MIN($B$6+$B$7,B492+C492),0)</f>
+        <f>IF(B492&gt;0.005,MIN($B$6+$B$7,B492+C492),0)</f>
         <v>0</v>
       </c>
       <c r="E492" s="2">
@@ -12202,11 +12202,11 @@
         <v>0.0</v>
       </c>
       <c r="C493" s="2">
-        <f>IF(B493&gt;0,ROUND(B493*$B$5/12,2),0)</f>
+        <f>IF(B493&gt;0.005,ROUND(B493*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D493" s="2">
-        <f>IF(B493&gt;0,MIN($B$6+$B$7,B493+C493),0)</f>
+        <f>IF(B493&gt;0.005,MIN($B$6+$B$7,B493+C493),0)</f>
         <v>0</v>
       </c>
       <c r="E493" s="2">
@@ -12227,11 +12227,11 @@
         <v>0.0</v>
       </c>
       <c r="C494" s="2">
-        <f>IF(B494&gt;0,ROUND(B494*$B$5/12,2),0)</f>
+        <f>IF(B494&gt;0.005,ROUND(B494*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D494" s="2">
-        <f>IF(B494&gt;0,MIN($B$6+$B$7,B494+C494),0)</f>
+        <f>IF(B494&gt;0.005,MIN($B$6+$B$7,B494+C494),0)</f>
         <v>0</v>
       </c>
       <c r="E494" s="2">
@@ -12252,11 +12252,11 @@
         <v>0.0</v>
       </c>
       <c r="C495" s="2">
-        <f>IF(B495&gt;0,ROUND(B495*$B$5/12,2),0)</f>
+        <f>IF(B495&gt;0.005,ROUND(B495*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D495" s="2">
-        <f>IF(B495&gt;0,MIN($B$6+$B$7,B495+C495),0)</f>
+        <f>IF(B495&gt;0.005,MIN($B$6+$B$7,B495+C495),0)</f>
         <v>0</v>
       </c>
       <c r="E495" s="2">
@@ -12277,11 +12277,11 @@
         <v>0.0</v>
       </c>
       <c r="C496" s="2">
-        <f>IF(B496&gt;0,ROUND(B496*$B$5/12,2),0)</f>
+        <f>IF(B496&gt;0.005,ROUND(B496*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D496" s="2">
-        <f>IF(B496&gt;0,MIN($B$6+$B$7,B496+C496),0)</f>
+        <f>IF(B496&gt;0.005,MIN($B$6+$B$7,B496+C496),0)</f>
         <v>0</v>
       </c>
       <c r="E496" s="2">
@@ -12302,11 +12302,11 @@
         <v>0.0</v>
       </c>
       <c r="C497" s="2">
-        <f>IF(B497&gt;0,ROUND(B497*$B$5/12,2),0)</f>
+        <f>IF(B497&gt;0.005,ROUND(B497*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D497" s="2">
-        <f>IF(B497&gt;0,MIN($B$6+$B$7,B497+C497),0)</f>
+        <f>IF(B497&gt;0.005,MIN($B$6+$B$7,B497+C497),0)</f>
         <v>0</v>
       </c>
       <c r="E497" s="2">
@@ -12327,11 +12327,11 @@
         <v>0.0</v>
       </c>
       <c r="C498" s="2">
-        <f>IF(B498&gt;0,ROUND(B498*$B$5/12,2),0)</f>
+        <f>IF(B498&gt;0.005,ROUND(B498*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D498" s="2">
-        <f>IF(B498&gt;0,MIN($B$6+$B$7,B498+C498),0)</f>
+        <f>IF(B498&gt;0.005,MIN($B$6+$B$7,B498+C498),0)</f>
         <v>0</v>
       </c>
       <c r="E498" s="2">
@@ -12352,11 +12352,11 @@
         <v>0.0</v>
       </c>
       <c r="C499" s="2">
-        <f>IF(B499&gt;0,ROUND(B499*$B$5/12,2),0)</f>
+        <f>IF(B499&gt;0.005,ROUND(B499*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D499" s="2">
-        <f>IF(B499&gt;0,MIN($B$6+$B$7,B499+C499),0)</f>
+        <f>IF(B499&gt;0.005,MIN($B$6+$B$7,B499+C499),0)</f>
         <v>0</v>
       </c>
       <c r="E499" s="2">
@@ -12377,11 +12377,11 @@
         <v>0.0</v>
       </c>
       <c r="C500" s="2">
-        <f>IF(B500&gt;0,ROUND(B500*$B$5/12,2),0)</f>
+        <f>IF(B500&gt;0.005,ROUND(B500*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D500" s="2">
-        <f>IF(B500&gt;0,MIN($B$6+$B$7,B500+C500),0)</f>
+        <f>IF(B500&gt;0.005,MIN($B$6+$B$7,B500+C500),0)</f>
         <v>0</v>
       </c>
       <c r="E500" s="2">
@@ -12402,11 +12402,11 @@
         <v>0.0</v>
       </c>
       <c r="C501" s="2">
-        <f>IF(B501&gt;0,ROUND(B501*$B$5/12,2),0)</f>
+        <f>IF(B501&gt;0.005,ROUND(B501*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D501" s="2">
-        <f>IF(B501&gt;0,MIN($B$6+$B$7,B501+C501),0)</f>
+        <f>IF(B501&gt;0.005,MIN($B$6+$B$7,B501+C501),0)</f>
         <v>0</v>
       </c>
       <c r="E501" s="2">
@@ -12427,11 +12427,11 @@
         <v>0.0</v>
       </c>
       <c r="C502" s="2">
-        <f>IF(B502&gt;0,ROUND(B502*$B$5/12,2),0)</f>
+        <f>IF(B502&gt;0.005,ROUND(B502*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D502" s="2">
-        <f>IF(B502&gt;0,MIN($B$6+$B$7,B502+C502),0)</f>
+        <f>IF(B502&gt;0.005,MIN($B$6+$B$7,B502+C502),0)</f>
         <v>0</v>
       </c>
       <c r="E502" s="2">
@@ -12452,11 +12452,11 @@
         <v>0.0</v>
       </c>
       <c r="C503" s="2">
-        <f>IF(B503&gt;0,ROUND(B503*$B$5/12,2),0)</f>
+        <f>IF(B503&gt;0.005,ROUND(B503*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D503" s="2">
-        <f>IF(B503&gt;0,MIN($B$6+$B$7,B503+C503),0)</f>
+        <f>IF(B503&gt;0.005,MIN($B$6+$B$7,B503+C503),0)</f>
         <v>0</v>
       </c>
       <c r="E503" s="2">
@@ -12477,11 +12477,11 @@
         <v>0.0</v>
       </c>
       <c r="C504" s="2">
-        <f>IF(B504&gt;0,ROUND(B504*$B$5/12,2),0)</f>
+        <f>IF(B504&gt;0.005,ROUND(B504*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D504" s="2">
-        <f>IF(B504&gt;0,MIN($B$6+$B$7,B504+C504),0)</f>
+        <f>IF(B504&gt;0.005,MIN($B$6+$B$7,B504+C504),0)</f>
         <v>0</v>
       </c>
       <c r="E504" s="2">
@@ -12502,11 +12502,11 @@
         <v>0.0</v>
       </c>
       <c r="C505" s="2">
-        <f>IF(B505&gt;0,ROUND(B505*$B$5/12,2),0)</f>
+        <f>IF(B505&gt;0.005,ROUND(B505*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D505" s="2">
-        <f>IF(B505&gt;0,MIN($B$6+$B$7,B505+C505),0)</f>
+        <f>IF(B505&gt;0.005,MIN($B$6+$B$7,B505+C505),0)</f>
         <v>0</v>
       </c>
       <c r="E505" s="2">
@@ -12527,11 +12527,11 @@
         <v>0.0</v>
       </c>
       <c r="C506" s="2">
-        <f>IF(B506&gt;0,ROUND(B506*$B$5/12,2),0)</f>
+        <f>IF(B506&gt;0.005,ROUND(B506*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D506" s="2">
-        <f>IF(B506&gt;0,MIN($B$6+$B$7,B506+C506),0)</f>
+        <f>IF(B506&gt;0.005,MIN($B$6+$B$7,B506+C506),0)</f>
         <v>0</v>
       </c>
       <c r="E506" s="2">
@@ -12552,11 +12552,11 @@
         <v>0.0</v>
       </c>
       <c r="C507" s="2">
-        <f>IF(B507&gt;0,ROUND(B507*$B$5/12,2),0)</f>
+        <f>IF(B507&gt;0.005,ROUND(B507*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D507" s="2">
-        <f>IF(B507&gt;0,MIN($B$6+$B$7,B507+C507),0)</f>
+        <f>IF(B507&gt;0.005,MIN($B$6+$B$7,B507+C507),0)</f>
         <v>0</v>
       </c>
       <c r="E507" s="2">
@@ -12577,11 +12577,11 @@
         <v>0.0</v>
       </c>
       <c r="C508" s="2">
-        <f>IF(B508&gt;0,ROUND(B508*$B$5/12,2),0)</f>
+        <f>IF(B508&gt;0.005,ROUND(B508*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D508" s="2">
-        <f>IF(B508&gt;0,MIN($B$6+$B$7,B508+C508),0)</f>
+        <f>IF(B508&gt;0.005,MIN($B$6+$B$7,B508+C508),0)</f>
         <v>0</v>
       </c>
       <c r="E508" s="2">
@@ -12602,11 +12602,11 @@
         <v>0.0</v>
       </c>
       <c r="C509" s="2">
-        <f>IF(B509&gt;0,ROUND(B509*$B$5/12,2),0)</f>
+        <f>IF(B509&gt;0.005,ROUND(B509*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D509" s="2">
-        <f>IF(B509&gt;0,MIN($B$6+$B$7,B509+C509),0)</f>
+        <f>IF(B509&gt;0.005,MIN($B$6+$B$7,B509+C509),0)</f>
         <v>0</v>
       </c>
       <c r="E509" s="2">
@@ -12627,11 +12627,11 @@
         <v>0.0</v>
       </c>
       <c r="C510" s="2">
-        <f>IF(B510&gt;0,ROUND(B510*$B$5/12,2),0)</f>
+        <f>IF(B510&gt;0.005,ROUND(B510*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D510" s="2">
-        <f>IF(B510&gt;0,MIN($B$6+$B$7,B510+C510),0)</f>
+        <f>IF(B510&gt;0.005,MIN($B$6+$B$7,B510+C510),0)</f>
         <v>0</v>
       </c>
       <c r="E510" s="2">
@@ -12652,11 +12652,11 @@
         <v>0.0</v>
       </c>
       <c r="C511" s="2">
-        <f>IF(B511&gt;0,ROUND(B511*$B$5/12,2),0)</f>
+        <f>IF(B511&gt;0.005,ROUND(B511*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D511" s="2">
-        <f>IF(B511&gt;0,MIN($B$6+$B$7,B511+C511),0)</f>
+        <f>IF(B511&gt;0.005,MIN($B$6+$B$7,B511+C511),0)</f>
         <v>0</v>
       </c>
       <c r="E511" s="2">
@@ -12677,11 +12677,11 @@
         <v>0.0</v>
       </c>
       <c r="C512" s="2">
-        <f>IF(B512&gt;0,ROUND(B512*$B$5/12,2),0)</f>
+        <f>IF(B512&gt;0.005,ROUND(B512*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D512" s="2">
-        <f>IF(B512&gt;0,MIN($B$6+$B$7,B512+C512),0)</f>
+        <f>IF(B512&gt;0.005,MIN($B$6+$B$7,B512+C512),0)</f>
         <v>0</v>
       </c>
       <c r="E512" s="2">
@@ -12702,11 +12702,11 @@
         <v>0.0</v>
       </c>
       <c r="C513" s="2">
-        <f>IF(B513&gt;0,ROUND(B513*$B$5/12,2),0)</f>
+        <f>IF(B513&gt;0.005,ROUND(B513*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D513" s="2">
-        <f>IF(B513&gt;0,MIN($B$6+$B$7,B513+C513),0)</f>
+        <f>IF(B513&gt;0.005,MIN($B$6+$B$7,B513+C513),0)</f>
         <v>0</v>
       </c>
       <c r="E513" s="2">
@@ -12727,11 +12727,11 @@
         <v>0.0</v>
       </c>
       <c r="C514" s="2">
-        <f>IF(B514&gt;0,ROUND(B514*$B$5/12,2),0)</f>
+        <f>IF(B514&gt;0.005,ROUND(B514*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D514" s="2">
-        <f>IF(B514&gt;0,MIN($B$6+$B$7,B514+C514),0)</f>
+        <f>IF(B514&gt;0.005,MIN($B$6+$B$7,B514+C514),0)</f>
         <v>0</v>
       </c>
       <c r="E514" s="2">
@@ -12752,11 +12752,11 @@
         <v>0.0</v>
       </c>
       <c r="C515" s="2">
-        <f>IF(B515&gt;0,ROUND(B515*$B$5/12,2),0)</f>
+        <f>IF(B515&gt;0.005,ROUND(B515*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D515" s="2">
-        <f>IF(B515&gt;0,MIN($B$6+$B$7,B515+C515),0)</f>
+        <f>IF(B515&gt;0.005,MIN($B$6+$B$7,B515+C515),0)</f>
         <v>0</v>
       </c>
       <c r="E515" s="2">
@@ -12777,11 +12777,11 @@
         <v>0.0</v>
       </c>
       <c r="C516" s="2">
-        <f>IF(B516&gt;0,ROUND(B516*$B$5/12,2),0)</f>
+        <f>IF(B516&gt;0.005,ROUND(B516*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D516" s="2">
-        <f>IF(B516&gt;0,MIN($B$6+$B$7,B516+C516),0)</f>
+        <f>IF(B516&gt;0.005,MIN($B$6+$B$7,B516+C516),0)</f>
         <v>0</v>
       </c>
       <c r="E516" s="2">
@@ -12802,11 +12802,11 @@
         <v>0.0</v>
       </c>
       <c r="C517" s="2">
-        <f>IF(B517&gt;0,ROUND(B517*$B$5/12,2),0)</f>
+        <f>IF(B517&gt;0.005,ROUND(B517*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D517" s="2">
-        <f>IF(B517&gt;0,MIN($B$6+$B$7,B517+C517),0)</f>
+        <f>IF(B517&gt;0.005,MIN($B$6+$B$7,B517+C517),0)</f>
         <v>0</v>
       </c>
       <c r="E517" s="2">
@@ -12827,11 +12827,11 @@
         <v>0.0</v>
       </c>
       <c r="C518" s="2">
-        <f>IF(B518&gt;0,ROUND(B518*$B$5/12,2),0)</f>
+        <f>IF(B518&gt;0.005,ROUND(B518*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D518" s="2">
-        <f>IF(B518&gt;0,MIN($B$6+$B$7,B518+C518),0)</f>
+        <f>IF(B518&gt;0.005,MIN($B$6+$B$7,B518+C518),0)</f>
         <v>0</v>
       </c>
       <c r="E518" s="2">
@@ -12852,11 +12852,11 @@
         <v>0.0</v>
       </c>
       <c r="C519" s="2">
-        <f>IF(B519&gt;0,ROUND(B519*$B$5/12,2),0)</f>
+        <f>IF(B519&gt;0.005,ROUND(B519*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D519" s="2">
-        <f>IF(B519&gt;0,MIN($B$6+$B$7,B519+C519),0)</f>
+        <f>IF(B519&gt;0.005,MIN($B$6+$B$7,B519+C519),0)</f>
         <v>0</v>
       </c>
       <c r="E519" s="2">
@@ -12877,11 +12877,11 @@
         <v>0.0</v>
       </c>
       <c r="C520" s="2">
-        <f>IF(B520&gt;0,ROUND(B520*$B$5/12,2),0)</f>
+        <f>IF(B520&gt;0.005,ROUND(B520*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D520" s="2">
-        <f>IF(B520&gt;0,MIN($B$6+$B$7,B520+C520),0)</f>
+        <f>IF(B520&gt;0.005,MIN($B$6+$B$7,B520+C520),0)</f>
         <v>0</v>
       </c>
       <c r="E520" s="2">
@@ -12902,11 +12902,11 @@
         <v>0.0</v>
       </c>
       <c r="C521" s="2">
-        <f>IF(B521&gt;0,ROUND(B521*$B$5/12,2),0)</f>
+        <f>IF(B521&gt;0.005,ROUND(B521*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D521" s="2">
-        <f>IF(B521&gt;0,MIN($B$6+$B$7,B521+C521),0)</f>
+        <f>IF(B521&gt;0.005,MIN($B$6+$B$7,B521+C521),0)</f>
         <v>0</v>
       </c>
       <c r="E521" s="2">
@@ -12927,11 +12927,11 @@
         <v>0.0</v>
       </c>
       <c r="C522" s="2">
-        <f>IF(B522&gt;0,ROUND(B522*$B$5/12,2),0)</f>
+        <f>IF(B522&gt;0.005,ROUND(B522*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D522" s="2">
-        <f>IF(B522&gt;0,MIN($B$6+$B$7,B522+C522),0)</f>
+        <f>IF(B522&gt;0.005,MIN($B$6+$B$7,B522+C522),0)</f>
         <v>0</v>
       </c>
       <c r="E522" s="2">
@@ -12952,11 +12952,11 @@
         <v>0.0</v>
       </c>
       <c r="C523" s="2">
-        <f>IF(B523&gt;0,ROUND(B523*$B$5/12,2),0)</f>
+        <f>IF(B523&gt;0.005,ROUND(B523*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D523" s="2">
-        <f>IF(B523&gt;0,MIN($B$6+$B$7,B523+C523),0)</f>
+        <f>IF(B523&gt;0.005,MIN($B$6+$B$7,B523+C523),0)</f>
         <v>0</v>
       </c>
       <c r="E523" s="2">
@@ -12977,11 +12977,11 @@
         <v>0.0</v>
       </c>
       <c r="C524" s="2">
-        <f>IF(B524&gt;0,ROUND(B524*$B$5/12,2),0)</f>
+        <f>IF(B524&gt;0.005,ROUND(B524*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D524" s="2">
-        <f>IF(B524&gt;0,MIN($B$6+$B$7,B524+C524),0)</f>
+        <f>IF(B524&gt;0.005,MIN($B$6+$B$7,B524+C524),0)</f>
         <v>0</v>
       </c>
       <c r="E524" s="2">
@@ -13002,11 +13002,11 @@
         <v>0.0</v>
       </c>
       <c r="C525" s="2">
-        <f>IF(B525&gt;0,ROUND(B525*$B$5/12,2),0)</f>
+        <f>IF(B525&gt;0.005,ROUND(B525*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D525" s="2">
-        <f>IF(B525&gt;0,MIN($B$6+$B$7,B525+C525),0)</f>
+        <f>IF(B525&gt;0.005,MIN($B$6+$B$7,B525+C525),0)</f>
         <v>0</v>
       </c>
       <c r="E525" s="2">
@@ -13027,11 +13027,11 @@
         <v>0.0</v>
       </c>
       <c r="C526" s="2">
-        <f>IF(B526&gt;0,ROUND(B526*$B$5/12,2),0)</f>
+        <f>IF(B526&gt;0.005,ROUND(B526*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D526" s="2">
-        <f>IF(B526&gt;0,MIN($B$6+$B$7,B526+C526),0)</f>
+        <f>IF(B526&gt;0.005,MIN($B$6+$B$7,B526+C526),0)</f>
         <v>0</v>
       </c>
       <c r="E526" s="2">
@@ -13052,11 +13052,11 @@
         <v>0.0</v>
       </c>
       <c r="C527" s="2">
-        <f>IF(B527&gt;0,ROUND(B527*$B$5/12,2),0)</f>
+        <f>IF(B527&gt;0.005,ROUND(B527*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D527" s="2">
-        <f>IF(B527&gt;0,MIN($B$6+$B$7,B527+C527),0)</f>
+        <f>IF(B527&gt;0.005,MIN($B$6+$B$7,B527+C527),0)</f>
         <v>0</v>
       </c>
       <c r="E527" s="2">
@@ -13077,11 +13077,11 @@
         <v>0.0</v>
       </c>
       <c r="C528" s="2">
-        <f>IF(B528&gt;0,ROUND(B528*$B$5/12,2),0)</f>
+        <f>IF(B528&gt;0.005,ROUND(B528*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D528" s="2">
-        <f>IF(B528&gt;0,MIN($B$6+$B$7,B528+C528),0)</f>
+        <f>IF(B528&gt;0.005,MIN($B$6+$B$7,B528+C528),0)</f>
         <v>0</v>
       </c>
       <c r="E528" s="2">
@@ -13102,11 +13102,11 @@
         <v>0.0</v>
       </c>
       <c r="C529" s="2">
-        <f>IF(B529&gt;0,ROUND(B529*$B$5/12,2),0)</f>
+        <f>IF(B529&gt;0.005,ROUND(B529*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D529" s="2">
-        <f>IF(B529&gt;0,MIN($B$6+$B$7,B529+C529),0)</f>
+        <f>IF(B529&gt;0.005,MIN($B$6+$B$7,B529+C529),0)</f>
         <v>0</v>
       </c>
       <c r="E529" s="2">
@@ -13127,11 +13127,11 @@
         <v>0.0</v>
       </c>
       <c r="C530" s="2">
-        <f>IF(B530&gt;0,ROUND(B530*$B$5/12,2),0)</f>
+        <f>IF(B530&gt;0.005,ROUND(B530*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D530" s="2">
-        <f>IF(B530&gt;0,MIN($B$6+$B$7,B530+C530),0)</f>
+        <f>IF(B530&gt;0.005,MIN($B$6+$B$7,B530+C530),0)</f>
         <v>0</v>
       </c>
       <c r="E530" s="2">
@@ -13152,11 +13152,11 @@
         <v>0.0</v>
       </c>
       <c r="C531" s="2">
-        <f>IF(B531&gt;0,ROUND(B531*$B$5/12,2),0)</f>
+        <f>IF(B531&gt;0.005,ROUND(B531*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D531" s="2">
-        <f>IF(B531&gt;0,MIN($B$6+$B$7,B531+C531),0)</f>
+        <f>IF(B531&gt;0.005,MIN($B$6+$B$7,B531+C531),0)</f>
         <v>0</v>
       </c>
       <c r="E531" s="2">
@@ -13177,11 +13177,11 @@
         <v>0.0</v>
       </c>
       <c r="C532" s="2">
-        <f>IF(B532&gt;0,ROUND(B532*$B$5/12,2),0)</f>
+        <f>IF(B532&gt;0.005,ROUND(B532*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D532" s="2">
-        <f>IF(B532&gt;0,MIN($B$6+$B$7,B532+C532),0)</f>
+        <f>IF(B532&gt;0.005,MIN($B$6+$B$7,B532+C532),0)</f>
         <v>0</v>
       </c>
       <c r="E532" s="2">
@@ -13202,11 +13202,11 @@
         <v>0.0</v>
       </c>
       <c r="C533" s="2">
-        <f>IF(B533&gt;0,ROUND(B533*$B$5/12,2),0)</f>
+        <f>IF(B533&gt;0.005,ROUND(B533*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D533" s="2">
-        <f>IF(B533&gt;0,MIN($B$6+$B$7,B533+C533),0)</f>
+        <f>IF(B533&gt;0.005,MIN($B$6+$B$7,B533+C533),0)</f>
         <v>0</v>
       </c>
       <c r="E533" s="2">
@@ -13227,11 +13227,11 @@
         <v>0.0</v>
       </c>
       <c r="C534" s="2">
-        <f>IF(B534&gt;0,ROUND(B534*$B$5/12,2),0)</f>
+        <f>IF(B534&gt;0.005,ROUND(B534*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D534" s="2">
-        <f>IF(B534&gt;0,MIN($B$6+$B$7,B534+C534),0)</f>
+        <f>IF(B534&gt;0.005,MIN($B$6+$B$7,B534+C534),0)</f>
         <v>0</v>
       </c>
       <c r="E534" s="2">
@@ -13252,11 +13252,11 @@
         <v>0.0</v>
       </c>
       <c r="C535" s="2">
-        <f>IF(B535&gt;0,ROUND(B535*$B$5/12,2),0)</f>
+        <f>IF(B535&gt;0.005,ROUND(B535*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D535" s="2">
-        <f>IF(B535&gt;0,MIN($B$6+$B$7,B535+C535),0)</f>
+        <f>IF(B535&gt;0.005,MIN($B$6+$B$7,B535+C535),0)</f>
         <v>0</v>
       </c>
       <c r="E535" s="2">
@@ -13277,11 +13277,11 @@
         <v>0.0</v>
       </c>
       <c r="C536" s="2">
-        <f>IF(B536&gt;0,ROUND(B536*$B$5/12,2),0)</f>
+        <f>IF(B536&gt;0.005,ROUND(B536*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D536" s="2">
-        <f>IF(B536&gt;0,MIN($B$6+$B$7,B536+C536),0)</f>
+        <f>IF(B536&gt;0.005,MIN($B$6+$B$7,B536+C536),0)</f>
         <v>0</v>
       </c>
       <c r="E536" s="2">
@@ -13302,11 +13302,11 @@
         <v>0.0</v>
       </c>
       <c r="C537" s="2">
-        <f>IF(B537&gt;0,ROUND(B537*$B$5/12,2),0)</f>
+        <f>IF(B537&gt;0.005,ROUND(B537*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D537" s="2">
-        <f>IF(B537&gt;0,MIN($B$6+$B$7,B537+C537),0)</f>
+        <f>IF(B537&gt;0.005,MIN($B$6+$B$7,B537+C537),0)</f>
         <v>0</v>
       </c>
       <c r="E537" s="2">
@@ -13327,11 +13327,11 @@
         <v>0.0</v>
       </c>
       <c r="C538" s="2">
-        <f>IF(B538&gt;0,ROUND(B538*$B$5/12,2),0)</f>
+        <f>IF(B538&gt;0.005,ROUND(B538*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D538" s="2">
-        <f>IF(B538&gt;0,MIN($B$6+$B$7,B538+C538),0)</f>
+        <f>IF(B538&gt;0.005,MIN($B$6+$B$7,B538+C538),0)</f>
         <v>0</v>
       </c>
       <c r="E538" s="2">
@@ -13352,11 +13352,11 @@
         <v>0.0</v>
       </c>
       <c r="C539" s="2">
-        <f>IF(B539&gt;0,ROUND(B539*$B$5/12,2),0)</f>
+        <f>IF(B539&gt;0.005,ROUND(B539*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D539" s="2">
-        <f>IF(B539&gt;0,MIN($B$6+$B$7,B539+C539),0)</f>
+        <f>IF(B539&gt;0.005,MIN($B$6+$B$7,B539+C539),0)</f>
         <v>0</v>
       </c>
       <c r="E539" s="2">
@@ -13377,11 +13377,11 @@
         <v>0.0</v>
       </c>
       <c r="C540" s="2">
-        <f>IF(B540&gt;0,ROUND(B540*$B$5/12,2),0)</f>
+        <f>IF(B540&gt;0.005,ROUND(B540*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D540" s="2">
-        <f>IF(B540&gt;0,MIN($B$6+$B$7,B540+C540),0)</f>
+        <f>IF(B540&gt;0.005,MIN($B$6+$B$7,B540+C540),0)</f>
         <v>0</v>
       </c>
       <c r="E540" s="2">
@@ -13402,11 +13402,11 @@
         <v>0.0</v>
       </c>
       <c r="C541" s="2">
-        <f>IF(B541&gt;0,ROUND(B541*$B$5/12,2),0)</f>
+        <f>IF(B541&gt;0.005,ROUND(B541*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D541" s="2">
-        <f>IF(B541&gt;0,MIN($B$6+$B$7,B541+C541),0)</f>
+        <f>IF(B541&gt;0.005,MIN($B$6+$B$7,B541+C541),0)</f>
         <v>0</v>
       </c>
       <c r="E541" s="2">
@@ -13427,11 +13427,11 @@
         <v>0.0</v>
       </c>
       <c r="C542" s="2">
-        <f>IF(B542&gt;0,ROUND(B542*$B$5/12,2),0)</f>
+        <f>IF(B542&gt;0.005,ROUND(B542*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D542" s="2">
-        <f>IF(B542&gt;0,MIN($B$6+$B$7,B542+C542),0)</f>
+        <f>IF(B542&gt;0.005,MIN($B$6+$B$7,B542+C542),0)</f>
         <v>0</v>
       </c>
       <c r="E542" s="2">
@@ -13452,11 +13452,11 @@
         <v>0.0</v>
       </c>
       <c r="C543" s="2">
-        <f>IF(B543&gt;0,ROUND(B543*$B$5/12,2),0)</f>
+        <f>IF(B543&gt;0.005,ROUND(B543*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D543" s="2">
-        <f>IF(B543&gt;0,MIN($B$6+$B$7,B543+C543),0)</f>
+        <f>IF(B543&gt;0.005,MIN($B$6+$B$7,B543+C543),0)</f>
         <v>0</v>
       </c>
       <c r="E543" s="2">
@@ -13477,11 +13477,11 @@
         <v>0.0</v>
       </c>
       <c r="C544" s="2">
-        <f>IF(B544&gt;0,ROUND(B544*$B$5/12,2),0)</f>
+        <f>IF(B544&gt;0.005,ROUND(B544*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D544" s="2">
-        <f>IF(B544&gt;0,MIN($B$6+$B$7,B544+C544),0)</f>
+        <f>IF(B544&gt;0.005,MIN($B$6+$B$7,B544+C544),0)</f>
         <v>0</v>
       </c>
       <c r="E544" s="2">
@@ -13502,11 +13502,11 @@
         <v>0.0</v>
       </c>
       <c r="C545" s="2">
-        <f>IF(B545&gt;0,ROUND(B545*$B$5/12,2),0)</f>
+        <f>IF(B545&gt;0.005,ROUND(B545*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D545" s="2">
-        <f>IF(B545&gt;0,MIN($B$6+$B$7,B545+C545),0)</f>
+        <f>IF(B545&gt;0.005,MIN($B$6+$B$7,B545+C545),0)</f>
         <v>0</v>
       </c>
       <c r="E545" s="2">
@@ -13527,11 +13527,11 @@
         <v>0.0</v>
       </c>
       <c r="C546" s="2">
-        <f>IF(B546&gt;0,ROUND(B546*$B$5/12,2),0)</f>
+        <f>IF(B546&gt;0.005,ROUND(B546*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D546" s="2">
-        <f>IF(B546&gt;0,MIN($B$6+$B$7,B546+C546),0)</f>
+        <f>IF(B546&gt;0.005,MIN($B$6+$B$7,B546+C546),0)</f>
         <v>0</v>
       </c>
       <c r="E546" s="2">
@@ -13552,11 +13552,11 @@
         <v>0.0</v>
       </c>
       <c r="C547" s="2">
-        <f>IF(B547&gt;0,ROUND(B547*$B$5/12,2),0)</f>
+        <f>IF(B547&gt;0.005,ROUND(B547*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D547" s="2">
-        <f>IF(B547&gt;0,MIN($B$6+$B$7,B547+C547),0)</f>
+        <f>IF(B547&gt;0.005,MIN($B$6+$B$7,B547+C547),0)</f>
         <v>0</v>
       </c>
       <c r="E547" s="2">
@@ -13577,11 +13577,11 @@
         <v>0.0</v>
       </c>
       <c r="C548" s="2">
-        <f>IF(B548&gt;0,ROUND(B548*$B$5/12,2),0)</f>
+        <f>IF(B548&gt;0.005,ROUND(B548*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D548" s="2">
-        <f>IF(B548&gt;0,MIN($B$6+$B$7,B548+C548),0)</f>
+        <f>IF(B548&gt;0.005,MIN($B$6+$B$7,B548+C548),0)</f>
         <v>0</v>
       </c>
       <c r="E548" s="2">
@@ -13602,11 +13602,11 @@
         <v>0.0</v>
       </c>
       <c r="C549" s="2">
-        <f>IF(B549&gt;0,ROUND(B549*$B$5/12,2),0)</f>
+        <f>IF(B549&gt;0.005,ROUND(B549*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D549" s="2">
-        <f>IF(B549&gt;0,MIN($B$6+$B$7,B549+C549),0)</f>
+        <f>IF(B549&gt;0.005,MIN($B$6+$B$7,B549+C549),0)</f>
         <v>0</v>
       </c>
       <c r="E549" s="2">
@@ -13627,11 +13627,11 @@
         <v>0.0</v>
       </c>
       <c r="C550" s="2">
-        <f>IF(B550&gt;0,ROUND(B550*$B$5/12,2),0)</f>
+        <f>IF(B550&gt;0.005,ROUND(B550*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D550" s="2">
-        <f>IF(B550&gt;0,MIN($B$6+$B$7,B550+C550),0)</f>
+        <f>IF(B550&gt;0.005,MIN($B$6+$B$7,B550+C550),0)</f>
         <v>0</v>
       </c>
       <c r="E550" s="2">
@@ -13652,11 +13652,11 @@
         <v>0.0</v>
       </c>
       <c r="C551" s="2">
-        <f>IF(B551&gt;0,ROUND(B551*$B$5/12,2),0)</f>
+        <f>IF(B551&gt;0.005,ROUND(B551*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D551" s="2">
-        <f>IF(B551&gt;0,MIN($B$6+$B$7,B551+C551),0)</f>
+        <f>IF(B551&gt;0.005,MIN($B$6+$B$7,B551+C551),0)</f>
         <v>0</v>
       </c>
       <c r="E551" s="2">
@@ -13677,11 +13677,11 @@
         <v>0.0</v>
       </c>
       <c r="C552" s="2">
-        <f>IF(B552&gt;0,ROUND(B552*$B$5/12,2),0)</f>
+        <f>IF(B552&gt;0.005,ROUND(B552*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D552" s="2">
-        <f>IF(B552&gt;0,MIN($B$6+$B$7,B552+C552),0)</f>
+        <f>IF(B552&gt;0.005,MIN($B$6+$B$7,B552+C552),0)</f>
         <v>0</v>
       </c>
       <c r="E552" s="2">
@@ -13702,11 +13702,11 @@
         <v>0.0</v>
       </c>
       <c r="C553" s="2">
-        <f>IF(B553&gt;0,ROUND(B553*$B$5/12,2),0)</f>
+        <f>IF(B553&gt;0.005,ROUND(B553*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D553" s="2">
-        <f>IF(B553&gt;0,MIN($B$6+$B$7,B553+C553),0)</f>
+        <f>IF(B553&gt;0.005,MIN($B$6+$B$7,B553+C553),0)</f>
         <v>0</v>
       </c>
       <c r="E553" s="2">
@@ -13727,11 +13727,11 @@
         <v>0.0</v>
       </c>
       <c r="C554" s="2">
-        <f>IF(B554&gt;0,ROUND(B554*$B$5/12,2),0)</f>
+        <f>IF(B554&gt;0.005,ROUND(B554*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D554" s="2">
-        <f>IF(B554&gt;0,MIN($B$6+$B$7,B554+C554),0)</f>
+        <f>IF(B554&gt;0.005,MIN($B$6+$B$7,B554+C554),0)</f>
         <v>0</v>
       </c>
       <c r="E554" s="2">
@@ -13752,11 +13752,11 @@
         <v>0.0</v>
       </c>
       <c r="C555" s="2">
-        <f>IF(B555&gt;0,ROUND(B555*$B$5/12,2),0)</f>
+        <f>IF(B555&gt;0.005,ROUND(B555*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D555" s="2">
-        <f>IF(B555&gt;0,MIN($B$6+$B$7,B555+C555),0)</f>
+        <f>IF(B555&gt;0.005,MIN($B$6+$B$7,B555+C555),0)</f>
         <v>0</v>
       </c>
       <c r="E555" s="2">
@@ -13777,11 +13777,11 @@
         <v>0.0</v>
       </c>
       <c r="C556" s="2">
-        <f>IF(B556&gt;0,ROUND(B556*$B$5/12,2),0)</f>
+        <f>IF(B556&gt;0.005,ROUND(B556*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D556" s="2">
-        <f>IF(B556&gt;0,MIN($B$6+$B$7,B556+C556),0)</f>
+        <f>IF(B556&gt;0.005,MIN($B$6+$B$7,B556+C556),0)</f>
         <v>0</v>
       </c>
       <c r="E556" s="2">
@@ -13802,11 +13802,11 @@
         <v>0.0</v>
       </c>
       <c r="C557" s="2">
-        <f>IF(B557&gt;0,ROUND(B557*$B$5/12,2),0)</f>
+        <f>IF(B557&gt;0.005,ROUND(B557*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D557" s="2">
-        <f>IF(B557&gt;0,MIN($B$6+$B$7,B557+C557),0)</f>
+        <f>IF(B557&gt;0.005,MIN($B$6+$B$7,B557+C557),0)</f>
         <v>0</v>
       </c>
       <c r="E557" s="2">
@@ -13827,11 +13827,11 @@
         <v>0.0</v>
       </c>
       <c r="C558" s="2">
-        <f>IF(B558&gt;0,ROUND(B558*$B$5/12,2),0)</f>
+        <f>IF(B558&gt;0.005,ROUND(B558*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D558" s="2">
-        <f>IF(B558&gt;0,MIN($B$6+$B$7,B558+C558),0)</f>
+        <f>IF(B558&gt;0.005,MIN($B$6+$B$7,B558+C558),0)</f>
         <v>0</v>
       </c>
       <c r="E558" s="2">
@@ -13852,11 +13852,11 @@
         <v>0.0</v>
       </c>
       <c r="C559" s="2">
-        <f>IF(B559&gt;0,ROUND(B559*$B$5/12,2),0)</f>
+        <f>IF(B559&gt;0.005,ROUND(B559*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D559" s="2">
-        <f>IF(B559&gt;0,MIN($B$6+$B$7,B559+C559),0)</f>
+        <f>IF(B559&gt;0.005,MIN($B$6+$B$7,B559+C559),0)</f>
         <v>0</v>
       </c>
       <c r="E559" s="2">
@@ -13877,11 +13877,11 @@
         <v>0.0</v>
       </c>
       <c r="C560" s="2">
-        <f>IF(B560&gt;0,ROUND(B560*$B$5/12,2),0)</f>
+        <f>IF(B560&gt;0.005,ROUND(B560*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D560" s="2">
-        <f>IF(B560&gt;0,MIN($B$6+$B$7,B560+C560),0)</f>
+        <f>IF(B560&gt;0.005,MIN($B$6+$B$7,B560+C560),0)</f>
         <v>0</v>
       </c>
       <c r="E560" s="2">
@@ -13902,11 +13902,11 @@
         <v>0.0</v>
       </c>
       <c r="C561" s="2">
-        <f>IF(B561&gt;0,ROUND(B561*$B$5/12,2),0)</f>
+        <f>IF(B561&gt;0.005,ROUND(B561*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D561" s="2">
-        <f>IF(B561&gt;0,MIN($B$6+$B$7,B561+C561),0)</f>
+        <f>IF(B561&gt;0.005,MIN($B$6+$B$7,B561+C561),0)</f>
         <v>0</v>
       </c>
       <c r="E561" s="2">
@@ -13927,11 +13927,11 @@
         <v>0.0</v>
       </c>
       <c r="C562" s="2">
-        <f>IF(B562&gt;0,ROUND(B562*$B$5/12,2),0)</f>
+        <f>IF(B562&gt;0.005,ROUND(B562*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D562" s="2">
-        <f>IF(B562&gt;0,MIN($B$6+$B$7,B562+C562),0)</f>
+        <f>IF(B562&gt;0.005,MIN($B$6+$B$7,B562+C562),0)</f>
         <v>0</v>
       </c>
       <c r="E562" s="2">
@@ -13952,11 +13952,11 @@
         <v>0.0</v>
       </c>
       <c r="C563" s="2">
-        <f>IF(B563&gt;0,ROUND(B563*$B$5/12,2),0)</f>
+        <f>IF(B563&gt;0.005,ROUND(B563*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D563" s="2">
-        <f>IF(B563&gt;0,MIN($B$6+$B$7,B563+C563),0)</f>
+        <f>IF(B563&gt;0.005,MIN($B$6+$B$7,B563+C563),0)</f>
         <v>0</v>
       </c>
       <c r="E563" s="2">
@@ -13977,11 +13977,11 @@
         <v>0.0</v>
       </c>
       <c r="C564" s="2">
-        <f>IF(B564&gt;0,ROUND(B564*$B$5/12,2),0)</f>
+        <f>IF(B564&gt;0.005,ROUND(B564*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D564" s="2">
-        <f>IF(B564&gt;0,MIN($B$6+$B$7,B564+C564),0)</f>
+        <f>IF(B564&gt;0.005,MIN($B$6+$B$7,B564+C564),0)</f>
         <v>0</v>
       </c>
       <c r="E564" s="2">
@@ -14002,11 +14002,11 @@
         <v>0.0</v>
       </c>
       <c r="C565" s="2">
-        <f>IF(B565&gt;0,ROUND(B565*$B$5/12,2),0)</f>
+        <f>IF(B565&gt;0.005,ROUND(B565*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D565" s="2">
-        <f>IF(B565&gt;0,MIN($B$6+$B$7,B565+C565),0)</f>
+        <f>IF(B565&gt;0.005,MIN($B$6+$B$7,B565+C565),0)</f>
         <v>0</v>
       </c>
       <c r="E565" s="2">
@@ -14027,11 +14027,11 @@
         <v>0.0</v>
       </c>
       <c r="C566" s="2">
-        <f>IF(B566&gt;0,ROUND(B566*$B$5/12,2),0)</f>
+        <f>IF(B566&gt;0.005,ROUND(B566*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D566" s="2">
-        <f>IF(B566&gt;0,MIN($B$6+$B$7,B566+C566),0)</f>
+        <f>IF(B566&gt;0.005,MIN($B$6+$B$7,B566+C566),0)</f>
         <v>0</v>
       </c>
       <c r="E566" s="2">
@@ -14052,11 +14052,11 @@
         <v>0.0</v>
       </c>
       <c r="C567" s="2">
-        <f>IF(B567&gt;0,ROUND(B567*$B$5/12,2),0)</f>
+        <f>IF(B567&gt;0.005,ROUND(B567*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D567" s="2">
-        <f>IF(B567&gt;0,MIN($B$6+$B$7,B567+C567),0)</f>
+        <f>IF(B567&gt;0.005,MIN($B$6+$B$7,B567+C567),0)</f>
         <v>0</v>
       </c>
       <c r="E567" s="2">
@@ -14077,11 +14077,11 @@
         <v>0.0</v>
       </c>
       <c r="C568" s="2">
-        <f>IF(B568&gt;0,ROUND(B568*$B$5/12,2),0)</f>
+        <f>IF(B568&gt;0.005,ROUND(B568*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D568" s="2">
-        <f>IF(B568&gt;0,MIN($B$6+$B$7,B568+C568),0)</f>
+        <f>IF(B568&gt;0.005,MIN($B$6+$B$7,B568+C568),0)</f>
         <v>0</v>
       </c>
       <c r="E568" s="2">
@@ -14102,11 +14102,11 @@
         <v>0.0</v>
       </c>
       <c r="C569" s="2">
-        <f>IF(B569&gt;0,ROUND(B569*$B$5/12,2),0)</f>
+        <f>IF(B569&gt;0.005,ROUND(B569*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D569" s="2">
-        <f>IF(B569&gt;0,MIN($B$6+$B$7,B569+C569),0)</f>
+        <f>IF(B569&gt;0.005,MIN($B$6+$B$7,B569+C569),0)</f>
         <v>0</v>
       </c>
       <c r="E569" s="2">
@@ -14127,11 +14127,11 @@
         <v>0.0</v>
       </c>
       <c r="C570" s="2">
-        <f>IF(B570&gt;0,ROUND(B570*$B$5/12,2),0)</f>
+        <f>IF(B570&gt;0.005,ROUND(B570*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D570" s="2">
-        <f>IF(B570&gt;0,MIN($B$6+$B$7,B570+C570),0)</f>
+        <f>IF(B570&gt;0.005,MIN($B$6+$B$7,B570+C570),0)</f>
         <v>0</v>
       </c>
       <c r="E570" s="2">
@@ -14152,11 +14152,11 @@
         <v>0.0</v>
       </c>
       <c r="C571" s="2">
-        <f>IF(B571&gt;0,ROUND(B571*$B$5/12,2),0)</f>
+        <f>IF(B571&gt;0.005,ROUND(B571*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D571" s="2">
-        <f>IF(B571&gt;0,MIN($B$6+$B$7,B571+C571),0)</f>
+        <f>IF(B571&gt;0.005,MIN($B$6+$B$7,B571+C571),0)</f>
         <v>0</v>
       </c>
       <c r="E571" s="2">
@@ -14177,11 +14177,11 @@
         <v>0.0</v>
       </c>
       <c r="C572" s="2">
-        <f>IF(B572&gt;0,ROUND(B572*$B$5/12,2),0)</f>
+        <f>IF(B572&gt;0.005,ROUND(B572*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D572" s="2">
-        <f>IF(B572&gt;0,MIN($B$6+$B$7,B572+C572),0)</f>
+        <f>IF(B572&gt;0.005,MIN($B$6+$B$7,B572+C572),0)</f>
         <v>0</v>
       </c>
       <c r="E572" s="2">
@@ -14202,11 +14202,11 @@
         <v>0.0</v>
       </c>
       <c r="C573" s="2">
-        <f>IF(B573&gt;0,ROUND(B573*$B$5/12,2),0)</f>
+        <f>IF(B573&gt;0.005,ROUND(B573*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D573" s="2">
-        <f>IF(B573&gt;0,MIN($B$6+$B$7,B573+C573),0)</f>
+        <f>IF(B573&gt;0.005,MIN($B$6+$B$7,B573+C573),0)</f>
         <v>0</v>
       </c>
       <c r="E573" s="2">
@@ -14227,11 +14227,11 @@
         <v>0.0</v>
       </c>
       <c r="C574" s="2">
-        <f>IF(B574&gt;0,ROUND(B574*$B$5/12,2),0)</f>
+        <f>IF(B574&gt;0.005,ROUND(B574*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D574" s="2">
-        <f>IF(B574&gt;0,MIN($B$6+$B$7,B574+C574),0)</f>
+        <f>IF(B574&gt;0.005,MIN($B$6+$B$7,B574+C574),0)</f>
         <v>0</v>
       </c>
       <c r="E574" s="2">
@@ -14252,11 +14252,11 @@
         <v>0.0</v>
       </c>
       <c r="C575" s="2">
-        <f>IF(B575&gt;0,ROUND(B575*$B$5/12,2),0)</f>
+        <f>IF(B575&gt;0.005,ROUND(B575*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D575" s="2">
-        <f>IF(B575&gt;0,MIN($B$6+$B$7,B575+C575),0)</f>
+        <f>IF(B575&gt;0.005,MIN($B$6+$B$7,B575+C575),0)</f>
         <v>0</v>
       </c>
       <c r="E575" s="2">
@@ -14277,11 +14277,11 @@
         <v>0.0</v>
       </c>
       <c r="C576" s="2">
-        <f>IF(B576&gt;0,ROUND(B576*$B$5/12,2),0)</f>
+        <f>IF(B576&gt;0.005,ROUND(B576*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D576" s="2">
-        <f>IF(B576&gt;0,MIN($B$6+$B$7,B576+C576),0)</f>
+        <f>IF(B576&gt;0.005,MIN($B$6+$B$7,B576+C576),0)</f>
         <v>0</v>
       </c>
       <c r="E576" s="2">
@@ -14302,11 +14302,11 @@
         <v>0.0</v>
       </c>
       <c r="C577" s="2">
-        <f>IF(B577&gt;0,ROUND(B577*$B$5/12,2),0)</f>
+        <f>IF(B577&gt;0.005,ROUND(B577*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D577" s="2">
-        <f>IF(B577&gt;0,MIN($B$6+$B$7,B577+C577),0)</f>
+        <f>IF(B577&gt;0.005,MIN($B$6+$B$7,B577+C577),0)</f>
         <v>0</v>
       </c>
       <c r="E577" s="2">
@@ -14327,11 +14327,11 @@
         <v>0.0</v>
       </c>
       <c r="C578" s="2">
-        <f>IF(B578&gt;0,ROUND(B578*$B$5/12,2),0)</f>
+        <f>IF(B578&gt;0.005,ROUND(B578*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D578" s="2">
-        <f>IF(B578&gt;0,MIN($B$6+$B$7,B578+C578),0)</f>
+        <f>IF(B578&gt;0.005,MIN($B$6+$B$7,B578+C578),0)</f>
         <v>0</v>
       </c>
       <c r="E578" s="2">
@@ -14352,11 +14352,11 @@
         <v>0.0</v>
       </c>
       <c r="C579" s="2">
-        <f>IF(B579&gt;0,ROUND(B579*$B$5/12,2),0)</f>
+        <f>IF(B579&gt;0.005,ROUND(B579*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D579" s="2">
-        <f>IF(B579&gt;0,MIN($B$6+$B$7,B579+C579),0)</f>
+        <f>IF(B579&gt;0.005,MIN($B$6+$B$7,B579+C579),0)</f>
         <v>0</v>
       </c>
       <c r="E579" s="2">
@@ -14377,11 +14377,11 @@
         <v>0.0</v>
       </c>
       <c r="C580" s="2">
-        <f>IF(B580&gt;0,ROUND(B580*$B$5/12,2),0)</f>
+        <f>IF(B580&gt;0.005,ROUND(B580*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D580" s="2">
-        <f>IF(B580&gt;0,MIN($B$6+$B$7,B580+C580),0)</f>
+        <f>IF(B580&gt;0.005,MIN($B$6+$B$7,B580+C580),0)</f>
         <v>0</v>
       </c>
       <c r="E580" s="2">
@@ -14402,11 +14402,11 @@
         <v>0.0</v>
       </c>
       <c r="C581" s="2">
-        <f>IF(B581&gt;0,ROUND(B581*$B$5/12,2),0)</f>
+        <f>IF(B581&gt;0.005,ROUND(B581*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D581" s="2">
-        <f>IF(B581&gt;0,MIN($B$6+$B$7,B581+C581),0)</f>
+        <f>IF(B581&gt;0.005,MIN($B$6+$B$7,B581+C581),0)</f>
         <v>0</v>
       </c>
       <c r="E581" s="2">
@@ -14427,11 +14427,11 @@
         <v>0.0</v>
       </c>
       <c r="C582" s="2">
-        <f>IF(B582&gt;0,ROUND(B582*$B$5/12,2),0)</f>
+        <f>IF(B582&gt;0.005,ROUND(B582*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D582" s="2">
-        <f>IF(B582&gt;0,MIN($B$6+$B$7,B582+C582),0)</f>
+        <f>IF(B582&gt;0.005,MIN($B$6+$B$7,B582+C582),0)</f>
         <v>0</v>
       </c>
       <c r="E582" s="2">
@@ -14452,11 +14452,11 @@
         <v>0.0</v>
       </c>
       <c r="C583" s="2">
-        <f>IF(B583&gt;0,ROUND(B583*$B$5/12,2),0)</f>
+        <f>IF(B583&gt;0.005,ROUND(B583*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D583" s="2">
-        <f>IF(B583&gt;0,MIN($B$6+$B$7,B583+C583),0)</f>
+        <f>IF(B583&gt;0.005,MIN($B$6+$B$7,B583+C583),0)</f>
         <v>0</v>
       </c>
       <c r="E583" s="2">
@@ -14477,11 +14477,11 @@
         <v>0.0</v>
       </c>
       <c r="C584" s="2">
-        <f>IF(B584&gt;0,ROUND(B584*$B$5/12,2),0)</f>
+        <f>IF(B584&gt;0.005,ROUND(B584*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D584" s="2">
-        <f>IF(B584&gt;0,MIN($B$6+$B$7,B584+C584),0)</f>
+        <f>IF(B584&gt;0.005,MIN($B$6+$B$7,B584+C584),0)</f>
         <v>0</v>
       </c>
       <c r="E584" s="2">
@@ -14502,11 +14502,11 @@
         <v>0.0</v>
       </c>
       <c r="C585" s="2">
-        <f>IF(B585&gt;0,ROUND(B585*$B$5/12,2),0)</f>
+        <f>IF(B585&gt;0.005,ROUND(B585*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D585" s="2">
-        <f>IF(B585&gt;0,MIN($B$6+$B$7,B585+C585),0)</f>
+        <f>IF(B585&gt;0.005,MIN($B$6+$B$7,B585+C585),0)</f>
         <v>0</v>
       </c>
       <c r="E585" s="2">
@@ -14527,11 +14527,11 @@
         <v>0.0</v>
       </c>
       <c r="C586" s="2">
-        <f>IF(B586&gt;0,ROUND(B586*$B$5/12,2),0)</f>
+        <f>IF(B586&gt;0.005,ROUND(B586*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D586" s="2">
-        <f>IF(B586&gt;0,MIN($B$6+$B$7,B586+C586),0)</f>
+        <f>IF(B586&gt;0.005,MIN($B$6+$B$7,B586+C586),0)</f>
         <v>0</v>
       </c>
       <c r="E586" s="2">
@@ -14552,11 +14552,11 @@
         <v>0.0</v>
       </c>
       <c r="C587" s="2">
-        <f>IF(B587&gt;0,ROUND(B587*$B$5/12,2),0)</f>
+        <f>IF(B587&gt;0.005,ROUND(B587*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D587" s="2">
-        <f>IF(B587&gt;0,MIN($B$6+$B$7,B587+C587),0)</f>
+        <f>IF(B587&gt;0.005,MIN($B$6+$B$7,B587+C587),0)</f>
         <v>0</v>
       </c>
       <c r="E587" s="2">
@@ -14577,11 +14577,11 @@
         <v>0.0</v>
       </c>
       <c r="C588" s="2">
-        <f>IF(B588&gt;0,ROUND(B588*$B$5/12,2),0)</f>
+        <f>IF(B588&gt;0.005,ROUND(B588*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D588" s="2">
-        <f>IF(B588&gt;0,MIN($B$6+$B$7,B588+C588),0)</f>
+        <f>IF(B588&gt;0.005,MIN($B$6+$B$7,B588+C588),0)</f>
         <v>0</v>
       </c>
       <c r="E588" s="2">
@@ -14602,11 +14602,11 @@
         <v>0.0</v>
       </c>
       <c r="C589" s="2">
-        <f>IF(B589&gt;0,ROUND(B589*$B$5/12,2),0)</f>
+        <f>IF(B589&gt;0.005,ROUND(B589*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D589" s="2">
-        <f>IF(B589&gt;0,MIN($B$6+$B$7,B589+C589),0)</f>
+        <f>IF(B589&gt;0.005,MIN($B$6+$B$7,B589+C589),0)</f>
         <v>0</v>
       </c>
       <c r="E589" s="2">
@@ -14627,11 +14627,11 @@
         <v>0.0</v>
       </c>
       <c r="C590" s="2">
-        <f>IF(B590&gt;0,ROUND(B590*$B$5/12,2),0)</f>
+        <f>IF(B590&gt;0.005,ROUND(B590*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D590" s="2">
-        <f>IF(B590&gt;0,MIN($B$6+$B$7,B590+C590),0)</f>
+        <f>IF(B590&gt;0.005,MIN($B$6+$B$7,B590+C590),0)</f>
         <v>0</v>
       </c>
       <c r="E590" s="2">
@@ -14652,11 +14652,11 @@
         <v>0.0</v>
       </c>
       <c r="C591" s="2">
-        <f>IF(B591&gt;0,ROUND(B591*$B$5/12,2),0)</f>
+        <f>IF(B591&gt;0.005,ROUND(B591*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D591" s="2">
-        <f>IF(B591&gt;0,MIN($B$6+$B$7,B591+C591),0)</f>
+        <f>IF(B591&gt;0.005,MIN($B$6+$B$7,B591+C591),0)</f>
         <v>0</v>
       </c>
       <c r="E591" s="2">
@@ -14677,11 +14677,11 @@
         <v>0.0</v>
       </c>
       <c r="C592" s="2">
-        <f>IF(B592&gt;0,ROUND(B592*$B$5/12,2),0)</f>
+        <f>IF(B592&gt;0.005,ROUND(B592*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D592" s="2">
-        <f>IF(B592&gt;0,MIN($B$6+$B$7,B592+C592),0)</f>
+        <f>IF(B592&gt;0.005,MIN($B$6+$B$7,B592+C592),0)</f>
         <v>0</v>
       </c>
       <c r="E592" s="2">
@@ -14702,11 +14702,11 @@
         <v>0.0</v>
       </c>
       <c r="C593" s="2">
-        <f>IF(B593&gt;0,ROUND(B593*$B$5/12,2),0)</f>
+        <f>IF(B593&gt;0.005,ROUND(B593*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D593" s="2">
-        <f>IF(B593&gt;0,MIN($B$6+$B$7,B593+C593),0)</f>
+        <f>IF(B593&gt;0.005,MIN($B$6+$B$7,B593+C593),0)</f>
         <v>0</v>
       </c>
       <c r="E593" s="2">
@@ -14727,11 +14727,11 @@
         <v>0.0</v>
       </c>
       <c r="C594" s="2">
-        <f>IF(B594&gt;0,ROUND(B594*$B$5/12,2),0)</f>
+        <f>IF(B594&gt;0.005,ROUND(B594*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D594" s="2">
-        <f>IF(B594&gt;0,MIN($B$6+$B$7,B594+C594),0)</f>
+        <f>IF(B594&gt;0.005,MIN($B$6+$B$7,B594+C594),0)</f>
         <v>0</v>
       </c>
       <c r="E594" s="2">
@@ -14752,11 +14752,11 @@
         <v>0.0</v>
       </c>
       <c r="C595" s="2">
-        <f>IF(B595&gt;0,ROUND(B595*$B$5/12,2),0)</f>
+        <f>IF(B595&gt;0.005,ROUND(B595*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D595" s="2">
-        <f>IF(B595&gt;0,MIN($B$6+$B$7,B595+C595),0)</f>
+        <f>IF(B595&gt;0.005,MIN($B$6+$B$7,B595+C595),0)</f>
         <v>0</v>
       </c>
       <c r="E595" s="2">
@@ -14777,11 +14777,11 @@
         <v>0.0</v>
       </c>
       <c r="C596" s="2">
-        <f>IF(B596&gt;0,ROUND(B596*$B$5/12,2),0)</f>
+        <f>IF(B596&gt;0.005,ROUND(B596*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D596" s="2">
-        <f>IF(B596&gt;0,MIN($B$6+$B$7,B596+C596),0)</f>
+        <f>IF(B596&gt;0.005,MIN($B$6+$B$7,B596+C596),0)</f>
         <v>0</v>
       </c>
       <c r="E596" s="2">
@@ -14802,11 +14802,11 @@
         <v>0.0</v>
       </c>
       <c r="C597" s="2">
-        <f>IF(B597&gt;0,ROUND(B597*$B$5/12,2),0)</f>
+        <f>IF(B597&gt;0.005,ROUND(B597*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D597" s="2">
-        <f>IF(B597&gt;0,MIN($B$6+$B$7,B597+C597),0)</f>
+        <f>IF(B597&gt;0.005,MIN($B$6+$B$7,B597+C597),0)</f>
         <v>0</v>
       </c>
       <c r="E597" s="2">
@@ -14827,11 +14827,11 @@
         <v>0.0</v>
       </c>
       <c r="C598" s="2">
-        <f>IF(B598&gt;0,ROUND(B598*$B$5/12,2),0)</f>
+        <f>IF(B598&gt;0.005,ROUND(B598*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D598" s="2">
-        <f>IF(B598&gt;0,MIN($B$6+$B$7,B598+C598),0)</f>
+        <f>IF(B598&gt;0.005,MIN($B$6+$B$7,B598+C598),0)</f>
         <v>0</v>
       </c>
       <c r="E598" s="2">
@@ -14852,11 +14852,11 @@
         <v>0.0</v>
       </c>
       <c r="C599" s="2">
-        <f>IF(B599&gt;0,ROUND(B599*$B$5/12,2),0)</f>
+        <f>IF(B599&gt;0.005,ROUND(B599*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D599" s="2">
-        <f>IF(B599&gt;0,MIN($B$6+$B$7,B599+C599),0)</f>
+        <f>IF(B599&gt;0.005,MIN($B$6+$B$7,B599+C599),0)</f>
         <v>0</v>
       </c>
       <c r="E599" s="2">
@@ -14877,11 +14877,11 @@
         <v>0.0</v>
       </c>
       <c r="C600" s="2">
-        <f>IF(B600&gt;0,ROUND(B600*$B$5/12,2),0)</f>
+        <f>IF(B600&gt;0.005,ROUND(B600*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D600" s="2">
-        <f>IF(B600&gt;0,MIN($B$6+$B$7,B600+C600),0)</f>
+        <f>IF(B600&gt;0.005,MIN($B$6+$B$7,B600+C600),0)</f>
         <v>0</v>
       </c>
       <c r="E600" s="2">
@@ -14902,11 +14902,11 @@
         <v>0.0</v>
       </c>
       <c r="C601" s="2">
-        <f>IF(B601&gt;0,ROUND(B601*$B$5/12,2),0)</f>
+        <f>IF(B601&gt;0.005,ROUND(B601*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D601" s="2">
-        <f>IF(B601&gt;0,MIN($B$6+$B$7,B601+C601),0)</f>
+        <f>IF(B601&gt;0.005,MIN($B$6+$B$7,B601+C601),0)</f>
         <v>0</v>
       </c>
       <c r="E601" s="2">
@@ -14927,11 +14927,11 @@
         <v>0.0</v>
       </c>
       <c r="C602" s="2">
-        <f>IF(B602&gt;0,ROUND(B602*$B$5/12,2),0)</f>
+        <f>IF(B602&gt;0.005,ROUND(B602*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D602" s="2">
-        <f>IF(B602&gt;0,MIN($B$6+$B$7,B602+C602),0)</f>
+        <f>IF(B602&gt;0.005,MIN($B$6+$B$7,B602+C602),0)</f>
         <v>0</v>
       </c>
       <c r="E602" s="2">
@@ -14952,11 +14952,11 @@
         <v>0.0</v>
       </c>
       <c r="C603" s="2">
-        <f>IF(B603&gt;0,ROUND(B603*$B$5/12,2),0)</f>
+        <f>IF(B603&gt;0.005,ROUND(B603*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D603" s="2">
-        <f>IF(B603&gt;0,MIN($B$6+$B$7,B603+C603),0)</f>
+        <f>IF(B603&gt;0.005,MIN($B$6+$B$7,B603+C603),0)</f>
         <v>0</v>
       </c>
       <c r="E603" s="2">
@@ -14977,11 +14977,11 @@
         <v>0.0</v>
       </c>
       <c r="C604" s="2">
-        <f>IF(B604&gt;0,ROUND(B604*$B$5/12,2),0)</f>
+        <f>IF(B604&gt;0.005,ROUND(B604*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D604" s="2">
-        <f>IF(B604&gt;0,MIN($B$6+$B$7,B604+C604),0)</f>
+        <f>IF(B604&gt;0.005,MIN($B$6+$B$7,B604+C604),0)</f>
         <v>0</v>
       </c>
       <c r="E604" s="2">
@@ -15002,11 +15002,11 @@
         <v>0.0</v>
       </c>
       <c r="C605" s="2">
-        <f>IF(B605&gt;0,ROUND(B605*$B$5/12,2),0)</f>
+        <f>IF(B605&gt;0.005,ROUND(B605*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D605" s="2">
-        <f>IF(B605&gt;0,MIN($B$6+$B$7,B605+C605),0)</f>
+        <f>IF(B605&gt;0.005,MIN($B$6+$B$7,B605+C605),0)</f>
         <v>0</v>
       </c>
       <c r="E605" s="2">
@@ -15027,11 +15027,11 @@
         <v>0.0</v>
       </c>
       <c r="C606" s="2">
-        <f>IF(B606&gt;0,ROUND(B606*$B$5/12,2),0)</f>
+        <f>IF(B606&gt;0.005,ROUND(B606*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D606" s="2">
-        <f>IF(B606&gt;0,MIN($B$6+$B$7,B606+C606),0)</f>
+        <f>IF(B606&gt;0.005,MIN($B$6+$B$7,B606+C606),0)</f>
         <v>0</v>
       </c>
       <c r="E606" s="2">
@@ -15052,11 +15052,11 @@
         <v>0.0</v>
       </c>
       <c r="C607" s="2">
-        <f>IF(B607&gt;0,ROUND(B607*$B$5/12,2),0)</f>
+        <f>IF(B607&gt;0.005,ROUND(B607*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D607" s="2">
-        <f>IF(B607&gt;0,MIN($B$6+$B$7,B607+C607),0)</f>
+        <f>IF(B607&gt;0.005,MIN($B$6+$B$7,B607+C607),0)</f>
         <v>0</v>
       </c>
       <c r="E607" s="2">
@@ -15077,11 +15077,11 @@
         <v>0.0</v>
       </c>
       <c r="C608" s="2">
-        <f>IF(B608&gt;0,ROUND(B608*$B$5/12,2),0)</f>
+        <f>IF(B608&gt;0.005,ROUND(B608*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D608" s="2">
-        <f>IF(B608&gt;0,MIN($B$6+$B$7,B608+C608),0)</f>
+        <f>IF(B608&gt;0.005,MIN($B$6+$B$7,B608+C608),0)</f>
         <v>0</v>
       </c>
       <c r="E608" s="2">
@@ -15102,11 +15102,11 @@
         <v>0.0</v>
       </c>
       <c r="C609" s="2">
-        <f>IF(B609&gt;0,ROUND(B609*$B$5/12,2),0)</f>
+        <f>IF(B609&gt;0.005,ROUND(B609*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D609" s="2">
-        <f>IF(B609&gt;0,MIN($B$6+$B$7,B609+C609),0)</f>
+        <f>IF(B609&gt;0.005,MIN($B$6+$B$7,B609+C609),0)</f>
         <v>0</v>
       </c>
       <c r="E609" s="2">
@@ -15127,11 +15127,11 @@
         <v>0.0</v>
       </c>
       <c r="C610" s="2">
-        <f>IF(B610&gt;0,ROUND(B610*$B$5/12,2),0)</f>
+        <f>IF(B610&gt;0.005,ROUND(B610*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D610" s="2">
-        <f>IF(B610&gt;0,MIN($B$6+$B$7,B610+C610),0)</f>
+        <f>IF(B610&gt;0.005,MIN($B$6+$B$7,B610+C610),0)</f>
         <v>0</v>
       </c>
       <c r="E610" s="2">
@@ -15152,11 +15152,11 @@
         <v>0.0</v>
       </c>
       <c r="C611" s="2">
-        <f>IF(B611&gt;0,ROUND(B611*$B$5/12,2),0)</f>
+        <f>IF(B611&gt;0.005,ROUND(B611*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D611" s="2">
-        <f>IF(B611&gt;0,MIN($B$6+$B$7,B611+C611),0)</f>
+        <f>IF(B611&gt;0.005,MIN($B$6+$B$7,B611+C611),0)</f>
         <v>0</v>
       </c>
       <c r="E611" s="2">
@@ -15177,11 +15177,11 @@
         <v>0.0</v>
       </c>
       <c r="C612" s="2">
-        <f>IF(B612&gt;0,ROUND(B612*$B$5/12,2),0)</f>
+        <f>IF(B612&gt;0.005,ROUND(B612*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D612" s="2">
-        <f>IF(B612&gt;0,MIN($B$6+$B$7,B612+C612),0)</f>
+        <f>IF(B612&gt;0.005,MIN($B$6+$B$7,B612+C612),0)</f>
         <v>0</v>
       </c>
       <c r="E612" s="2">
@@ -15202,11 +15202,11 @@
         <v>0.0</v>
       </c>
       <c r="C613" s="2">
-        <f>IF(B613&gt;0,ROUND(B613*$B$5/12,2),0)</f>
+        <f>IF(B613&gt;0.005,ROUND(B613*$B$5/12,2),0)</f>
         <v>0</v>
       </c>
       <c r="D613" s="2">
-        <f>IF(B613&gt;0,MIN($B$6+$B$7,B613+C613),0)</f>
+        <f>IF(B613&gt;0.005,MIN($B$6+$B$7,B613+C613),0)</f>
         <v>0</v>
       </c>
       <c r="E613" s="2">
